--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-301.1800000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.32371e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-67.977</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01575433911882367</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.002420856610799424</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5938962360121987</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.438078902229933</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.41886389617179</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.46502329812238</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.608x + -26512.619</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.415310947677803e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2410.448049943559</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8233824879217257</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-219.55</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.27875e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-69.797</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3082210242587696</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.4001349527665555</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9851943755169142</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.973079492317973</v>
+      </c>
+      <c r="J3" t="n">
+        <v>32.13402264537932</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.01872816656795</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.368x + -29617.468</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.011366547673892e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2359.317609741626</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000215e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8233904233678926</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-188.1500000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.26419e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.614</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05466237942121539</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5841807909604443</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.37890442890439</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.077980456026101</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.26730097667861</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.01905782346823</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.369x + -29107.971</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.104590956173844e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2320.892027456387</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8234056046303073</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-181.5500000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.25594e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.068</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1577680525164098</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3983709273182684</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.078103315343079</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.897581699346319</v>
+      </c>
+      <c r="J5" t="n">
+        <v>33.44492000605699</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.12382935935841</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.759x + -29473.007</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.913578887301948e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2285.819968891027</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000264e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8235052362770372</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-171.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.25026e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.563</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.210745233968823</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4955786736021136</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.023116089613024</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.887412587412628</v>
+      </c>
+      <c r="J6" t="n">
+        <v>26.70903795241034</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.91615261099008</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.006x + -27455.432</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.633778004024203e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2250.227692224049</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000649e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8236709883754649</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-160.3499999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.24808e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.98</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1611263736263687</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4287380699893699</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.01772151898723</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.635299145299093</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.58949857001882</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.90613361084375</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.972x + -26980.663</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.302073442772051e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2215.639602243329</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000001893e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8238878356306352</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-159.2499999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.24698e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.328</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.06542057126002078</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6303688896605991</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.63129725553657</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.078027739177654</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.72401982761939</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.375x + -25375.119</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.84599431062659e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2181.660894811766</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000093e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8241075674849676</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-146.8899999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2455e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.651</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2910290237466855</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3506963788301051</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7874269005848177</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.990821256038708</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.1539926175388</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.98038142467519</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.231x + -26702.595</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.606193303780935e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2149.985626840088</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000253e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8243225855446978</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-140.25</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.24504e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.977</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3619582664526448</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3673437499999841</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9012208657048381</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.035925612848683</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.88729463789171</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.86205760765881</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.822x + -25554.504</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.715284651378623e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2119.966405870303</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000007374e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8245325174446646</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-140.1899999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.24506e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-73.235</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1365533417420565</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7330079791909093</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.709923149880702</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.125179212934257</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.78245531365859</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.561x + -24703.076</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.079048882999982e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2091.506950994974</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000531e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8247652552925044</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-213.23</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.19786e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66.867</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1802071346375068</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5785915492957741</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.451624933404409</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.492857142857138</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.34008100768899</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.50598793787236</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.723x + -30660.022</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.075396332685376e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2757.57009933029</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000562e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8239737920711422</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-165.1400000000003</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.23489e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-68.33799999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5511930585682971</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8598851517637072</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.476523582405947</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.515280464216627</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.37491727899916</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.361x + -28099.156</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.180535016618823e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2628.895283461112</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8243521382922012</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-155.3899999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.24766e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-68.764</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4578002244669354</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7948696383515627</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.919136172765452</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.636610738254964</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.30000873053365</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.163x + -27112.953</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.034578536778927e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2583.028355356804</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000002802e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8244304712573326</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-156.7000000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.2551e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-69.04900000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1092522179974737</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9742179072275774</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.57566820276496</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.110467289719682</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.020735313118535</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.03164750472718</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.503x + -25225.262</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.736386840969188e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2549.26393814946</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001974e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8245172483092832</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-152.4200000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.26554e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-69.342</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1400000000000118</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5327956989247116</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.151415525114055</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.835872235872209</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.018957815828966</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.66596044994454</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.710x + -23117.854</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.734692249110454e-13</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2517.318306344748</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8246550093241634</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-130.25</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.2703e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-69.624</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5412054120541531</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.06234309623428</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.670918665886443</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.836098981077149</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.01050864696612</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.454x + -24527.172</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.441533647954122e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2485.543471191366</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8248736551774272</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-121.5599999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.2791e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-69.913</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.128387734915926</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.39521094640839</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.709373097991405</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.729118250170881</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.67699592376789</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.733x + -22627.340</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.033304018910433e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2453.951101126005</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8251194166917888</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-130.9200000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2848e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-70.16200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02919896640827236</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.317182497331934</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.022502424830318</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.694043321299626</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.29826115100296</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.016x + -20780.160</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.948437754477155e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2424.035502175891</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000309e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8254046977366076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-118.8299999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.29191e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-70.395</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4997405966277689</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6021596244131465</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.518346456692978</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.133608949416354</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.2712164075494</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.968x + -20449.782</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.254071109854306e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2395.761097073741</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8256932436551032</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-115.3699999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.29819e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-70.666</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.135006119951049</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7344244984160547</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.004152712659027</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.759837092731814</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.75832372707492</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.143x + -18462.857</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.263430458204318e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2368.05908293269</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.826008644242491</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-114.7399999999998</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.30304e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-70.87</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2628532974428122</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8041509433962931</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.140512333965837</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.154610951008759</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.78996971321338</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.190x + -18355.648</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.464301324947811e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2340.665388963708</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000083176e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8263375904205432</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-101.0600000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.30797e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-71.11799999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3218403547672029</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8378521126760539</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.279046129788924</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.381999999999885</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.45126095644565</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 8.711x + -17156.135</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.631307393981735e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2313.782422428646</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8266969867697139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-96.05000000000018</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.31384e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-71.34699999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5927016645326141</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.244992947813806</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.65286738351246</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.917790262172152</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.17518335639733</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 8.355x + -16227.324</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.706458700410186e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2286.936405802662</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8270545364460221</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-87.21000000000004</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.32064e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-71.587</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.337026239067047</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7141509433962131</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.6944600938967</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.715100864553279</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>82.28085262154526</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 7.378x + -14059.649</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.203271988021492e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2260.62424563863</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000003576e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.827436630697757</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-83.31999999999994</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.32462e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-71.815</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5232258064515973</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.40558659217883</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.475256916996072</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.577396893411866</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>81.89092025946779</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 7.018x + -13177.044</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.890564578953269e-12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2234.884909838563</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8278227955550146</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-81.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.33055e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-72.033</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4485568760610772</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3660098522167387</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8396864686468625</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.070670391061319</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>81.68937925222713</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 6.846x + -12692.447</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>212.4812723188523</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2223.75627310775</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.380833949190603e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8209815868380305</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-77.52999999999997</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.33788e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-72.25700000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3045882352941126</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.083644189383168</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.084695817490599</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.190494296577945</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80.74281756918141</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 6.135x + -11148.922</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>206.861668179744</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2197.477832755963</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.40792039562032e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8195633697059974</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-72.68000000000006</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.34189e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-72.465</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6690962099124523</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4795226130653476</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.24868651488616</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.827852586817832</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>80.35663735634036</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 5.885x + -10532.813</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.47998912098377e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2156.5440610064</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8290581426232366</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-69.31999999999994</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.34684e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-72.685</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3172727272727013</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.179904306220037</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.312691466083251</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.819213114754107</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>79.50211583326845</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 5.397x + -9469.765</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.072714896296982e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2130.146285283991</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8294699482796445</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-56.75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.35226e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.93300000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.109752066115668</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.109416445623318</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.43614457831318</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3869.825999999938</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7.020329891677771</v>
+      </c>
+      <c r="K21" t="n">
+        <v>75.13928367587035</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 3.769x + -6233.095</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>5.966431116877329e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2103.727843958342</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000169e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8298965896031515</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-63.19000000000005</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.35769e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-73.16800000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1232809430255364</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4383522727273231</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8847385272144909</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.583150800337002</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>76.35452891099136</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 4.119x + -6862.052</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.614793725905983e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2078.340268613085</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8303157667479026</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-296.21</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.11868e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-65.646</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1098455598455433</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8441637630661368</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.59448123620311</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.576652692679827</v>
+      </c>
+      <c r="J2" t="n">
+        <v>42.35610608393787</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.47740357708268</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.642x + -32182.283</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.59442307260886e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2915.954589926854</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000087e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8220981973325222</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-223.5999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.14598e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.401</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1445640473627439</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6408829174663828</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.086684599865488</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.933839022334632</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.02176452649005</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.40729846195727</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.449x + -30102.179</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.117241225930757e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2809.082698967638</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000192e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.822087465869785</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-186.9000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.14944e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.93000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1706691109074243</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7913617886179025</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.306173496540693</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.670488044546418</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.270687415058976</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.6031663285822</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.006x + -31151.404</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.825737732110178e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2779.103494459513</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000637e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8219147326852899</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-188.9300000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.15305e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.21599999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08549734244494966</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6131639722863405</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.241092814371271</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.204386792452783</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.783876611418</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.33117075431733</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.245x + -28949.677</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.137282678068201e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2752.227983503276</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8219250745537761</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-160.8200000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.15907e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.55500000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.185291005290999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9443946188340352</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.407814149947247</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.088693373268399</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.41581355186332</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.472x + -29241.180</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.034390778127763e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2723.276059701413</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8220989419735825</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-162.1199999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.16352e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.83199999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1442020665901259</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3890710382513604</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.092827256425648</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.273155929038388</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.669810255625353</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.17673575532864</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.851x + -27379.587</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.519918255122773e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2690.199763488245</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000006e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8223384124082387</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-152.3099999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.17234e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-69.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1422163588390584</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8428044280441966</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.244055433989742</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.127853260869508</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.07080889104667</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.595x + -26427.706</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.342906300109985e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2655.487400575091</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000878e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8225911753494387</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-145.4200000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.17781e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.401</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.008898305084734433</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.4965798045602346</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.209722222222238</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.978830823737812</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.93251314701644</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.277x + -25369.223</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.939495515668526e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2623.329471766109</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000696e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.822851788607222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-136.5500000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.18538e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.67400000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.07467532467532592</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9119820828667052</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.888967343336295</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.504748908296921</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.7572836689485</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 10.898x + -24202.139</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.706620553159562e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2592.348915597973</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000002331e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8230841242048756</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-139.04</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.1917e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.905</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1583710407239683</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1160780669144989</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6299870466321181</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.853763440860316</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7256032147506585</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.48698420787788</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.361x + -22687.219</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.127431609741145e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2563.02284458603</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000386e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8233149760934312</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-126.3000000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.19756e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-70.202</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.03377403846153303</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.2061965811966036</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9566897918732133</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.95441176470595</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.05746256025441</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.607x + -20732.166</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.859345571410595e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2534.730011262545</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000299e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8235502638891337</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-118.4299999999998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.20377e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.38200000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1953846153846251</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7242004264392643</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.460220994475175</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.540000000000011</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.19017320735685</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.828x + -21023.296</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.239488607329279e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2507.234636243908</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000076e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8238066182788678</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-112.27</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.20764e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.608</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.07652270210409827</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.897517730496484</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.261376404494422</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.359563409563315</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.0597828895913</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.611x + -20322.202</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>9.359231651318668e-11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2480.629410918885</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8240655230017409</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-109.25</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.2129e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.81</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3312101910827592</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9457249070630582</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.36671675431999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.87262124002458</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.8901954968315</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 9.342x + -19518.573</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.973967348233778e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2454.630797555196</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000107e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8243369069067397</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-103.8200000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.21886e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-71.004</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2723427331887356</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4587778855480008</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.881640624999999</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.153864059590277</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.74941351313974</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.130x + -18859.623</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.45003817486749e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2428.185404745177</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000084e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8246493687092759</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-94.85000000000036</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.22354e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.259</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3485675306957466</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.011145833333333</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.50279569892478</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.426176176176132</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>83.06412942258612</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 8.220x + -16703.090</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.970517935624754e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2401.983530257716</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8249770548153392</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-95.95000000000027</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.22879e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.473</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3025757575757648</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4279661016948995</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9549635036496484</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.920328282828279</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.7794422333864</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 7.893x + -15828.722</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>9.627140714989261e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2375.280445590422</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000782e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8253435196826101</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-88.6099999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.2336e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.724</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0949105914718029</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4800632911392513</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.006318082788606</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.934666666666655</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.04578403029792</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 7.157x + -14100.434</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.29289101531848e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2347.508273255232</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8257276008085358</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-86.05999999999995</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.23833e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-71.91800000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2085981308411403</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.520278099652362</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.153530950305083</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.137734537873553</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>81.99373261841544</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 7.110x + -13842.076</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.075119883901549e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2320.071994721753</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8261241899379637</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-83.0799999999997</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.24414e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.128</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3473491773308761</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6112412177986117</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9204152249134706</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.947265077139058</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>81.49581742349871</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 6.688x + -12814.541</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.777177309290668e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2292.691756936614</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8265312128622175</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-72.85000000000014</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.24924e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.405</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1813106796116408</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4153474903474602</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.620291616038882</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.153587443946236</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>79.35258673424356</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 5.319x + -9880.900</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.319115630141283e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2264.958903157273</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000029683e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8269492738709937</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-491.8600000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.22095e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-63.118</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1220486111111091</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7008005822416385</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.347007366482514</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.093574186431338</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.32987887890171</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.03803453681488</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.576x + -23184.556</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.175791473510778e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2713.895048948965</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8226209941140983</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-293.5999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.29232e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.717</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3162087912088161</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5683640303358953</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.548994974874328</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.045325389550874</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.13223226671916</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.74417511292592</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.438x + -29079.413</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.613124622069379e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2462.955700602321</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000027034e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8231340282117653</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-247.6500000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.28638e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-69.13500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4070301291248039</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.41938283510127</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.020137299771166</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.854754505904197</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.07278178709917</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.89763405516429</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.943x + -29117.097</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.866575263797109e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2391.660990471461</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.823235943927017</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-210.2399999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.27723e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-69.914</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1895899053627418</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.121363040629071</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.664781491002689</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.585289163391339</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41.67392060173427</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.22216617206217</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.144x + -31187.051</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>6.252834411476645e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2350.065362473626</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8232282947826255</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-210.6399999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.27069e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-70.39400000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2501182033096876</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.476215738284692</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9676067073171003</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.858579088471822</v>
+      </c>
+      <c r="J6" t="n">
+        <v>33.16918599947498</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.09348935868756</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.644x + -29621.553</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.230498828401794e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2314.022769149911</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000214e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8233952573463059</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-201.05</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.26984e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-70.85599999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.08515624999999723</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05123966942147855</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9014038876890423</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.702127659574402</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.18575678552921</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.85877222536543</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.811x + -27432.601</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>8.075233288206583e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2278.892645829634</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000017374e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8235924097749807</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-191.8599999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.26812e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.202</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3318627450980517</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3161538461538473</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.832163742690067</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.872208883553501</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33.56191142807042</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.16905453599718</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.934x + -29333.320</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.655333856793304e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2243.353996478384</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8238469270957746</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-189.78</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.26852e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-71.56100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1249999999999899</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2471956224350241</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.154967502321266</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.69293924466331</v>
+      </c>
+      <c r="J9" t="n">
+        <v>28.45347751775343</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.03247901786544</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.418x + -27820.637</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.270528794341422e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2208.580200814447</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8241363452360965</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-177.24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.26951e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-71.896</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5293670886075377</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.479439252336388</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.164573991031357</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.363161711385153</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.00875072411803</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.25867427784912</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.293x + -29172.183</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.592247695071056e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2175.345500587092</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000348e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8244195535222555</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-163.5600000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.27246e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.233</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6108481262326875</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.952957359009571</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.866439135380954</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.969736842105297</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.92381894142269</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.28112362820183</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.385x + -28947.258</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.279332546116162e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2144.019452580205</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8247099040408369</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-346.3000000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.2132e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-64.26000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04047393364928762</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9164908916586658</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.285432473444619</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.188699551569524</v>
+      </c>
+      <c r="J2" t="n">
+        <v>30.79266949516174</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.15439600006185</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.796x + -29342.820</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.129234063954383e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2845.948042091551</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000011e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8222241979160136</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-243.1199999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.23485e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-66.61</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1341726618705011</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3148979591836766</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.114285714285739</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.914896373057035</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.29955128211617</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.43070239531707</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.513x + -29607.453</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.320284713375369e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2736.327374494666</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001217e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8223748627702101</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-205.0600000000004</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.23952e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.298</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02356389214536648</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8233937397034857</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.6879128137385</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.63320920785384</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36.48417236147111</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.68678733577332</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.259x + -30951.444</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.500191835565047e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2694.955799695584</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001151e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8223615677257196</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-187.1099999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.24564e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-67.818</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1156488549618358</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4454767726161264</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9403225806451495</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.093678707224317</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20.74049801809669</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.27414832266591</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.096x + -27757.302</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.607539098225247e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2662.460103949847</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8223624909571154</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-163.1100000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.25379e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.19799999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03056603773584505</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9198096885813276</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.962694651320219</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.734963768115925</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.4115635437113</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.460x + -28307.209</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.87015092989737e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2629.468457631028</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8225151409289783</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-163.8399999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.26035e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.468</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2323809523809657</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3945261437908364</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.756717687074789</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.155678160919474</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.7414236785126</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.13057979456765</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.738x + -26260.520</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.249466642569781e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2597.564665233623</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000504e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8226875476927562</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-145.2800000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.26865e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-68.752</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2087649402390367</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7957403651115159</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.456453488372073</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.871153846153851</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.30570000872549</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.178x + -27001.913</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.515287388830445e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2567.732605236057</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8228613277627862</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-139.7200000000003</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2748e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.023</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6843888070692123</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.814323784143848</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.726468481375337</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.22706329430788</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.977x + -26231.710</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.014359159496607e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2537.481018250261</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8230824662655123</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-134.9499999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.28008e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.279</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1899147727272484</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9814285714285785</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.669898605830247</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.747302608074345</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.11867932411808</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.709x + -25330.308</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.11453348004922e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2508.488900648735</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000142e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8233193736138535</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-132.77</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.28817e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.54000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2600000000000281</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9957678355501665</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.346407624633448</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.555450500556183</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.81339168368416</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 11.017x + -23485.125</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.147155854151793e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2479.048500598249</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8236209212926803</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-117.1100000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.29736e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-69.783</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4852941176471022</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.008219178082242</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.484637350085594</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.932651485912797</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.77473285432448</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.935x + -23048.369</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.515346933716058e-11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2449.680458364413</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8239501520027088</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-121.6799999999998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.30153e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.101</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.01227495908346669</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6361702127659588</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.146112886048983</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.839500912964054</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.05446588382652</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 9.602x + -19862.955</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.229944194588911e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2419.819317598993</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000196e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8243123698056691</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-115.5599999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.30755e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.367</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1147627416520174</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.489266547406058</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.109372236958438</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.703928571428658</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.69720606072319</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.054x + -18460.854</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.89318947762486e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2391.138214515793</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000123e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8246902588566679</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-109.8500000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.31374e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.598</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2696458684654143</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3953455571226735</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.9396378269618257</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.513562091503234</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>83.58707067747386</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 8.897x + -17913.343</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>6.788585878560492e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2362.419624778477</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.825081230583431</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-100.1099999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.3206e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-70.815</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.2981461286804799</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7021837349397462</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.379871692061011</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.618269747447632</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>83.4736610241447</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 8.741x + -17384.610</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.555286651214082e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2334.801746610437</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000007969e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8254671928352076</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-101.28</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.32423e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.054</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.07460317460317165</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2896718146718121</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.314396887159522</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.988235294117687</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>83.27502334215912</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 8.481x + -16647.101</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.797281210055078e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2307.80205912893</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000512e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8258693475308785</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-93.81999999999971</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.33175e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.309</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.03333333333333663</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.4337625178826869</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.161163032191077</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.47549842602309</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82.39789008811356</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 7.493x + -14434.272</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.31020319319979e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2280.930890948543</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8262783354061436</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-89.97000000000003</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.3373e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.505</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1572496263079194</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3895072992700779</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.316071428571395</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.602076970067188</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.35609982469042</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 7.451x + -14192.040</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.333047516245059e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2254.676723734933</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000014787e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8266918028915716</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-84.19000000000005</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.34266e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-71.741</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4541910331383483</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.3448359659781006</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.727453416149203</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.770740223463655</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>81.76283892476937</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 6.908x + -12937.893</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.460650300269002e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2227.970377721017</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000839e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8271051462140998</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-80.11999999999989</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.34789e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-71.97199999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3286451612903075</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6538261997405984</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.336847710330121</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.804721549636801</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>81.06612897739333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 6.361x + -11706.661</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>214.0256189424472</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2207.389570706674</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.363638032946128e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8213434993113213</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-68.63999999999987</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.35429e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3031746031746149</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7615631691648806</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.370565749235529</v>
+      </c>
+      <c r="I22" t="n">
+        <v>601.8416753926655</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.042389155177109</v>
+      </c>
+      <c r="K22" t="n">
+        <v>79.43008667995478</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 5.359x + -9586.325</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.193834251485703e-12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2174.872196386693</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8279655906794595</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-562.9000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.20078e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-60.202</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1040333796940281</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4511385816525647</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.285525070955493</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.053920181149171</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.08887945959876</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.00035781414279</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.145x + -21007.564</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.041846685555586e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2855.65665514407</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8204215626802764</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-284.3699999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.33503e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.166</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.537909186905984</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9771992818670909</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.627439024390211</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.618230277185515</v>
+      </c>
+      <c r="J3" t="n">
+        <v>39.97008204670375</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.8198252162511</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.682x + -29762.804</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.158947464803032e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2460.840346272374</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000072e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8214456177052405</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-227.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.3384e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-68.83799999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3777960526315622</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6938461538461717</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.315348208248859</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.392331768388165</v>
+      </c>
+      <c r="J4" t="n">
+        <v>36.82064225037296</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.01260614144554</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.346x + -29847.436</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.56846089924788e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2373.551420344808</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000021011e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8215641561774838</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-214.8199999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.33246e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-69.529</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2934782608695099</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.798453038674102</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.613242009132506</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.757312252964392</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.96204194217254</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.85115141078617</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.786x + -28068.067</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.334758227760508e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2333.537564832739</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8215930723633277</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-203.5799999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.32974e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-69.97199999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8006726457398874</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4491614255765128</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.762284820031518</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.653255131964861</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.88959434536302</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.93285633669966</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.064x + -28245.927</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.736481504495536e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2300.107205920785</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8216909541616423</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-197.6800000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.33135e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-70.355</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1713080168776374</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4923588039867518</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.064382239382267</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.398034591195023</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25.60772086173403</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.78326682271455</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.563x + -26819.058</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.425876005003627e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2269.287311431293</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000003992e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8217908062015363</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-191.5999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.33142e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-70.691</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1009324009323884</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5792279411765235</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9313294797687937</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.509238249594776</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.23455671333188</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.83747668403021</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.740x + -26811.475</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.288055662162158e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2237.907758369383</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000146e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8219453149809027</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-180.4000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.33424e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-71.036</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3611260053619244</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5078864353312126</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9369418132610492</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.52115518441191</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.80868672096129</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.83781108931814</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.742x + -26448.811</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.374342983002057e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2206.807522206962</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8221534722933097</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-175.6000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.33649e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-71.327</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.009266409266412539</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4111398963730439</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.112142038946202</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.49617834394908</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.74560314492659</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.88364294295634</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.895x + -26404.514</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.40292540559079e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2176.098698950425</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000004222e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8223805662431459</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-168.73</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.34023e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-71.66</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9051109736292599</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.697284832594463</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.119095126010044</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.619261944851646</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.66028011763316</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 13.177x + -24635.613</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.742571044718832e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2146.827841083477</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8226377992422598</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-330.77</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.23371e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-64.34099999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0809061488673158</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1023454157782567</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8288996372430152</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.029238095238278</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.00162207437533</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.97606556400319</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.375x + -28098.656</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.516309795665231e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2832.479758107666</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8218694643867974</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-220.8800000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.25922e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-66.69</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3217267552181979</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8364925373134581</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.549771092217152</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.675247175141254</v>
+      </c>
+      <c r="J3" t="n">
+        <v>43.30795581512977</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.65134975680714</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.150x + -30921.529</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.558440525962691e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2709.448860319832</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001159e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8221500865567808</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-200.9100000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.26895e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2802492809203852</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8331536388139784</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.434259727134891</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.594490644490689</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.00766521514688</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.64293230504576</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.125x + -30303.515</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.013495115745491e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2665.179508477985</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8221849038869791</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-190.5099999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.27855e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-67.661</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02744886975242326</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2292573143286009</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.184395318595566</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.224987775061072</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.21012721728083</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.30943588204234</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.188x + -27674.417</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.912568205178581e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2631.110526981742</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.822277231834462</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-172.0099999999998</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.28716e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.130037546933661</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6874023437500634</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.442436727486785</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.646309898565917</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.48201254710068</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.655x + -28438.269</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.395283970990217e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2595.744206171674</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000622e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8225465393082664</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-171.2999999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.29535e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.31399999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.00669856459328325</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7736998514114718</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.110273556231087</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.233889418493688</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12.84863328387019</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.15700123226335</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.802x + -26079.561</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.097861802157766e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2561.390606631469</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000005275e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8228030056295692</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-163.3799999999997</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.30346e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-68.599</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.05796105383735044</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8685685685686056</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.173164392462603</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.309392547217955</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.38602817894076</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.08619277063494</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.632x + -25375.223</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.303595998404677e-12</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2529.255322404762</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8230318450763889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-164</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.30949e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-68.84</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2586466165413275</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2469072164948295</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6554216867469626</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.452947424322871</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14.82751354128434</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.9062979099409</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.219x + -24136.306</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.1400411281563e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2499.487328830749</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.823273375898105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-146.4000000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.31837e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.161</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3041666666666669</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7017297297297563</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.511480362537788</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.199494949494985</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.87960821906553</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.160x + -23748.956</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.264077801157476e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2470.362966036245</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000007143e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.823525410754765</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-141.6200000000003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.32653e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.352</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.03813333333334976</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.035560588901516</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.365130111524119</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.042268041237089</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.94434092385205</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 11.304x + -23811.521</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.736970107731786e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2442.704039156864</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000017284e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8237838347778901</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-139.8899999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.33275e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-69.622</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2040350877193175</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.6175544794189241</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.328907168037511</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.700172018348655</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.137615845988649</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.55642893097483</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.494x + -21778.605</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.703072928447077e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2415.773380742343</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000004286e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8240697090143507</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-133.5500000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.33855e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-69.863</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3227790432801905</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4027737226277694</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.696302003081642</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.824007330482529</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.854485635614069</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.50021061082096</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 10.386x + -21320.763</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.796389850219528e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2389.21634967006</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000065e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8243677071297558</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-136.3100000000002</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.34328e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.08499999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0133086876155333</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.03235955056179655</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.066167023554578</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.220197740113074</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.021444629477305</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.26300311926651</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 9.954x + -20159.528</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.824930918373567e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2362.603687215268</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000197e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8246845197610774</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-112.4700000000003</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.35094e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.354</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2200371057513933</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.057422680412351</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.587196110210733</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.006810709253115</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.13873340762382</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 9.741x + -19518.801</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.473080802826887e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2336.332762416729</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000004113e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8250098687698577</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-100.4500000000003</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.35864e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-70.565</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5773881499395267</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9449699054170516</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.641075650118218</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.995249597423582</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.04451907982248</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 9.586x + -18992.521</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.667522414754383e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2310.940986393167</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000308e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8253397893911518</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-113.97</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.36385e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-70.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2260245901639544</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7179012345678809</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.246932952924365</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>83.513309699044</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 8.795x + -17149.488</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.002937517158759e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2285.377112737908</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000010564e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8256829077079835</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-101.8799999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.37029e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.01300000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1558904109588963</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.3820568927789874</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.128640308582387</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.718535031847054</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>83.38946512490763</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 8.629x + -16631.399</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.75017130529854e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2259.916081722555</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000010925e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8260437833206654</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-96.98000000000002</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.37695e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.254</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.04683698296836433</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3808618504435921</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.165964172813463</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.891546391752542</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>82.83076238342716</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 7.950x + -15087.003</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.186025180523736e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2234.719984376756</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000713e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.826405951208726</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-83.66000000000008</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.3828e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-71.467</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3764705882353017</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5918181818181696</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.673052245646301</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.454574811625402</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>82.57466012938002</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 7.673x + -14364.122</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.112743634453489e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2209.293118100206</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000094e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8267873042100341</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-81.50999999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.38759e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-71.675</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5140703517588011</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7286191536747774</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.462418831168834</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.608103545300964</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>82.45793970557759</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 7.553x + -13962.155</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.77775154945498e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2183.771627758495</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000501e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8271748786062363</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-77.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.39541e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-71.93300000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2981967213114778</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.4647777777777389</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.179924242424327</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.298817034700333</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>81.27339245855396</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 6.515x + -11790.909</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.409358536093444e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2157.791352734257</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000728e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8275681735177792</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-518.3900000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.2951e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-61.452</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4160278745644348</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9753569211669666</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.625624024961014</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.661461051062258</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.09758723828508</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.55552605910758</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.853x + -21350.109</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.288473459606596e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2640.53776847434</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000024413e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8242984860832673</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-275.29</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.3632e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-67.754</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5007399577167322</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.313785310734404</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.601752402487271</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.968958893584331</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.9674588641219</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.91443960564308</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.000x + -29479.661</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.054871269118177e-12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2349.503403421527</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000012586e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8251235722242805</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-236.45</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.35847e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-69.217</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1504424778761148</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4919014084506652</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.888244766505627</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.847430058555695</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.59654714010141</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.76694640305577</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.511x + -27298.556</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.317944178429333e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2279.715259742693</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8252129352714285</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-207.6599999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.35448e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-69.95099999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04457274826789211</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2721719457013488</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.137408088235341</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.86001213592231</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.68672015104412</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.81296358917007</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.660x + -27115.736</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.899469626949051e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2242.36267692865</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.825212890366271</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-187.1000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.35076e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-70.405</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4699186991869847</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8912816041848701</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.544372093023271</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.292757371960615</v>
+      </c>
+      <c r="J6" t="n">
+        <v>37.34837149265547</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.07823582328332</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.587x + -28667.123</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>186.1080253299602</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2211.862347563584</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.382244200619495e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8159039158184652</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-183.5699999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.35186e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-70.762</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.312907608695647</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4997455470738197</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.265306122448948</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.038978668390476</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28.97436229499401</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.90297124511967</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 13.961x + -26993.331</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.675000967276618e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2180.94831184644</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000015584e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8254023148446075</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-168.99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.35504e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.176</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0251213592232991</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4588571428571035</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.468770764119623</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.950234427327516</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.47506797986986</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.85662652813693</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 13.804x + -26286.683</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.101096256983958e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2148.73215383579</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000427e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8256323614413871</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-160.3999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.35779e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-71.517</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5572078907435488</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2037720033529005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.529585152838445</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.894195583596128</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25.41187575372227</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.86279157538219</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.825x + -25941.163</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.252752228430736e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2115.756282430544</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8259010857081182</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-159.4199999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.36144e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-71.828</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5006482982171756</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.784459459459438</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8204139228598286</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.287045454545467</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.54277039829208</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.65624277715484</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.165x + -24281.903</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.290137604425771e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2084.486497516774</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8261887128519112</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-155.6899999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.36593e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.128</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3775688605583363</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.699446554381619</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.103115810472999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.43695396758204</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.530x + -22725.384</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.546089694979385e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2054.950347124875</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000053009e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8264845125175559</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-274.1100000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.25991e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-64.831</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5723749999999403</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.312478031634365</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.685557894736832</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.170070648683279</v>
+      </c>
+      <c r="J2" t="n">
+        <v>101.8860566448791</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.63524863918384</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.102x + -32128.849</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.018497924899276e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2766.750533962472</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8252253134487614</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-201.1000000000004</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.27602e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-66.834</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1120231213872788</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5649017933390124</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.376593465452596</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.604135338345854</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.16175837511034</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.35730990994833</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.314x + -28740.528</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.482444433917909e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2667.402029510698</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8254504445705302</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-174.9000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.28726e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-67.413</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1365753424657578</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8870329670329908</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.791141034727171</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.553001053001076</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.35317263523869</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.303x + -28195.257</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.750350788854377e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2621.92439174166</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8255304963047722</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-157.3599999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.29696e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-67.84699999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3219745222929785</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.635750853242292</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.457060849598147</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.557975034674046</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.09924036513074</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.663x + -26301.867</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.947837157897419e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2585.253226771898</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8256235195939408</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-150.7200000000003</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.3042e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-68.17400000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.001942740286291946</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6601859024012048</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.530011520737455</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.77569648093854</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.97962710126282</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.383x + -25313.033</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.953554496488012e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2551.158655032718</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001853e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8257504715414885</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-140.5300000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.31277e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-68.489</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3398137369033932</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8916666666666568</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.454398663697092</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.92703020792467</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.75671805038773</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.897x + -23891.638</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.166065075582911e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2519.883370992912</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000656e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8259028022210997</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-131.4099999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.32009e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-68.764</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2668428005283719</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8126948775055723</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.583255269320848</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.592251815980618</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.64720096815343</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.673x + -23111.431</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.009672237852387e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2490.440800320759</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001725e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8260852607427001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-118.0699999999997</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.3284e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-69.053</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1503042596348779</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8238645747316141</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.557203907203963</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.822773777946202</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.35774023042264</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.122x + -21624.099</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.021825600564301e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2461.192357789637</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001761e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8263354310367195</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-110.3499999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.33579e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-69.334</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2535256410256428</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.080947012401343</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.715498392282939</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.681988873435331</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.98921141455334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.497x + -19985.387</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>6.280938585877643e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2431.737844928728</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8266642920549608</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-106.0599999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.34293e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-69.59699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2878995433790343</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7415413533834884</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.8355057705363</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.962480680061886</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.69762411592801</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 9.054x + -18778.431</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.971303253004576e-11</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2402.151911987078</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8270396121778827</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-109.5900000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.34913e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-69.849</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1959459459459592</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.3916809605488831</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.632053742802306</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.623685800604308</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.55078183886248</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 8.847x + -18100.473</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.92107921365423e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2371.647713132661</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000153e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8274583103561436</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-101.48</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.35566e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-70.139</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0144110275689139</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.022893772893792</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.447757475083052</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.34336877448235</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>82.96560479702194</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 8.104x + -16302.093</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.593582725294761e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2342.020353029596</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8278971848263614</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-109.9100000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.36302e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-70.392</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3474254742547305</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001884057971008142</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4034155597723186</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.181689141234956</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.55800099243558</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 7.656x + -15156.612</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.326223305162802e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2311.659965095116</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8283458396673902</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-82.61000000000013</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.37135e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-70.64</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.5605324074074219</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.640379403794121</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.584392699811261</v>
+      </c>
+      <c r="I15" t="n">
+        <v>596.9381465517057</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7.13848497661192</v>
+      </c>
+      <c r="K15" t="n">
+        <v>81.75868938459175</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 6.904x + -13392.695</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.345693589351309e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2281.619374699685</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8288164091000833</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-74.67000000000007</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.37598e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-70.94199999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5507763975154822</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8870071684588102</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.683710961420757</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5140.91018518183</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7.44372470179876</v>
+      </c>
+      <c r="K16" t="n">
+        <v>80.34619777210902</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 5.879x + -11112.436</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>9.047915646325895e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2252.811461591035</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000587e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8292669708099299</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-88.48000000000002</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.38251e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-71.146</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1912977099236809</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3223985890652784</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.169556840077134</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.643558282208636</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>81.52007563877578</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 6.707x + -12675.786</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>4.918555176209131e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2223.671646583151</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000016e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8297354120510478</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-72.79999999999995</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.38904e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-71.414</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0245330012453345</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.646008869179612</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.894066985646014</v>
+      </c>
+      <c r="I18" t="n">
+        <v>384.7309065933882</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.346020165896984</v>
+      </c>
+      <c r="K18" t="n">
+        <v>79.82663183593523</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 5.573x + -10239.691</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>5.034582895725092e-12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2195.094847795729</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000055e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8302051714946416</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-63.86999999999989</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.3969e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-71.696</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1837096774193462</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.7720183486238464</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.737690631808223</v>
+      </c>
+      <c r="I19" t="n">
+        <v>935.6347245408055</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6.555251169481611</v>
+      </c>
+      <c r="K19" t="n">
+        <v>76.98816776782273</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 4.327x + -7640.346</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.432931517641712e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2165.992430881933</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8306727791216445</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-59.73000000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.40298e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-71.95399999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1939580764488281</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.50547147846332</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.573830845771184</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3400.357575757806</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6.825901617404211</v>
+      </c>
+      <c r="K20" t="n">
+        <v>74.31179345564641</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 3.560x + -6039.215</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.660458373077296e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2137.132715118158</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000002782e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8311611615719875</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-57.72000000000003</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.41056e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-72.226</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.08940170940169886</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6626112759643923</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.216792249730922</v>
+      </c>
+      <c r="I21" t="n">
+        <v>785.3685236767851</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.044026163819121</v>
+      </c>
+      <c r="K21" t="n">
+        <v>72.70441040408457</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 3.212x + -5310.017</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.92893508239642e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2108.33894790977</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.0000000000003e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8316375930716181</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-47.51999999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.41613e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-72.45</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3944367176634253</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7806768558952196</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.437854609929031</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>7.078815382166172</v>
+      </c>
+      <c r="K22" t="n">
+        <v>60.72049696681752</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 1.783x + -2490.739</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.570472746967216e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2081.046908599812</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000047997e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8321209555534694</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-491.5599999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.46739e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-65.28700000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.148071495766701</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4071428571428432</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.168761220825841</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.485561797752806</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13.14007254924212</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.81095713910436</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.222x + -18277.826</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>162.6737353687826</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2162.228436743672</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.521377037002092e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8096593554514424</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-246.52</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.46746e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-71.31699999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.09920159680639046</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8220216606497706</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.163281249999947</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.802617801047157</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26.92419408642001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.13256016928565</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.792x + -25629.094</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.323351647208594e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1916.660323873801</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8277510929816904</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-190.22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.4432e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-72.71299999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3014109347442888</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4793048973144131</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.291356382978837</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.710690789473662</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.59098951499389</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.43465412858183</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.049x + -26886.779</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.793287299827609e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1860.144351889452</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.827919603522968</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-170.6099999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.43125e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-73.36799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1564978190786663</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8641974120131196</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.822934842459651</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.371834686067927</v>
+      </c>
+      <c r="J5" t="n">
+        <v>90.59509644737403</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.25734388198219</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.287x + -25053.523</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>5.202144731797539e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1826.396393760933</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8280891351992294</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-147.0799999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.42612e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-73.81</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.199054820415874</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.056344410876083</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.572947976878567</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.281065918653554</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38.56824195629877</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.67647062046937</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.220x + -27927.971</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.696445211737782e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1794.850558248901</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8283454907159454</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-145.3600000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.42319e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-74.22199999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2498593865056875</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.197721990346083</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.857777937773798</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.520881064632068</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.578145077480873</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.27229855641723</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.349x + -24313.640</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.459990444312311e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1762.967762768062</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8286812595417239</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-150.23</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.42295e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-74.518</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09165315017653425</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6457027632349499</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.32994630754852</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.385940363634762</v>
+      </c>
+      <c r="J8" t="n">
+        <v>37.68441587148421</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.06161589753195</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.525x + -22522.850</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.839332757947256e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1731.525000378381</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000668e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8290768969353889</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-128.0800000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.42347e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-74.91800000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5078999893496523</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8008512156044596</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.045334526025893</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.667334227684406</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.21354702955047</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.110x + -23105.850</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.278126041582441e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1700.93793595741</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.829482136310853</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-121.51</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.42372e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-75.209</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5554768075315711</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.25520627560639</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.399482020099188</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.848198602599174</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.27818843129664</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.373x + -23136.454</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.727421379567755e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1671.997039690264</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8298934578820746</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-117.97</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.42542e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-75.501</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4094739861139957</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.159202638471224</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.077429005319718</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.016222018158163</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.0168749706659</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.361x + -21211.210</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.501400957957264e-07</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1645.259342180763</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000010075e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8303035760423194</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>85.46502329812238</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.608x + -26512.619</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26512.61895166363</v>
       </c>
       <c r="Y2" t="n">
         <v>7.415310947677803e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2410.448049943559</v>
+        <v>301.1800000000003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000015e-08</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>86.01872816656795</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.368x + -29617.468</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29617.4678162674</v>
       </c>
       <c r="Y3" t="n">
         <v>6.011366547673892e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2359.317609741626</v>
+        <v>219.55</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000215e-08</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>86.01905782346823</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.369x + -29107.971</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-29107.97135255189</v>
       </c>
       <c r="Y4" t="n">
         <v>2.104590956173844e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2320.892027456387</v>
+        <v>195.04</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000011e-08</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>86.12382935935841</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.759x + -29473.007</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-29473.00660329694</v>
       </c>
       <c r="Y5" t="n">
         <v>3.913578887301948e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2285.819968891027</v>
+        <v>189.4500000000003</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000264e-08</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>85.91615261099008</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.006x + -27455.432</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-27455.43201969614</v>
       </c>
       <c r="Y6" t="n">
         <v>4.633778004024203e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2250.227692224049</v>
+        <v>189.3399999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000649e-08</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>85.90613361084375</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.972x + -26980.663</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26980.66251654135</v>
       </c>
       <c r="Y7" t="n">
         <v>5.302073442772051e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2215.639602243329</v>
+        <v>184.96</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001893e-08</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>85.72401982761939</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.375x + -25375.119</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-25375.11933162333</v>
       </c>
       <c r="Y8" t="n">
         <v>4.84599431062659e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2181.660894811766</v>
+        <v>185.8100000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000093e-08</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>85.98038142467519</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.231x + -26702.595</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-26702.59540322645</v>
       </c>
       <c r="Y9" t="n">
         <v>1.606193303780935e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2149.985626840088</v>
+        <v>175.1299999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000253e-08</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>85.86205760765881</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.822x + -25554.504</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-25554.5036609288</v>
       </c>
       <c r="Y10" t="n">
         <v>2.715284651378623e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2119.966405870303</v>
+        <v>172.5699999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000007374e-08</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>85.78245531365859</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.561x + -24703.076</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-24703.07649563891</v>
       </c>
       <c r="Y11" t="n">
         <v>5.079048882999982e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2091.506950994974</v>
+        <v>172.5999999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000531e-08</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>85.50598793787236</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.723x + -30660.022</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-30660.02153502501</v>
       </c>
       <c r="Y2" t="n">
         <v>2.075396332685376e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2757.57009933029</v>
+        <v>230.75</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000562e-08</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>85.37491727899916</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.361x + -28099.156</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-28099.15557419353</v>
       </c>
       <c r="Y3" t="n">
         <v>1.180535016618823e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2628.895283461112</v>
+        <v>212.8600000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>85.30000873053365</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.163x + -27112.953</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-27112.95277324877</v>
       </c>
       <c r="Y4" t="n">
         <v>1.034578536778927e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2583.028355356804</v>
+        <v>207.6300000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000002802e-08</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>85.03164750472718</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.503x + -25225.262</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-25225.26241618456</v>
       </c>
       <c r="Y5" t="n">
         <v>1.736386840969188e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2549.26393814946</v>
+        <v>211.9200000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001974e-08</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>84.66596044994454</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.710x + -23117.854</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-23117.85400731676</v>
       </c>
       <c r="Y6" t="n">
         <v>1.734692249110454e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>2517.318306344748</v>
+        <v>214.9300000000003</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>85.01050864696612</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.454x + -24527.172</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-24527.17234841071</v>
       </c>
       <c r="Y7" t="n">
         <v>2.441533647954122e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2485.543471191366</v>
+        <v>194.1900000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>84.67699592376789</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.733x + -22627.340</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-22627.33967337245</v>
       </c>
       <c r="Y8" t="n">
         <v>7.033304018910433e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2453.951101126005</v>
+        <v>193.1000000000004</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>84.29826115100296</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.016x + -20780.160</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20780.16045926497</v>
       </c>
       <c r="Y9" t="n">
         <v>3.948437754477155e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2424.035502175891</v>
+        <v>204.8800000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000309e-08</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>84.2712164075494</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.968x + -20449.782</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20449.78197501574</v>
       </c>
       <c r="Y10" t="n">
         <v>3.254071109854306e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2395.761097073741</v>
+        <v>195.1700000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>83.75832372707492</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 9.143x + -18462.857</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18462.85703754847</v>
       </c>
       <c r="Y11" t="n">
         <v>3.263430458204318e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>2368.05908293269</v>
+        <v>198.3400000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>83.78996971321338</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 9.190x + -18355.648</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-18355.64765139138</v>
       </c>
       <c r="Y12" t="n">
         <v>2.464301324947811e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2340.665388963708</v>
+        <v>196.7599999999998</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000083176e-08</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>83.45126095644565</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 8.711x + -17156.135</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-17156.13490481778</v>
       </c>
       <c r="Y13" t="n">
         <v>6.631307393981735e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2313.782422428646</v>
+        <v>187.3900000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>83.17518335639733</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 8.355x + -16227.324</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-16227.32390932036</v>
       </c>
       <c r="Y14" t="n">
         <v>2.706458700410186e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2286.936405802662</v>
+        <v>183.9900000000002</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>82.28085262154526</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 7.378x + -14059.649</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-14059.64894322642</v>
       </c>
       <c r="Y15" t="n">
         <v>5.203271988021492e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2260.62424563863</v>
+        <v>181.8099999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000003576e-08</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>81.89092025946779</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 7.018x + -13177.044</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-13177.04396881474</v>
       </c>
       <c r="Y16" t="n">
         <v>9.890564578953269e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>2234.884909838563</v>
+        <v>178.8799999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>81.68937925222713</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 6.846x + -12692.447</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12692.44696356226</v>
       </c>
       <c r="Y17" t="n">
         <v>212.4812723188523</v>
       </c>
       <c r="Z17" t="n">
-        <v>2223.75627310775</v>
+        <v>179.4399999999998</v>
       </c>
       <c r="AA17" t="n">
         <v>1.380833949190603e-08</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>80.74281756918141</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 6.135x + -11148.922</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11148.92228587478</v>
       </c>
       <c r="Y18" t="n">
         <v>206.861668179744</v>
       </c>
       <c r="Z18" t="n">
-        <v>2197.477832755963</v>
+        <v>180.1099999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.40792039562032e-08</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>80.35663735634036</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 5.885x + -10532.813</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-10532.81262975529</v>
       </c>
       <c r="Y19" t="n">
         <v>4.47998912098377e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2156.5440610064</v>
+        <v>174.76</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000101e-08</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>79.50211583326845</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 5.397x + -9469.765</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9469.764652776803</v>
       </c>
       <c r="Y20" t="n">
         <v>2.072714896296982e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2130.146285283991</v>
+        <v>172.0899999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000007e-08</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>75.13928367587035</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 3.769x + -6233.095</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-6233.095012111938</v>
       </c>
       <c r="Y21" t="n">
         <v>5.966431116877329e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>2103.727843958342</v>
+        <v>164.22</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000169e-08</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>76.35452891099136</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 4.119x + -6862.052</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-6862.051675706942</v>
       </c>
       <c r="Y22" t="n">
         <v>2.614793725905983e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>2078.340268613085</v>
+        <v>175.1400000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000005e-08</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>85.47740357708268</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.642x + -32182.283</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-32182.28269469809</v>
       </c>
       <c r="Y2" t="n">
         <v>3.59442307260886e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2915.954589926854</v>
+        <v>296.21</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000087e-08</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>85.40729846195727</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.449x + -30102.179</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30102.17944132951</v>
       </c>
       <c r="Y3" t="n">
         <v>1.117241225930757e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2809.082698967638</v>
+        <v>236.8599999999997</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000192e-08</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>85.6031663285822</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.006x + -31151.404</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31151.40379032491</v>
       </c>
       <c r="Y4" t="n">
         <v>2.825737732110178e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2779.103494459513</v>
+        <v>218.29</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000637e-08</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>85.33117075431733</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.245x + -28949.677</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-28949.67655070433</v>
       </c>
       <c r="Y5" t="n">
         <v>1.137282678068201e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2752.227983503276</v>
+        <v>224.3400000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>85.41581355186332</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.472x + -29241.180</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-29241.17998515358</v>
       </c>
       <c r="Y6" t="n">
         <v>1.034390778127763e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2723.276059701413</v>
+        <v>208.8099999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>85.17673575532864</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.851x + -27379.587</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-27379.5874050473</v>
       </c>
       <c r="Y7" t="n">
         <v>1.519918255122773e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2690.199763488245</v>
+        <v>211.9499999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000006e-08</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>85.07080889104667</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.595x + -26427.706</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-26427.70560616207</v>
       </c>
       <c r="Y8" t="n">
         <v>4.342906300109985e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2655.487400575091</v>
+        <v>208.0099999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000878e-08</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>84.93251314701644</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.277x + -25369.223</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25369.22255346926</v>
       </c>
       <c r="Y9" t="n">
         <v>2.939495515668526e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>2623.329471766109</v>
+        <v>204.6400000000003</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000696e-08</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>84.7572836689485</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 10.898x + -24202.139</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-24202.13855168521</v>
       </c>
       <c r="Y10" t="n">
         <v>8.706620553159562e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>2592.348915597973</v>
+        <v>202.3800000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002331e-08</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>84.48698420787788</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.361x + -22687.219</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-22687.21857963646</v>
       </c>
       <c r="Y11" t="n">
         <v>2.127431609741145e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2563.02284458603</v>
+        <v>206.9699999999998</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000386e-08</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>84.05746256025441</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 9.607x + -20732.166</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-20732.16588551441</v>
       </c>
       <c r="Y12" t="n">
         <v>1.859345571410595e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2534.730011262545</v>
+        <v>202.0100000000002</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000299e-08</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>84.19017320735685</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 9.828x + -21023.296</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-21023.29645173243</v>
       </c>
       <c r="Y13" t="n">
         <v>4.239488607329279e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2507.234636243908</v>
+        <v>193.7199999999998</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000076e-08</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>84.0597828895913</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 9.611x + -20322.202</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-20322.20238838419</v>
       </c>
       <c r="Y14" t="n">
         <v>9.359231651318668e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>2480.629410918885</v>
+        <v>189.77</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>83.8901954968315</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 9.342x + -19518.573</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-19518.57299755024</v>
       </c>
       <c r="Y15" t="n">
         <v>4.973967348233778e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2454.630797555196</v>
+        <v>188.4900000000002</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000107e-08</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>83.74941351313974</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 9.130x + -18859.623</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-18859.62323868267</v>
       </c>
       <c r="Y16" t="n">
         <v>3.45003817486749e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2428.185404745177</v>
+        <v>184.0999999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000084e-08</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>83.06412942258612</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 8.220x + -16703.090</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-16703.09046365776</v>
       </c>
       <c r="Y17" t="n">
         <v>5.970517935624754e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>2401.983530257716</v>
+        <v>181.3400000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000009e-08</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>82.7794422333864</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 7.893x + -15828.722</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-15828.72167675995</v>
       </c>
       <c r="Y18" t="n">
         <v>9.627140714989261e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>2375.280445590422</v>
+        <v>183.9200000000001</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000782e-08</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>82.04578403029792</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 7.157x + -14100.434</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14100.43427184204</v>
       </c>
       <c r="Y19" t="n">
         <v>5.29289101531848e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2347.508273255232</v>
+        <v>182.1400000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>81.99373261841544</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 7.110x + -13842.076</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-13842.07640576425</v>
       </c>
       <c r="Y20" t="n">
         <v>7.075119883901549e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>2320.071994721753</v>
+        <v>178.3299999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000034e-08</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>81.49581742349871</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 6.688x + -12814.541</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-12814.5406608731</v>
       </c>
       <c r="Y21" t="n">
         <v>3.777177309290668e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>2292.691756936614</v>
+        <v>177.4199999999998</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>79.35258673424356</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 5.319x + -9880.900</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9880.899672481139</v>
       </c>
       <c r="Y22" t="n">
         <v>4.319115630141283e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2264.958903157273</v>
+        <v>174.4800000000002</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000029683e-08</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.03803453681488</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.576x + -23184.556</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-23184.55585740781</v>
       </c>
       <c r="Y2" t="n">
         <v>3.175791473510778e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2713.895048948965</v>
+        <v>491.8600000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.74417511292592</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.438x + -29079.413</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29079.41320062482</v>
       </c>
       <c r="Y3" t="n">
         <v>1.613124622069379e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2462.955700602321</v>
+        <v>293.5999999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000027034e-08</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>85.89763405516429</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.943x + -29117.097</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-29117.09723860739</v>
       </c>
       <c r="Y4" t="n">
         <v>4.866575263797109e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2391.660990471461</v>
+        <v>247.6500000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>86.22216617206217</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.144x + -31187.051</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31187.05100397402</v>
       </c>
       <c r="Y5" t="n">
         <v>6.252834411476645e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2350.065362473626</v>
+        <v>210.2399999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000008e-08</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.09348935868756</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.644x + -29621.553</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-29621.55290490708</v>
       </c>
       <c r="Y6" t="n">
         <v>1.230498828401794e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2314.022769149911</v>
+        <v>210.6399999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000214e-08</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>85.85877222536543</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.811x + -27432.601</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-27432.60076755711</v>
       </c>
       <c r="Y7" t="n">
         <v>8.075233288206583e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2278.892645829634</v>
+        <v>203.4799999999998</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000017374e-08</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.16905453599718</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.934x + -29333.320</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-29333.3200110806</v>
       </c>
       <c r="Y8" t="n">
         <v>2.655333856793304e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2243.353996478384</v>
+        <v>193.6699999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.03247901786544</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.418x + -27820.637</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-27820.63681942162</v>
       </c>
       <c r="Y9" t="n">
         <v>3.270528794341422e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2208.580200814447</v>
+        <v>194.2100000000003</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000022e-08</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.25867427784912</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.293x + -29172.183</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-29172.18338027941</v>
       </c>
       <c r="Y10" t="n">
         <v>1.592247695071056e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2175.345500587092</v>
+        <v>185.0600000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000348e-08</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.28112362820183</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.385x + -28947.258</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-28947.25785771579</v>
       </c>
       <c r="Y11" t="n">
         <v>1.279332546116162e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2144.019452580205</v>
+        <v>178.3900000000003</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000015e-08</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.15439600006185</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.796x + -29342.820</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-29342.81972963851</v>
       </c>
       <c r="Y2" t="n">
         <v>2.129234063954383e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2845.948042091551</v>
+        <v>346.3000000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000011e-08</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.43070239531707</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.513x + -29607.453</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29607.45348988348</v>
       </c>
       <c r="Y3" t="n">
         <v>1.320284713375369e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>2736.327374494666</v>
+        <v>243.1199999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001217e-08</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>85.68678733577332</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.259x + -30951.444</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30951.44415194967</v>
       </c>
       <c r="Y4" t="n">
         <v>1.500191835565047e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>2694.955799695584</v>
+        <v>217.0400000000004</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001151e-08</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>85.27414832266591</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.096x + -27757.302</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-27757.30246292592</v>
       </c>
       <c r="Y5" t="n">
         <v>1.607539098225247e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2662.460103949847</v>
+        <v>218.8099999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000002e-08</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>85.4115635437113</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.460x + -28307.209</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-28307.20923820126</v>
       </c>
       <c r="Y6" t="n">
         <v>9.87015092989737e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2629.468457631028</v>
+        <v>206.5999999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000023e-08</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>85.13057979456765</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.738x + -26260.520</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26260.51963328112</v>
       </c>
       <c r="Y7" t="n">
         <v>1.249466642569781e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2597.564665233623</v>
+        <v>209.75</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000504e-08</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>85.30570000872549</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.178x + -27001.913</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-27001.91315188662</v>
       </c>
       <c r="Y8" t="n">
         <v>2.515287388830445e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2567.732605236057</v>
+        <v>196.5999999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000019e-08</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>85.22706329430788</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.977x + -26231.710</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-26231.71028594182</v>
       </c>
       <c r="Y9" t="n">
         <v>1.014359159496607e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2537.481018250261</v>
+        <v>194.9700000000003</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>85.11867932411808</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.709x + -25330.308</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-25330.30802200493</v>
       </c>
       <c r="Y10" t="n">
         <v>1.11453348004922e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2508.488900648735</v>
+        <v>191.6599999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000142e-08</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>84.81339168368416</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 11.017x + -23485.125</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-23485.12470902395</v>
       </c>
       <c r="Y11" t="n">
         <v>1.147155854151793e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2479.048500598249</v>
+        <v>194.8800000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000017e-08</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>84.77473285432448</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.935x + -23048.369</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-23048.36933268379</v>
       </c>
       <c r="Y12" t="n">
         <v>1.515346933716058e-11</v>
       </c>
       <c r="Z12" t="n">
-        <v>2449.680458364413</v>
+        <v>183.02</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>84.05446588382652</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 9.602x + -19862.955</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19862.95549832066</v>
       </c>
       <c r="Y13" t="n">
         <v>6.229944194588911e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2419.819317598993</v>
+        <v>194.5999999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000196e-08</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>83.69720606072319</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 9.054x + -18460.854</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-18460.8542965073</v>
       </c>
       <c r="Y14" t="n">
         <v>7.89318947762486e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2391.138214515793</v>
+        <v>194.3899999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000123e-08</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>83.58707067747386</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 8.897x + -17913.343</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-17913.34268513276</v>
       </c>
       <c r="Y15" t="n">
         <v>6.788585878560492e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2362.419624778477</v>
+        <v>190.0599999999997</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000001e-08</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>83.4736610241447</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 8.741x + -17384.610</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-17384.61005729551</v>
       </c>
       <c r="Y16" t="n">
         <v>2.555286651214082e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2334.801746610437</v>
+        <v>181.0699999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000007969e-08</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>83.27502334215912</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 8.481x + -16647.101</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-16647.10093931793</v>
       </c>
       <c r="Y17" t="n">
         <v>1.797281210055078e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2307.80205912893</v>
+        <v>184.0400000000002</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000512e-08</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>82.39789008811356</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 7.493x + -14434.272</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-14434.2722710301</v>
       </c>
       <c r="Y18" t="n">
         <v>1.31020319319979e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>2280.930890948543</v>
+        <v>184.4899999999998</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>82.35609982469042</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 7.451x + -14192.040</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-14192.03971697599</v>
       </c>
       <c r="Y19" t="n">
         <v>5.333047516245059e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>2254.676723734933</v>
+        <v>179.6499999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000014787e-08</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>81.76283892476937</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 6.908x + -12937.893</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-12937.89300768527</v>
       </c>
       <c r="Y20" t="n">
         <v>5.460650300269002e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>2227.970377721017</v>
+        <v>175.76</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000839e-08</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>81.06612897739333</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 6.361x + -11706.661</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-11706.66105071141</v>
       </c>
       <c r="Y21" t="n">
         <v>214.0256189424472</v>
       </c>
       <c r="Z21" t="n">
-        <v>2207.389570706674</v>
+        <v>175.0300000000002</v>
       </c>
       <c r="AA21" t="n">
         <v>1.363638032946128e-08</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>79.43008667995478</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 5.359x + -9586.325</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-9586.32539212309</v>
       </c>
       <c r="Y22" t="n">
         <v>2.193834251485703e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>2174.872196386693</v>
+        <v>166.3599999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.00035781414279</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.145x + -21007.564</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21007.56366235087</v>
       </c>
       <c r="Y2" t="n">
         <v>7.041846685555586e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2855.65665514407</v>
+        <v>562.9000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000009e-08</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.8198252162511</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.682x + -29762.804</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29762.80413971239</v>
       </c>
       <c r="Y3" t="n">
         <v>3.158947464803032e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2460.840346272374</v>
+        <v>284.3699999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000072e-08</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>86.01260614144554</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.346x + -29847.436</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-29847.4360263286</v>
       </c>
       <c r="Y4" t="n">
         <v>6.56846089924788e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2373.551420344808</v>
+        <v>227.25</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000021011e-08</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>85.85115141078617</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.786x + -28068.067</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-28068.06724866177</v>
       </c>
       <c r="Y5" t="n">
         <v>3.334758227760508e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2333.537564832739</v>
+        <v>214.8199999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>85.93285633669966</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.064x + -28245.927</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-28245.92726466854</v>
       </c>
       <c r="Y6" t="n">
         <v>6.736481504495536e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2300.107205920785</v>
+        <v>203.5799999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>85.78326682271455</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.563x + -26819.058</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26819.05838577188</v>
       </c>
       <c r="Y7" t="n">
         <v>1.425876005003627e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2269.287311431293</v>
+        <v>202.1299999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003992e-08</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>85.83747668403021</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.740x + -26811.475</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-26811.47510177144</v>
       </c>
       <c r="Y8" t="n">
         <v>2.288055662162158e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2237.907758369383</v>
+        <v>197.52</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000146e-08</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>85.83781108931814</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.742x + -26448.811</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-26448.81097753151</v>
       </c>
       <c r="Y9" t="n">
         <v>1.374342983002057e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2206.807522206962</v>
+        <v>192.4299999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000029e-08</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>85.88364294295634</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.895x + -26404.514</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-26404.51397399669</v>
       </c>
       <c r="Y10" t="n">
         <v>1.40292540559079e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2176.098698950425</v>
+        <v>189.9399999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004222e-08</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>85.66028011763316</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 13.177x + -24635.613</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-24635.61255281352</v>
       </c>
       <c r="Y11" t="n">
         <v>2.742571044718832e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>2146.827841083477</v>
+        <v>190.5999999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000184e-08</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>84.97606556400319</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.375x + -28098.656</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-28098.65600786905</v>
       </c>
       <c r="Y2" t="n">
         <v>1.516309795665231e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2832.479758107666</v>
+        <v>330.77</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>85.65134975680714</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.150x + -30921.529</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30921.52940052495</v>
       </c>
       <c r="Y3" t="n">
         <v>1.558440525962691e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>2709.448860319832</v>
+        <v>222.4000000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001159e-08</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>85.64293230504576</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.125x + -30303.515</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30303.514849251</v>
       </c>
       <c r="Y4" t="n">
         <v>1.013495115745491e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2665.179508477985</v>
+        <v>216.7000000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>85.30943588204234</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.188x + -27674.417</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-27674.41706039802</v>
       </c>
       <c r="Y5" t="n">
         <v>8.912568205178581e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2631.110526981742</v>
+        <v>219.3599999999997</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000014e-08</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>85.48201254710068</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.655x + -28438.269</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-28438.26903061018</v>
       </c>
       <c r="Y6" t="n">
         <v>4.395283970990217e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2595.744206171674</v>
+        <v>208.7799999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000622e-08</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>85.15700123226335</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.802x + -26079.561</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26079.56078795576</v>
       </c>
       <c r="Y7" t="n">
         <v>2.097861802157766e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>2561.390606631469</v>
+        <v>213.8399999999997</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000005275e-08</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>85.08619277063494</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.632x + -25375.223</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-25375.22291093219</v>
       </c>
       <c r="Y8" t="n">
         <v>7.303595998404677e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>2529.255322404762</v>
+        <v>210.1499999999996</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000001e-08</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>84.9062979099409</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.219x + -24136.306</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-24136.30563903323</v>
       </c>
       <c r="Y9" t="n">
         <v>3.1400411281563e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2499.487328830749</v>
+        <v>211.2800000000002</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>84.87960821906553</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.160x + -23748.956</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-23748.95608733457</v>
       </c>
       <c r="Y10" t="n">
         <v>1.264077801157476e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2470.362966036245</v>
+        <v>204.3400000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000007143e-08</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>84.94434092385205</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 11.304x + -23811.521</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-23811.52145006346</v>
       </c>
       <c r="Y11" t="n">
         <v>4.736970107731786e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2442.704039156864</v>
+        <v>199.0300000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000017284e-08</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>84.55642893097483</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.494x + -21778.605</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-21778.60456972539</v>
       </c>
       <c r="Y12" t="n">
         <v>7.703072928447077e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>2415.773380742343</v>
+        <v>202.2999999999997</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000004286e-08</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>84.50021061082096</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 10.386x + -21320.763</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-21320.76304847044</v>
       </c>
       <c r="Y13" t="n">
         <v>5.796389850219528e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2389.21634967006</v>
+        <v>199.0300000000002</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000065e-08</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>84.26300311926651</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 9.954x + -20159.528</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-20159.52844389887</v>
       </c>
       <c r="Y14" t="n">
         <v>2.824930918373567e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>2362.603687215268</v>
+        <v>202.6000000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000197e-08</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>84.13873340762382</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 9.741x + -19518.801</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-19518.80075947692</v>
       </c>
       <c r="Y15" t="n">
         <v>1.473080802826887e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2336.332762416729</v>
+        <v>186.8200000000002</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000004113e-08</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>84.04451907982248</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 9.586x + -18992.521</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-18992.52057695977</v>
       </c>
       <c r="Y16" t="n">
         <v>2.667522414754383e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2310.940986393167</v>
+        <v>175.9400000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000308e-08</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>83.513309699044</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 8.795x + -17149.488</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-17149.4884667881</v>
       </c>
       <c r="Y17" t="n">
         <v>6.002937517158759e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>2285.377112737908</v>
+        <v>193.49</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000010564e-08</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>83.38946512490763</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 8.629x + -16631.399</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-16631.39926971079</v>
       </c>
       <c r="Y18" t="n">
         <v>5.75017130529854e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>2259.916081722555</v>
+        <v>183.47</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000010925e-08</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>82.83076238342716</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 7.950x + -15087.003</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-15087.00295811185</v>
       </c>
       <c r="Y19" t="n">
         <v>3.186025180523736e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2234.719984376756</v>
+        <v>183.7199999999998</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000713e-08</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>82.57466012938002</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 7.673x + -14364.122</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-14364.12233441492</v>
       </c>
       <c r="Y20" t="n">
         <v>3.112743634453489e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2209.293118100206</v>
+        <v>170.0200000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000094e-08</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>82.45793970557759</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 7.553x + -13962.155</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-13962.15478543122</v>
       </c>
       <c r="Y21" t="n">
         <v>6.77775154945498e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>2183.771627758495</v>
+        <v>168.3700000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000501e-08</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>81.27339245855396</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 6.515x + -11790.909</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-11790.90891477915</v>
       </c>
       <c r="Y22" t="n">
         <v>3.409358536093444e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2157.791352734257</v>
+        <v>171.4799999999998</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000728e-08</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>83.55552605910758</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.853x + -21350.109</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-21350.10912091603</v>
       </c>
       <c r="Y2" t="n">
         <v>8.288473459606596e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2640.53776847434</v>
+        <v>518.3900000000003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000024413e-08</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.91443960564308</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.000x + -29479.661</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29479.66127775418</v>
       </c>
       <c r="Y3" t="n">
         <v>3.054871269118177e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>2349.503403421527</v>
+        <v>275.29</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000012586e-08</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>85.76694640305577</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.511x + -27298.556</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-27298.55563783196</v>
       </c>
       <c r="Y4" t="n">
         <v>2.317944178429333e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2279.715259742693</v>
+        <v>236.45</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000005e-08</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>85.81296358917007</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.660x + -27115.736</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-27115.73589711453</v>
       </c>
       <c r="Y5" t="n">
         <v>7.899469626949051e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2242.36267692865</v>
+        <v>207.6599999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.07823582328332</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.587x + -28667.123</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-28667.12261074701</v>
       </c>
       <c r="Y6" t="n">
         <v>186.1080253299602</v>
       </c>
       <c r="Z6" t="n">
-        <v>2211.862347563584</v>
+        <v>193.0399999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.382244200619495e-08</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>85.90297124511967</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 13.961x + -26993.331</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-26993.33078943432</v>
       </c>
       <c r="Y7" t="n">
         <v>3.675000967276618e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2180.94831184644</v>
+        <v>194.6200000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000015584e-08</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>85.85662652813693</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 13.804x + -26286.683</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-26286.68335206001</v>
       </c>
       <c r="Y8" t="n">
         <v>4.101096256983958e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2148.73215383579</v>
+        <v>191.2499999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000427e-08</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>85.86279157538219</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.825x + -25941.163</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25941.16270923146</v>
       </c>
       <c r="Y9" t="n">
         <v>4.252752228430736e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2115.756282430544</v>
+        <v>185.54</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>85.65624277715484</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.165x + -24281.903</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-24281.90336628448</v>
       </c>
       <c r="Y10" t="n">
         <v>1.290137604425771e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2084.486497516774</v>
+        <v>188.49</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>85.43695396758204</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.530x + -22725.384</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-22725.38444258767</v>
       </c>
       <c r="Y11" t="n">
         <v>1.546089694979385e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2054.950347124875</v>
+        <v>188.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000053009e-08</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.63524863918384</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.102x + -32128.849</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-32128.84861043092</v>
       </c>
       <c r="Y2" t="n">
         <v>1.018497924899276e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2766.750533962472</v>
+        <v>274.1100000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000032e-08</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>85.35730990994833</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.314x + -28740.528</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-28740.52815406123</v>
       </c>
       <c r="Y3" t="n">
         <v>1.482444433917909e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2667.402029510698</v>
+        <v>224.3500000000004</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>85.35317263523869</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.303x + -28195.257</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-28195.25688813455</v>
       </c>
       <c r="Y4" t="n">
         <v>2.750350788854377e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>2621.92439174166</v>
+        <v>212.5600000000004</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>85.09924036513074</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.663x + -26301.867</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-26301.86661403129</v>
       </c>
       <c r="Y5" t="n">
         <v>9.947837157897419e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2585.253226771898</v>
+        <v>208.71</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>84.97962710126282</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.383x + -25313.033</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-25313.03262601143</v>
       </c>
       <c r="Y6" t="n">
         <v>6.953554496488012e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2551.158655032718</v>
+        <v>206.0600000000004</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001853e-08</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>84.75671805038773</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.897x + -23891.638</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-23891.63781397516</v>
       </c>
       <c r="Y7" t="n">
         <v>1.166065075582911e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2519.883370992912</v>
+        <v>203.4400000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000656e-08</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>84.64720096815343</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.673x + -23111.431</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-23111.43067449572</v>
       </c>
       <c r="Y8" t="n">
         <v>1.009672237852387e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2490.440800320759</v>
+        <v>198.4900000000002</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001725e-08</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>84.35774023042264</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.122x + -21624.099</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-21624.09864836832</v>
       </c>
       <c r="Y9" t="n">
         <v>1.021825600564301e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2461.192357789637</v>
+        <v>191.8299999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001761e-08</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>83.98921141455334</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.497x + -19985.387</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19985.38718802719</v>
       </c>
       <c r="Y10" t="n">
         <v>6.280938585877643e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2431.737844928728</v>
+        <v>189.2600000000002</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000012e-08</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>83.69762411592801</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 9.054x + -18778.431</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18778.43135635072</v>
       </c>
       <c r="Y11" t="n">
         <v>3.971303253004576e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>2402.151911987078</v>
+        <v>188.23</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>83.55078183886248</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 8.847x + -18100.473</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-18100.47329219053</v>
       </c>
       <c r="Y12" t="n">
         <v>3.92107921365423e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2371.647713132661</v>
+        <v>192.2700000000004</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000153e-08</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>82.96560479702194</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 8.104x + -16302.093</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-16302.09312969965</v>
       </c>
       <c r="Y13" t="n">
         <v>5.593582725294761e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2342.020353029596</v>
+        <v>190.1199999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000001e-08</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>82.55800099243558</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 7.656x + -15156.612</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-15156.61205430785</v>
       </c>
       <c r="Y14" t="n">
         <v>5.326223305162802e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2311.659965095116</v>
+        <v>199.6899999999998</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000009e-08</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>81.75868938459175</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 6.904x + -13392.695</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-13392.69519369811</v>
       </c>
       <c r="Y15" t="n">
         <v>5.345693589351309e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>2281.619374699685</v>
+        <v>176.6999999999998</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000001e-08</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>80.34619777210902</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 5.879x + -11112.436</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11112.43555011945</v>
       </c>
       <c r="Y16" t="n">
         <v>9.047915646325895e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>2252.811461591035</v>
+        <v>172.6300000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000587e-08</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>81.52007563877578</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 6.707x + -12675.786</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12675.7855336765</v>
       </c>
       <c r="Y17" t="n">
         <v>4.918555176209131e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2223.671646583151</v>
+        <v>185.4099999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000016e-08</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>79.82663183593523</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 5.573x + -10239.691</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10239.6909478978</v>
       </c>
       <c r="Y18" t="n">
         <v>5.034582895725092e-12</v>
       </c>
       <c r="Z18" t="n">
-        <v>2195.094847795729</v>
+        <v>173.75</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000055e-08</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>76.98816776782273</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 4.327x + -7640.346</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7640.345798778478</v>
       </c>
       <c r="Y19" t="n">
         <v>2.432931517641712e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2165.992430881933</v>
+        <v>170.46</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000026e-08</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>74.31179345564641</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 3.560x + -6039.215</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-6039.21534301539</v>
       </c>
       <c r="Y20" t="n">
         <v>8.660458373077296e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>2137.132715118158</v>
+        <v>168.4300000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000002782e-08</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>72.70441040408457</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 3.212x + -5310.017</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-5310.017213698121</v>
       </c>
       <c r="Y21" t="n">
         <v>1.92893508239642e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>2108.33894790977</v>
+        <v>171.9300000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.0000000000003e-08</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>60.72049696681752</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 1.783x + -2490.739</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-2490.739084547793</v>
       </c>
       <c r="Y22" t="n">
         <v>1.570472746967216e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>2081.046908599812</v>
+        <v>161.1700000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000047997e-08</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>83.81095713910436</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.222x + -18277.826</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-18277.82618051678</v>
       </c>
       <c r="Y2" t="n">
         <v>162.6737353687826</v>
       </c>
       <c r="Z2" t="n">
-        <v>2162.228436743672</v>
+        <v>491.5599999999997</v>
       </c>
       <c r="AA2" t="n">
         <v>1.521377037002092e-08</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.13256016928565</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.792x + -25629.094</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-25629.09437306778</v>
       </c>
       <c r="Y3" t="n">
         <v>1.323351647208594e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1916.660323873801</v>
+        <v>246.52</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.43465412858183</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.049x + -26886.779</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-26886.77868228229</v>
       </c>
       <c r="Y4" t="n">
         <v>3.793287299827609e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>1860.144351889452</v>
+        <v>190.22</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>86.25734388198219</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.287x + -25053.523</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-25053.52312847711</v>
       </c>
       <c r="Y5" t="n">
         <v>5.202144731797539e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1826.396393760933</v>
+        <v>170.6099999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000031e-08</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.67647062046937</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.220x + -27927.971</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-27927.97081087231</v>
       </c>
       <c r="Y6" t="n">
         <v>1.696445211737782e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1794.850558248901</v>
+        <v>155.0799999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000024e-08</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>86.27229855641723</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.349x + -24313.640</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-24313.63993911394</v>
       </c>
       <c r="Y7" t="n">
         <v>5.459990444312311e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1762.967762768062</v>
+        <v>160.76</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>86.06161589753195</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.525x + -22522.850</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-22522.8502908081</v>
       </c>
       <c r="Y8" t="n">
         <v>3.839332757947256e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1731.525000378381</v>
+        <v>163.45</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000668e-08</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>86.21354702955047</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.110x + -23105.850</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-23105.8503023518</v>
       </c>
       <c r="Y9" t="n">
         <v>6.278126041582441e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>1700.93793595741</v>
+        <v>152.55</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>86.27818843129664</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.373x + -23136.454</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-23136.45351873905</v>
       </c>
       <c r="Y10" t="n">
         <v>3.727421379567755e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>1671.997039690264</v>
+        <v>146.78</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>86.0168749706659</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.361x + -21211.210</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-21211.2100944628</v>
       </c>
       <c r="Y11" t="n">
         <v>1.501400957957264e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>1645.259342180763</v>
+        <v>148.0800000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000010075e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>85.46502329812238</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.608x + -26512.619</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.6078004481823</v>
       </c>
       <c r="X2" t="n">
         <v>-26512.61895166363</v>
@@ -600,7 +598,7 @@
         <v>7.415310947677803e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>301.1800000000003</v>
+        <v>2410.448049943559</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000015e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.01872816656795</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.368x + -29617.468</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.36815610460482</v>
       </c>
       <c r="X3" t="n">
         <v>-29617.4678162674</v>
@@ -652,7 +648,7 @@
         <v>6.011366547673892e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>219.55</v>
+        <v>2359.317609741626</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000215e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.01905782346823</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.369x + -29107.971</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.36934975221151</v>
       </c>
       <c r="X4" t="n">
         <v>-29107.97135255189</v>
@@ -704,7 +698,7 @@
         <v>2.104590956173844e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>195.04</v>
+        <v>2320.892027456387</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000011e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.12382935935841</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.759x + -29473.007</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.75898457011279</v>
       </c>
       <c r="X5" t="n">
         <v>-29473.00660329694</v>
@@ -756,7 +748,7 @@
         <v>3.913578887301948e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>189.4500000000003</v>
+        <v>2285.819968891027</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000264e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>85.91615261099008</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.006x + -27455.432</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.00608632591148</v>
       </c>
       <c r="X6" t="n">
         <v>-27455.43201969614</v>
@@ -808,7 +798,7 @@
         <v>4.633778004024203e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>189.3399999999999</v>
+        <v>2250.227692224049</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000649e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>85.90613361084375</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.972x + -26980.663</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.97169244112645</v>
       </c>
       <c r="X7" t="n">
         <v>-26980.66251654135</v>
@@ -860,7 +848,7 @@
         <v>5.302073442772051e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>184.96</v>
+        <v>2215.639602243329</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001893e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>85.72401982761939</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.375x + -25375.119</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.37456341053684</v>
       </c>
       <c r="X8" t="n">
         <v>-25375.11933162333</v>
@@ -912,7 +898,7 @@
         <v>4.84599431062659e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>185.8100000000002</v>
+        <v>2181.660894811766</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000093e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>85.98038142467519</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.231x + -26702.595</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.23064104904719</v>
       </c>
       <c r="X9" t="n">
         <v>-26702.59540322645</v>
@@ -964,7 +948,7 @@
         <v>1.606193303780935e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>175.1299999999999</v>
+        <v>2149.985626840088</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000253e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>85.86205760765881</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.822x + -25554.504</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.82236009498581</v>
       </c>
       <c r="X10" t="n">
         <v>-25554.5036609288</v>
@@ -1016,7 +998,7 @@
         <v>2.715284651378623e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>172.5699999999999</v>
+        <v>2119.966405870303</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000007374e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>85.78245531365859</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.561x + -24703.076</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.5605575802007</v>
       </c>
       <c r="X11" t="n">
         <v>-24703.07649563891</v>
@@ -1068,7 +1048,7 @@
         <v>5.079048882999982e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>172.5999999999999</v>
+        <v>2091.506950994974</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000531e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.50598793787236</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.723x + -30660.022</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.72320458846078</v>
       </c>
       <c r="X2" t="n">
         <v>-30660.02153502501</v>
@@ -1266,7 +1244,7 @@
         <v>2.075396332685376e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>230.75</v>
+        <v>2757.57009933029</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000562e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>85.37491727899916</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.361x + -28099.156</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.36113574657744</v>
       </c>
       <c r="X3" t="n">
         <v>-28099.15557419353</v>
@@ -1318,7 +1294,7 @@
         <v>1.180535016618823e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>212.8600000000001</v>
+        <v>2628.895283461112</v>
       </c>
       <c r="AA3" t="n">
         <v>1e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>85.30000873053365</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.163x + -27112.953</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.1632583156551</v>
       </c>
       <c r="X4" t="n">
         <v>-27112.95277324877</v>
@@ -1370,7 +1344,7 @@
         <v>1.034578536778927e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>207.6300000000001</v>
+        <v>2583.028355356804</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000002802e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>85.03164750472718</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.503x + -25225.262</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.50322944524455</v>
       </c>
       <c r="X5" t="n">
         <v>-25225.26241618456</v>
@@ -1422,7 +1394,7 @@
         <v>1.736386840969188e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>211.9200000000001</v>
+        <v>2549.26393814946</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001974e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>84.66596044994454</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.710x + -23117.854</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.71048618201072</v>
       </c>
       <c r="X6" t="n">
         <v>-23117.85400731676</v>
@@ -1474,7 +1444,7 @@
         <v>1.734692249110454e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>214.9300000000003</v>
+        <v>2517.318306344748</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>85.01050864696612</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.454x + -24527.172</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.45424830216113</v>
       </c>
       <c r="X7" t="n">
         <v>-24527.17234841071</v>
@@ -1526,7 +1494,7 @@
         <v>2.441533647954122e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>194.1900000000001</v>
+        <v>2485.543471191366</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>84.67699592376789</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.733x + -22627.340</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.73281948843169</v>
       </c>
       <c r="X8" t="n">
         <v>-22627.33967337245</v>
@@ -1578,7 +1544,7 @@
         <v>7.033304018910433e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>193.1000000000004</v>
+        <v>2453.951101126005</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>84.29826115100296</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.016x + -20780.160</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.01563234301469</v>
       </c>
       <c r="X9" t="n">
         <v>-20780.16045926497</v>
@@ -1630,7 +1594,7 @@
         <v>3.948437754477155e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>204.8800000000001</v>
+        <v>2424.035502175891</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000309e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>84.2712164075494</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.968x + -20449.782</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.968035663900809</v>
       </c>
       <c r="X10" t="n">
         <v>-20449.78197501574</v>
@@ -1682,7 +1644,7 @@
         <v>3.254071109854306e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>195.1700000000001</v>
+        <v>2395.761097073741</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>83.75832372707492</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.143x + -18462.857</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.143208650833428</v>
       </c>
       <c r="X11" t="n">
         <v>-18462.85703754847</v>
@@ -1734,7 +1694,7 @@
         <v>3.263430458204318e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>198.3400000000001</v>
+        <v>2368.05908293269</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>83.78996971321338</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 9.190x + -18355.648</t>
-        </is>
+      <c r="W12" t="n">
+        <v>9.190171697026022</v>
       </c>
       <c r="X12" t="n">
         <v>-18355.64765139138</v>
@@ -1786,7 +1744,7 @@
         <v>2.464301324947811e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>196.7599999999998</v>
+        <v>2340.665388963708</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000083176e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>83.45126095644565</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 8.711x + -17156.135</t>
-        </is>
+      <c r="W13" t="n">
+        <v>8.710999328556046</v>
       </c>
       <c r="X13" t="n">
         <v>-17156.13490481778</v>
@@ -1838,7 +1794,7 @@
         <v>6.631307393981735e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>187.3900000000001</v>
+        <v>2313.782422428646</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>83.17518335639733</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 8.355x + -16227.324</t>
-        </is>
+      <c r="W14" t="n">
+        <v>8.355468768286636</v>
       </c>
       <c r="X14" t="n">
         <v>-16227.32390932036</v>
@@ -1890,7 +1844,7 @@
         <v>2.706458700410186e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>183.9900000000002</v>
+        <v>2286.936405802662</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>82.28085262154526</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 7.378x + -14059.649</t>
-        </is>
+      <c r="W15" t="n">
+        <v>7.377590253911315</v>
       </c>
       <c r="X15" t="n">
         <v>-14059.64894322642</v>
@@ -1942,7 +1894,7 @@
         <v>5.203271988021492e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>181.8099999999999</v>
+        <v>2260.62424563863</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000003576e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>81.89092025946779</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 7.018x + -13177.044</t>
-        </is>
+      <c r="W16" t="n">
+        <v>7.018392932429194</v>
       </c>
       <c r="X16" t="n">
         <v>-13177.04396881474</v>
@@ -1994,7 +1944,7 @@
         <v>9.890564578953269e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>178.8799999999999</v>
+        <v>2234.884909838563</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>81.68937925222713</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 6.846x + -12692.447</t>
-        </is>
+      <c r="W17" t="n">
+        <v>6.845866801445387</v>
       </c>
       <c r="X17" t="n">
         <v>-12692.44696356226</v>
@@ -2046,7 +1994,7 @@
         <v>212.4812723188523</v>
       </c>
       <c r="Z17" t="n">
-        <v>179.4399999999998</v>
+        <v>2223.75627310775</v>
       </c>
       <c r="AA17" t="n">
         <v>1.380833949190603e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>80.74281756918141</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 6.135x + -11148.922</t>
-        </is>
+      <c r="W18" t="n">
+        <v>6.135382375984592</v>
       </c>
       <c r="X18" t="n">
         <v>-11148.92228587478</v>
@@ -2098,7 +2044,7 @@
         <v>206.861668179744</v>
       </c>
       <c r="Z18" t="n">
-        <v>180.1099999999999</v>
+        <v>2197.477832755963</v>
       </c>
       <c r="AA18" t="n">
         <v>1.40792039562032e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>80.35663735634036</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.885x + -10532.813</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.885264029021153</v>
       </c>
       <c r="X19" t="n">
         <v>-10532.81262975529</v>
@@ -2150,7 +2094,7 @@
         <v>4.47998912098377e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>174.76</v>
+        <v>2156.5440610064</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000101e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>79.50211583326845</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 5.397x + -9469.765</t>
-        </is>
+      <c r="W20" t="n">
+        <v>5.39662936502856</v>
       </c>
       <c r="X20" t="n">
         <v>-9469.764652776803</v>
@@ -2202,7 +2144,7 @@
         <v>2.072714896296982e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>172.0899999999999</v>
+        <v>2130.146285283991</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000007e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>75.13928367587035</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 3.769x + -6233.095</t>
-        </is>
+      <c r="W21" t="n">
+        <v>3.768672979039274</v>
       </c>
       <c r="X21" t="n">
         <v>-6233.095012111938</v>
@@ -2254,7 +2194,7 @@
         <v>5.966431116877329e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>164.22</v>
+        <v>2103.727843958342</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000169e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>76.35452891099136</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 4.119x + -6862.052</t>
-        </is>
+      <c r="W22" t="n">
+        <v>4.11919820013659</v>
       </c>
       <c r="X22" t="n">
         <v>-6862.051675706942</v>
@@ -2306,7 +2244,7 @@
         <v>2.614793725905983e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>175.1400000000001</v>
+        <v>2078.340268613085</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000005e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>85.47740357708268</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.642x + -32182.283</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.64245775396967</v>
       </c>
       <c r="X2" t="n">
         <v>-32182.28269469809</v>
@@ -2504,7 +2440,7 @@
         <v>3.59442307260886e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>296.21</v>
+        <v>2915.954589926854</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000087e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.40729846195727</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.449x + -30102.179</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.44866727823189</v>
       </c>
       <c r="X3" t="n">
         <v>-30102.17944132951</v>
@@ -2556,7 +2490,7 @@
         <v>1.117241225930757e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>236.8599999999997</v>
+        <v>2809.082698967638</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000192e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>85.6031663285822</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.006x + -31151.404</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.00555575634132</v>
       </c>
       <c r="X4" t="n">
         <v>-31151.40379032491</v>
@@ -2608,7 +2540,7 @@
         <v>2.825737732110178e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>218.29</v>
+        <v>2779.103494459513</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000637e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>85.33117075431733</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.245x + -28949.677</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.24480590383915</v>
       </c>
       <c r="X5" t="n">
         <v>-28949.67655070433</v>
@@ -2660,7 +2590,7 @@
         <v>1.137282678068201e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>224.3400000000001</v>
+        <v>2752.227983503276</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000001e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>85.41581355186332</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.472x + -29241.180</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.4718898332636</v>
       </c>
       <c r="X6" t="n">
         <v>-29241.17998515358</v>
@@ -2712,7 +2640,7 @@
         <v>1.034390778127763e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>208.8099999999999</v>
+        <v>2723.276059701413</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>85.17673575532864</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.851x + -27379.587</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.85097246861213</v>
       </c>
       <c r="X7" t="n">
         <v>-27379.5874050473</v>
@@ -2764,7 +2690,7 @@
         <v>1.519918255122773e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>211.9499999999998</v>
+        <v>2690.199763488245</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000006e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>85.07080889104667</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.595x + -26427.706</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.59507811208227</v>
       </c>
       <c r="X8" t="n">
         <v>-26427.70560616207</v>
@@ -2816,7 +2740,7 @@
         <v>4.342906300109985e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>208.0099999999998</v>
+        <v>2655.487400575091</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000878e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>84.93251314701644</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.277x + -25369.223</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.27705041499087</v>
       </c>
       <c r="X9" t="n">
         <v>-25369.22255346926</v>
@@ -2868,7 +2790,7 @@
         <v>2.939495515668526e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>204.6400000000003</v>
+        <v>2623.329471766109</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000696e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>84.7572836689485</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.898x + -24202.139</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.8981259096984</v>
       </c>
       <c r="X10" t="n">
         <v>-24202.13855168521</v>
@@ -2920,7 +2840,7 @@
         <v>8.706620553159562e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>202.3800000000001</v>
+        <v>2592.348915597973</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000002331e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>84.48698420787788</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.361x + -22687.219</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.36072652966269</v>
       </c>
       <c r="X11" t="n">
         <v>-22687.21857963646</v>
@@ -2972,7 +2890,7 @@
         <v>2.127431609741145e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>206.9699999999998</v>
+        <v>2563.02284458603</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000386e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>84.05746256025441</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 9.607x + -20732.166</t>
-        </is>
+      <c r="W12" t="n">
+        <v>9.607038328102856</v>
       </c>
       <c r="X12" t="n">
         <v>-20732.16588551441</v>
@@ -3024,7 +2940,7 @@
         <v>1.859345571410595e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>202.0100000000002</v>
+        <v>2534.730011262545</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000299e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>84.19017320735685</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.828x + -21023.296</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.828050558208488</v>
       </c>
       <c r="X13" t="n">
         <v>-21023.29645173243</v>
@@ -3076,7 +2990,7 @@
         <v>4.239488607329279e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>193.7199999999998</v>
+        <v>2507.234636243908</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000076e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>84.0597828895913</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 9.611x + -20322.202</t>
-        </is>
+      <c r="W14" t="n">
+        <v>9.610818009825834</v>
       </c>
       <c r="X14" t="n">
         <v>-20322.20238838419</v>
@@ -3128,7 +3040,7 @@
         <v>9.359231651318668e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>189.77</v>
+        <v>2480.629410918885</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>83.8901954968315</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 9.342x + -19518.573</t>
-        </is>
+      <c r="W15" t="n">
+        <v>9.342105661777383</v>
       </c>
       <c r="X15" t="n">
         <v>-19518.57299755024</v>
@@ -3180,7 +3090,7 @@
         <v>4.973967348233778e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>188.4900000000002</v>
+        <v>2454.630797555196</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000107e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>83.74941351313974</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.130x + -18859.623</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.130071237065776</v>
       </c>
       <c r="X16" t="n">
         <v>-18859.62323868267</v>
@@ -3232,7 +3140,7 @@
         <v>3.45003817486749e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>184.0999999999999</v>
+        <v>2428.185404745177</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000084e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>83.06412942258612</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 8.220x + -16703.090</t>
-        </is>
+      <c r="W17" t="n">
+        <v>8.220400592297104</v>
       </c>
       <c r="X17" t="n">
         <v>-16703.09046365776</v>
@@ -3284,7 +3190,7 @@
         <v>5.970517935624754e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>181.3400000000001</v>
+        <v>2401.983530257716</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000009e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>82.7794422333864</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.893x + -15828.722</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.893038477879482</v>
       </c>
       <c r="X18" t="n">
         <v>-15828.72167675995</v>
@@ -3336,7 +3240,7 @@
         <v>9.627140714989261e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>183.9200000000001</v>
+        <v>2375.280445590422</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000782e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>82.04578403029792</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.157x + -14100.434</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.156861038940522</v>
       </c>
       <c r="X19" t="n">
         <v>-14100.43427184204</v>
@@ -3388,7 +3290,7 @@
         <v>5.29289101531848e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>182.1400000000001</v>
+        <v>2347.508273255232</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>81.99373261841544</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.110x + -13842.076</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.109726657969135</v>
       </c>
       <c r="X20" t="n">
         <v>-13842.07640576425</v>
@@ -3440,7 +3340,7 @@
         <v>7.075119883901549e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>178.3299999999999</v>
+        <v>2320.071994721753</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000034e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>81.49581742349871</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 6.688x + -12814.541</t>
-        </is>
+      <c r="W21" t="n">
+        <v>6.687816557150684</v>
       </c>
       <c r="X21" t="n">
         <v>-12814.5406608731</v>
@@ -3492,7 +3390,7 @@
         <v>3.777177309290668e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>177.4199999999998</v>
+        <v>2292.691756936614</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>79.35258673424356</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 5.319x + -9880.900</t>
-        </is>
+      <c r="W22" t="n">
+        <v>5.319105195019072</v>
       </c>
       <c r="X22" t="n">
         <v>-9880.899672481139</v>
@@ -3544,7 +3440,7 @@
         <v>4.319115630141283e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>174.4800000000002</v>
+        <v>2264.958903157273</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000029683e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.03803453681488</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.576x + -23184.556</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.575506236164767</v>
       </c>
       <c r="X2" t="n">
         <v>-23184.55585740781</v>
@@ -3742,7 +3636,7 @@
         <v>3.175791473510778e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>491.8600000000001</v>
+        <v>2713.895048948965</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.74417511292592</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.438x + -29079.413</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.43813964239288</v>
       </c>
       <c r="X3" t="n">
         <v>-29079.41320062482</v>
@@ -3794,7 +3686,7 @@
         <v>1.613124622069379e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>293.5999999999999</v>
+        <v>2462.955700602321</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000027034e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.89763405516429</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.943x + -29117.097</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.94264609402739</v>
       </c>
       <c r="X4" t="n">
         <v>-29117.09723860739</v>
@@ -3846,7 +3736,7 @@
         <v>4.866575263797109e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>247.6500000000001</v>
+        <v>2391.660990471461</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>86.22216617206217</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.144x + -31187.051</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.14431993250762</v>
       </c>
       <c r="X5" t="n">
         <v>-31187.05100397402</v>
@@ -3898,7 +3786,7 @@
         <v>6.252834411476645e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>210.2399999999998</v>
+        <v>2350.065362473626</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000008e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.09348935868756</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.644x + -29621.553</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.64400672490536</v>
       </c>
       <c r="X6" t="n">
         <v>-29621.55290490708</v>
@@ -3950,7 +3836,7 @@
         <v>1.230498828401794e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>210.6399999999999</v>
+        <v>2314.022769149911</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000214e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>85.85877222536543</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.811x + -27432.601</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.81135608980062</v>
       </c>
       <c r="X7" t="n">
         <v>-27432.60076755711</v>
@@ -4002,7 +3886,7 @@
         <v>8.075233288206583e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>203.4799999999998</v>
+        <v>2278.892645829634</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000017374e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.16905453599718</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.934x + -29333.320</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.93374736148099</v>
       </c>
       <c r="X8" t="n">
         <v>-29333.3200110806</v>
@@ -4054,7 +3936,7 @@
         <v>2.655333856793304e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>193.6699999999998</v>
+        <v>2243.353996478384</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.03247901786544</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.418x + -27820.637</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.4181144247495</v>
       </c>
       <c r="X9" t="n">
         <v>-27820.63681942162</v>
@@ -4106,7 +3986,7 @@
         <v>3.270528794341422e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>194.2100000000003</v>
+        <v>2208.580200814447</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000022e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.25867427784912</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.293x + -29172.183</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.29252632478277</v>
       </c>
       <c r="X10" t="n">
         <v>-29172.18338027941</v>
@@ -4158,7 +4036,7 @@
         <v>1.592247695071056e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>185.0600000000002</v>
+        <v>2175.345500587092</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000348e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.28112362820183</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.385x + -28947.258</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.38510325869044</v>
       </c>
       <c r="X11" t="n">
         <v>-28947.25785771579</v>
@@ -4210,7 +4086,7 @@
         <v>1.279332546116162e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>178.3900000000003</v>
+        <v>2144.019452580205</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000015e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.15439600006185</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.796x + -29342.820</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.79607618392666</v>
       </c>
       <c r="X2" t="n">
         <v>-29342.81972963851</v>
@@ -4408,7 +4282,7 @@
         <v>2.129234063954383e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>346.3000000000002</v>
+        <v>2845.948042091551</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000011e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.43070239531707</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.513x + -29607.453</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.51270257503911</v>
       </c>
       <c r="X3" t="n">
         <v>-29607.45348988348</v>
@@ -4460,7 +4332,7 @@
         <v>1.320284713375369e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>243.1199999999999</v>
+        <v>2736.327374494666</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001217e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>85.68678733577332</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.259x + -30951.444</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.2586799007924</v>
       </c>
       <c r="X4" t="n">
         <v>-30951.44415194967</v>
@@ -4512,7 +4382,7 @@
         <v>1.500191835565047e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>217.0400000000004</v>
+        <v>2694.955799695584</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001151e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>85.27414832266591</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.096x + -27757.302</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.09639920983481</v>
       </c>
       <c r="X5" t="n">
         <v>-27757.30246292592</v>
@@ -4564,7 +4432,7 @@
         <v>1.607539098225247e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>218.8099999999999</v>
+        <v>2662.460103949847</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000002e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>85.4115635437113</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.460x + -28307.209</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.46028835942666</v>
       </c>
       <c r="X6" t="n">
         <v>-28307.20923820126</v>
@@ -4616,7 +4482,7 @@
         <v>9.87015092989737e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>206.5999999999999</v>
+        <v>2629.468457631028</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000023e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>85.13057979456765</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.738x + -26260.520</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.73810518550821</v>
       </c>
       <c r="X7" t="n">
         <v>-26260.51963328112</v>
@@ -4668,7 +4532,7 @@
         <v>1.249466642569781e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>209.75</v>
+        <v>2597.564665233623</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000504e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>85.30570000872549</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.178x + -27001.913</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.17807113455072</v>
       </c>
       <c r="X8" t="n">
         <v>-27001.91315188662</v>
@@ -4720,7 +4582,7 @@
         <v>2.515287388830445e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>196.5999999999999</v>
+        <v>2567.732605236057</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000019e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>85.22706329430788</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.977x + -26231.710</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.97652255515362</v>
       </c>
       <c r="X9" t="n">
         <v>-26231.71028594182</v>
@@ -4772,7 +4632,7 @@
         <v>1.014359159496607e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>194.9700000000003</v>
+        <v>2537.481018250261</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>85.11867932411808</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.709x + -25330.308</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.70934970729109</v>
       </c>
       <c r="X10" t="n">
         <v>-25330.30802200493</v>
@@ -4824,7 +4682,7 @@
         <v>1.11453348004922e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>191.6599999999999</v>
+        <v>2508.488900648735</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000142e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>84.81339168368416</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.017x + -23485.125</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.0166774388787</v>
       </c>
       <c r="X11" t="n">
         <v>-23485.12470902395</v>
@@ -4876,7 +4732,7 @@
         <v>1.147155854151793e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>194.8800000000001</v>
+        <v>2479.048500598249</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000017e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>84.77473285432448</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.935x + -23048.369</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.93472255779627</v>
       </c>
       <c r="X12" t="n">
         <v>-23048.36933268379</v>
@@ -4928,7 +4782,7 @@
         <v>1.515346933716058e-11</v>
       </c>
       <c r="Z12" t="n">
-        <v>183.02</v>
+        <v>2449.680458364413</v>
       </c>
       <c r="AA12" t="n">
         <v>1e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>84.05446588382652</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 9.602x + -19862.955</t>
-        </is>
+      <c r="W13" t="n">
+        <v>9.602161265969851</v>
       </c>
       <c r="X13" t="n">
         <v>-19862.95549832066</v>
@@ -4980,7 +4832,7 @@
         <v>6.229944194588911e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>194.5999999999999</v>
+        <v>2419.819317598993</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000196e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>83.69720606072319</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 9.054x + -18460.854</t>
-        </is>
+      <c r="W14" t="n">
+        <v>9.053838899109923</v>
       </c>
       <c r="X14" t="n">
         <v>-18460.8542965073</v>
@@ -5032,7 +4882,7 @@
         <v>7.89318947762486e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>194.3899999999999</v>
+        <v>2391.138214515793</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000123e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>83.58707067747386</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 8.897x + -17913.343</t>
-        </is>
+      <c r="W15" t="n">
+        <v>8.897076074909853</v>
       </c>
       <c r="X15" t="n">
         <v>-17913.34268513276</v>
@@ -5084,7 +4932,7 @@
         <v>6.788585878560492e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>190.0599999999997</v>
+        <v>2362.419624778477</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000001e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>83.4736610241447</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 8.741x + -17384.610</t>
-        </is>
+      <c r="W16" t="n">
+        <v>8.741159248358283</v>
       </c>
       <c r="X16" t="n">
         <v>-17384.61005729551</v>
@@ -5136,7 +4982,7 @@
         <v>2.555286651214082e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>181.0699999999999</v>
+        <v>2334.801746610437</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000007969e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>83.27502334215912</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 8.481x + -16647.101</t>
-        </is>
+      <c r="W17" t="n">
+        <v>8.480687778600023</v>
       </c>
       <c r="X17" t="n">
         <v>-16647.10093931793</v>
@@ -5188,7 +5032,7 @@
         <v>1.797281210055078e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>184.0400000000002</v>
+        <v>2307.80205912893</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000512e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>82.39789008811356</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 7.493x + -14434.272</t>
-        </is>
+      <c r="W18" t="n">
+        <v>7.492546707066781</v>
       </c>
       <c r="X18" t="n">
         <v>-14434.2722710301</v>
@@ -5240,7 +5082,7 @@
         <v>1.31020319319979e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>184.4899999999998</v>
+        <v>2280.930890948543</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>82.35609982469042</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.451x + -14192.040</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.451097844058213</v>
       </c>
       <c r="X19" t="n">
         <v>-14192.03971697599</v>
@@ -5292,7 +5132,7 @@
         <v>5.333047516245059e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>179.6499999999999</v>
+        <v>2254.676723734933</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000014787e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>81.76283892476937</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 6.908x + -12937.893</t>
-        </is>
+      <c r="W20" t="n">
+        <v>6.907779746240011</v>
       </c>
       <c r="X20" t="n">
         <v>-12937.89300768527</v>
@@ -5344,7 +5182,7 @@
         <v>5.460650300269002e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>175.76</v>
+        <v>2227.970377721017</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000839e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>81.06612897739333</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 6.361x + -11706.661</t>
-        </is>
+      <c r="W21" t="n">
+        <v>6.361261055691005</v>
       </c>
       <c r="X21" t="n">
         <v>-11706.66105071141</v>
@@ -5396,7 +5232,7 @@
         <v>214.0256189424472</v>
       </c>
       <c r="Z21" t="n">
-        <v>175.0300000000002</v>
+        <v>2207.389570706674</v>
       </c>
       <c r="AA21" t="n">
         <v>1.363638032946128e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>79.43008667995478</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 5.359x + -9586.325</t>
-        </is>
+      <c r="W22" t="n">
+        <v>5.359014765432666</v>
       </c>
       <c r="X22" t="n">
         <v>-9586.32539212309</v>
@@ -5448,7 +5282,7 @@
         <v>2.193834251485703e-12</v>
       </c>
       <c r="Z22" t="n">
-        <v>166.3599999999999</v>
+        <v>2174.872196386693</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.00035781414279</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.145x + -21007.564</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.144766929927242</v>
       </c>
       <c r="X2" t="n">
         <v>-21007.56366235087</v>
@@ -5646,7 +5478,7 @@
         <v>7.041846685555586e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>562.9000000000001</v>
+        <v>2855.65665514407</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000009e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.8198252162511</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.682x + -29762.804</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.68222325035115</v>
       </c>
       <c r="X3" t="n">
         <v>-29762.80413971239</v>
@@ -5698,7 +5528,7 @@
         <v>3.158947464803032e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>284.3699999999999</v>
+        <v>2460.840346272374</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000072e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>86.01260614144554</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.346x + -29847.436</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.34602480409702</v>
       </c>
       <c r="X4" t="n">
         <v>-29847.4360263286</v>
@@ -5750,7 +5578,7 @@
         <v>6.56846089924788e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>227.25</v>
+        <v>2373.551420344808</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000021011e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>85.85115141078617</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.786x + -28068.067</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.78589804091581</v>
       </c>
       <c r="X5" t="n">
         <v>-28068.06724866177</v>
@@ -5802,7 +5628,7 @@
         <v>3.334758227760508e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>214.8199999999999</v>
+        <v>2333.537564832739</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>85.93285633669966</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.064x + -28245.927</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.06380409498742</v>
       </c>
       <c r="X6" t="n">
         <v>-28245.92726466854</v>
@@ -5854,7 +5678,7 @@
         <v>6.736481504495536e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>203.5799999999999</v>
+        <v>2300.107205920785</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>85.78326682271455</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.563x + -26819.058</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.56317675557796</v>
       </c>
       <c r="X7" t="n">
         <v>-26819.05838577188</v>
@@ -5906,7 +5728,7 @@
         <v>1.425876005003627e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>202.1299999999999</v>
+        <v>2269.287311431293</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000003992e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>85.83747668403021</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.740x + -26811.475</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.74044962876983</v>
       </c>
       <c r="X8" t="n">
         <v>-26811.47510177144</v>
@@ -5958,7 +5778,7 @@
         <v>2.288055662162158e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>197.52</v>
+        <v>2237.907758369383</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000146e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>85.83781108931814</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.742x + -26448.811</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.74155747999234</v>
       </c>
       <c r="X9" t="n">
         <v>-26448.81097753151</v>
@@ -6010,7 +5828,7 @@
         <v>1.374342983002057e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>192.4299999999998</v>
+        <v>2206.807522206962</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000029e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>85.88364294295634</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.895x + -26404.514</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.89509371658258</v>
       </c>
       <c r="X10" t="n">
         <v>-26404.51397399669</v>
@@ -6062,7 +5878,7 @@
         <v>1.40292540559079e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>189.9399999999998</v>
+        <v>2176.098698950425</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004222e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>85.66028011763316</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 13.177x + -24635.613</t>
-        </is>
+      <c r="W11" t="n">
+        <v>13.17738752761341</v>
       </c>
       <c r="X11" t="n">
         <v>-24635.61255281352</v>
@@ -6114,7 +5928,7 @@
         <v>2.742571044718832e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>190.5999999999999</v>
+        <v>2146.827841083477</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000184e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>84.97606556400319</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.375x + -28098.656</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.37532048525893</v>
       </c>
       <c r="X2" t="n">
         <v>-28098.65600786905</v>
@@ -6312,7 +6124,7 @@
         <v>1.516309795665231e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>330.77</v>
+        <v>2832.479758107666</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.65134975680714</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.150x + -30921.529</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.15022264494989</v>
       </c>
       <c r="X3" t="n">
         <v>-30921.52940052495</v>
@@ -6364,7 +6174,7 @@
         <v>1.558440525962691e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>222.4000000000001</v>
+        <v>2709.448860319832</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001159e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>85.64293230504576</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.125x + -30303.515</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.12471970893197</v>
       </c>
       <c r="X4" t="n">
         <v>-30303.514849251</v>
@@ -6416,7 +6224,7 @@
         <v>1.013495115745491e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>216.7000000000003</v>
+        <v>2665.179508477985</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>85.30943588204234</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.188x + -27674.417</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.18781407529653</v>
       </c>
       <c r="X5" t="n">
         <v>-27674.41706039802</v>
@@ -6468,7 +6274,7 @@
         <v>8.912568205178581e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>219.3599999999997</v>
+        <v>2631.110526981742</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000014e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.48201254710068</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.655x + -28438.269</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.65540850339689</v>
       </c>
       <c r="X6" t="n">
         <v>-28438.26903061018</v>
@@ -6520,7 +6324,7 @@
         <v>4.395283970990217e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>208.7799999999997</v>
+        <v>2595.744206171674</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000622e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>85.15700123226335</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.802x + -26079.561</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.80245208977526</v>
       </c>
       <c r="X7" t="n">
         <v>-26079.56078795576</v>
@@ -6572,7 +6374,7 @@
         <v>2.097861802157766e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>213.8399999999997</v>
+        <v>2561.390606631469</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000005275e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>85.08619277063494</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.632x + -25375.223</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.63155880635866</v>
       </c>
       <c r="X8" t="n">
         <v>-25375.22291093219</v>
@@ -6624,7 +6424,7 @@
         <v>7.303595998404677e-12</v>
       </c>
       <c r="Z8" t="n">
-        <v>210.1499999999996</v>
+        <v>2529.255322404762</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000001e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>84.9062979099409</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.219x + -24136.306</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.21870740715667</v>
       </c>
       <c r="X9" t="n">
         <v>-24136.30563903323</v>
@@ -6676,7 +6474,7 @@
         <v>3.1400411281563e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>211.2800000000002</v>
+        <v>2499.487328830749</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>84.87960821906553</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.160x + -23748.956</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.1599205966619</v>
       </c>
       <c r="X10" t="n">
         <v>-23748.95608733457</v>
@@ -6728,7 +6524,7 @@
         <v>1.264077801157476e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>204.3400000000001</v>
+        <v>2470.362966036245</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000007143e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>84.94434092385205</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.304x + -23811.521</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.30357114063363</v>
       </c>
       <c r="X11" t="n">
         <v>-23811.52145006346</v>
@@ -6780,7 +6574,7 @@
         <v>4.736970107731786e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>199.0300000000002</v>
+        <v>2442.704039156864</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000017284e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>84.55642893097483</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.494x + -21778.605</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.49371455950274</v>
       </c>
       <c r="X12" t="n">
         <v>-21778.60456972539</v>
@@ -6832,7 +6624,7 @@
         <v>7.703072928447077e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>202.2999999999997</v>
+        <v>2415.773380742343</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000004286e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>84.50021061082096</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 10.386x + -21320.763</t>
-        </is>
+      <c r="W13" t="n">
+        <v>10.38579723572532</v>
       </c>
       <c r="X13" t="n">
         <v>-21320.76304847044</v>
@@ -6884,7 +6674,7 @@
         <v>5.796389850219528e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>199.0300000000002</v>
+        <v>2389.21634967006</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000065e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>84.26300311926651</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 9.954x + -20159.528</t>
-        </is>
+      <c r="W14" t="n">
+        <v>9.953669445178058</v>
       </c>
       <c r="X14" t="n">
         <v>-20159.52844389887</v>
@@ -6936,7 +6724,7 @@
         <v>2.824930918373567e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>202.6000000000001</v>
+        <v>2362.603687215268</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000197e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>84.13873340762382</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 9.741x + -19518.801</t>
-        </is>
+      <c r="W15" t="n">
+        <v>9.741200637983383</v>
       </c>
       <c r="X15" t="n">
         <v>-19518.80075947692</v>
@@ -6988,7 +6774,7 @@
         <v>1.473080802826887e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>186.8200000000002</v>
+        <v>2336.332762416729</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000004113e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>84.04451907982248</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 9.586x + -18992.521</t>
-        </is>
+      <c r="W16" t="n">
+        <v>9.58600799485348</v>
       </c>
       <c r="X16" t="n">
         <v>-18992.52057695977</v>
@@ -7040,7 +6824,7 @@
         <v>2.667522414754383e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>175.9400000000001</v>
+        <v>2310.940986393167</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000308e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>83.513309699044</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 8.795x + -17149.488</t>
-        </is>
+      <c r="W17" t="n">
+        <v>8.795051481163036</v>
       </c>
       <c r="X17" t="n">
         <v>-17149.4884667881</v>
@@ -7092,7 +6874,7 @@
         <v>6.002937517158759e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>193.49</v>
+        <v>2285.377112737908</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000010564e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>83.38946512490763</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 8.629x + -16631.399</t>
-        </is>
+      <c r="W18" t="n">
+        <v>8.628851252904269</v>
       </c>
       <c r="X18" t="n">
         <v>-16631.39926971079</v>
@@ -7144,7 +6924,7 @@
         <v>5.75017130529854e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>183.47</v>
+        <v>2259.916081722555</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000010925e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>82.83076238342716</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 7.950x + -15087.003</t>
-        </is>
+      <c r="W19" t="n">
+        <v>7.950140409021635</v>
       </c>
       <c r="X19" t="n">
         <v>-15087.00295811185</v>
@@ -7196,7 +6974,7 @@
         <v>3.186025180523736e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>183.7199999999998</v>
+        <v>2234.719984376756</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000713e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>82.57466012938002</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 7.673x + -14364.122</t>
-        </is>
+      <c r="W20" t="n">
+        <v>7.673002776236249</v>
       </c>
       <c r="X20" t="n">
         <v>-14364.12233441492</v>
@@ -7248,7 +7024,7 @@
         <v>3.112743634453489e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>170.0200000000002</v>
+        <v>2209.293118100206</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000094e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>82.45793970557759</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 7.553x + -13962.155</t>
-        </is>
+      <c r="W21" t="n">
+        <v>7.552905227386511</v>
       </c>
       <c r="X21" t="n">
         <v>-13962.15478543122</v>
@@ -7300,7 +7074,7 @@
         <v>6.77775154945498e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>168.3700000000001</v>
+        <v>2183.771627758495</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000501e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>81.27339245855396</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 6.515x + -11790.909</t>
-        </is>
+      <c r="W22" t="n">
+        <v>6.514793796397279</v>
       </c>
       <c r="X22" t="n">
         <v>-11790.90891477915</v>
@@ -7352,7 +7124,7 @@
         <v>3.409358536093444e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>171.4799999999998</v>
+        <v>2157.791352734257</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000728e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>83.55552605910758</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.853x + -21350.109</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.853159625008077</v>
       </c>
       <c r="X2" t="n">
         <v>-21350.10912091603</v>
@@ -7550,7 +7320,7 @@
         <v>8.288473459606596e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>518.3900000000003</v>
+        <v>2640.53776847434</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000024413e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.91443960564308</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.000x + -29479.661</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.0001938732639</v>
       </c>
       <c r="X3" t="n">
         <v>-29479.66127775418</v>
@@ -7602,7 +7370,7 @@
         <v>3.054871269118177e-12</v>
       </c>
       <c r="Z3" t="n">
-        <v>275.29</v>
+        <v>2349.503403421527</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000012586e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.76694640305577</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.511x + -27298.556</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.51069463908578</v>
       </c>
       <c r="X4" t="n">
         <v>-27298.55563783196</v>
@@ -7654,7 +7420,7 @@
         <v>2.317944178429333e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>236.45</v>
+        <v>2279.715259742693</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000005e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>85.81296358917007</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.660x + -27115.736</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.65972128107918</v>
       </c>
       <c r="X5" t="n">
         <v>-27115.73589711453</v>
@@ -7706,7 +7470,7 @@
         <v>7.899469626949051e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>207.6599999999999</v>
+        <v>2242.36267692865</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.07823582328332</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.587x + -28667.123</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.58687223386161</v>
       </c>
       <c r="X6" t="n">
         <v>-28667.12261074701</v>
@@ -7758,7 +7520,7 @@
         <v>186.1080253299602</v>
       </c>
       <c r="Z6" t="n">
-        <v>193.0399999999997</v>
+        <v>2211.862347563584</v>
       </c>
       <c r="AA6" t="n">
         <v>1.382244200619495e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>85.90297124511967</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.961x + -26993.331</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.96087133101888</v>
       </c>
       <c r="X7" t="n">
         <v>-26993.33078943432</v>
@@ -7810,7 +7570,7 @@
         <v>3.675000967276618e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>194.6200000000001</v>
+        <v>2180.94831184644</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000015584e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>85.85662652813693</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 13.804x + -26286.683</t>
-        </is>
+      <c r="W8" t="n">
+        <v>13.8041787308637</v>
       </c>
       <c r="X8" t="n">
         <v>-26286.68335206001</v>
@@ -7862,7 +7620,7 @@
         <v>4.101096256983958e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>191.2499999999998</v>
+        <v>2148.73215383579</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000427e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>85.86279157538219</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.825x + -25941.163</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.82482081850526</v>
       </c>
       <c r="X9" t="n">
         <v>-25941.16270923146</v>
@@ -7914,7 +7670,7 @@
         <v>4.252752228430736e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>185.54</v>
+        <v>2115.756282430544</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>85.65624277715484</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.165x + -24281.903</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.165092706867</v>
       </c>
       <c r="X10" t="n">
         <v>-24281.90336628448</v>
@@ -7966,7 +7720,7 @@
         <v>1.290137604425771e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>188.49</v>
+        <v>2084.486497516774</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>85.43695396758204</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.530x + -22725.384</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.52991837568329</v>
       </c>
       <c r="X11" t="n">
         <v>-22725.38444258767</v>
@@ -8018,7 +7770,7 @@
         <v>1.546089694979385e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>188.8</v>
+        <v>2054.950347124875</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000053009e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.63524863918384</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.102x + -32128.849</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.10152568608163</v>
       </c>
       <c r="X2" t="n">
         <v>-32128.84861043092</v>
@@ -8216,7 +7966,7 @@
         <v>1.018497924899276e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>274.1100000000001</v>
+        <v>2766.750533962472</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000032e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>85.35730990994833</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.314x + -28740.528</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.31405156636912</v>
       </c>
       <c r="X3" t="n">
         <v>-28740.52815406123</v>
@@ -8268,7 +8016,7 @@
         <v>1.482444433917909e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>224.3500000000004</v>
+        <v>2667.402029510698</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000002e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>85.35317263523869</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.303x + -28195.257</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.30303966469938</v>
       </c>
       <c r="X4" t="n">
         <v>-28195.25688813455</v>
@@ -8320,7 +8066,7 @@
         <v>2.750350788854377e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>212.5600000000004</v>
+        <v>2621.92439174166</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>85.09924036513074</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.663x + -26301.867</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.66267838901804</v>
       </c>
       <c r="X5" t="n">
         <v>-26301.86661403129</v>
@@ -8372,7 +8116,7 @@
         <v>9.947837157897419e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>208.71</v>
+        <v>2585.253226771898</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>84.97962710126282</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.383x + -25313.033</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.383431827165</v>
       </c>
       <c r="X6" t="n">
         <v>-25313.03262601143</v>
@@ -8424,7 +8166,7 @@
         <v>6.953554496488012e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>206.0600000000004</v>
+        <v>2551.158655032718</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001853e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>84.75671805038773</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.897x + -23891.638</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.8969436870905</v>
       </c>
       <c r="X7" t="n">
         <v>-23891.63781397516</v>
@@ -8476,7 +8216,7 @@
         <v>1.166065075582911e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>203.4400000000001</v>
+        <v>2519.883370992912</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000656e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>84.64720096815343</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.673x + -23111.431</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.67273194047834</v>
       </c>
       <c r="X8" t="n">
         <v>-23111.43067449572</v>
@@ -8528,7 +8266,7 @@
         <v>1.009672237852387e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>198.4900000000002</v>
+        <v>2490.440800320759</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001725e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>84.35774023042264</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.122x + -21624.099</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.12191088673692</v>
       </c>
       <c r="X9" t="n">
         <v>-21624.09864836832</v>
@@ -8580,7 +8316,7 @@
         <v>1.021825600564301e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>191.8299999999999</v>
+        <v>2461.192357789637</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001761e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>83.98921141455334</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.497x + -19985.387</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.497161802539541</v>
       </c>
       <c r="X10" t="n">
         <v>-19985.38718802719</v>
@@ -8632,7 +8366,7 @@
         <v>6.280938585877643e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>189.2600000000002</v>
+        <v>2431.737844928728</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000012e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>83.69762411592801</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 9.054x + -18778.431</t>
-        </is>
+      <c r="W11" t="n">
+        <v>9.054444339298467</v>
       </c>
       <c r="X11" t="n">
         <v>-18778.43135635072</v>
@@ -8684,7 +8416,7 @@
         <v>3.971303253004576e-11</v>
       </c>
       <c r="Z11" t="n">
-        <v>188.23</v>
+        <v>2402.151911987078</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>83.55078183886248</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 8.847x + -18100.473</t>
-        </is>
+      <c r="W12" t="n">
+        <v>8.8465917255314</v>
       </c>
       <c r="X12" t="n">
         <v>-18100.47329219053</v>
@@ -8736,7 +8466,7 @@
         <v>3.92107921365423e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>192.2700000000004</v>
+        <v>2371.647713132661</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000153e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>82.96560479702194</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 8.104x + -16302.093</t>
-        </is>
+      <c r="W13" t="n">
+        <v>8.104124007129103</v>
       </c>
       <c r="X13" t="n">
         <v>-16302.09312969965</v>
@@ -8788,7 +8516,7 @@
         <v>5.593582725294761e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>190.1199999999999</v>
+        <v>2342.020353029596</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000001e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>82.55800099243558</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.656x + -15156.612</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.655632473944894</v>
       </c>
       <c r="X14" t="n">
         <v>-15156.61205430785</v>
@@ -8840,7 +8566,7 @@
         <v>5.326223305162802e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>199.6899999999998</v>
+        <v>2311.659965095116</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000009e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>81.75868938459175</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 6.904x + -13392.695</t>
-        </is>
+      <c r="W15" t="n">
+        <v>6.904253241952115</v>
       </c>
       <c r="X15" t="n">
         <v>-13392.69519369811</v>
@@ -8892,7 +8616,7 @@
         <v>5.345693589351309e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>176.6999999999998</v>
+        <v>2281.619374699685</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000001e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>80.34619777210902</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 5.879x + -11112.436</t>
-        </is>
+      <c r="W16" t="n">
+        <v>5.878777862048966</v>
       </c>
       <c r="X16" t="n">
         <v>-11112.43555011945</v>
@@ -8944,7 +8666,7 @@
         <v>9.047915646325895e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>172.6300000000001</v>
+        <v>2252.811461591035</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000587e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>81.52007563877578</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 6.707x + -12675.786</t>
-        </is>
+      <c r="W17" t="n">
+        <v>6.707231645344365</v>
       </c>
       <c r="X17" t="n">
         <v>-12675.7855336765</v>
@@ -8996,7 +8716,7 @@
         <v>4.918555176209131e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>185.4099999999999</v>
+        <v>2223.671646583151</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000016e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>79.82663183593523</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 5.573x + -10239.691</t>
-        </is>
+      <c r="W18" t="n">
+        <v>5.572627045231184</v>
       </c>
       <c r="X18" t="n">
         <v>-10239.6909478978</v>
@@ -9048,7 +8766,7 @@
         <v>5.034582895725092e-12</v>
       </c>
       <c r="Z18" t="n">
-        <v>173.75</v>
+        <v>2195.094847795729</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000055e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>76.98816776782273</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 4.327x + -7640.346</t>
-        </is>
+      <c r="W19" t="n">
+        <v>4.327398508367631</v>
       </c>
       <c r="X19" t="n">
         <v>-7640.345798778478</v>
@@ -9100,7 +8816,7 @@
         <v>2.432931517641712e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>170.46</v>
+        <v>2165.992430881933</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000026e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>74.31179345564641</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 3.560x + -6039.215</t>
-        </is>
+      <c r="W20" t="n">
+        <v>3.560426366862554</v>
       </c>
       <c r="X20" t="n">
         <v>-6039.21534301539</v>
@@ -9152,7 +8866,7 @@
         <v>8.660458373077296e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>168.4300000000001</v>
+        <v>2137.132715118158</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000002782e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>72.70441040408457</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 3.212x + -5310.017</t>
-        </is>
+      <c r="W21" t="n">
+        <v>3.211501033589583</v>
       </c>
       <c r="X21" t="n">
         <v>-5310.017213698121</v>
@@ -9204,7 +8916,7 @@
         <v>1.92893508239642e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>171.9300000000001</v>
+        <v>2108.33894790977</v>
       </c>
       <c r="AA21" t="n">
         <v>1.0000000000003e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>60.72049696681752</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 1.783x + -2490.739</t>
-        </is>
+      <c r="W22" t="n">
+        <v>1.783473718065563</v>
       </c>
       <c r="X22" t="n">
         <v>-2490.739084547793</v>
@@ -9256,7 +8966,7 @@
         <v>1.570472746967216e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>161.1700000000001</v>
+        <v>2081.046908599812</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000047997e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>83.81095713910436</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.222x + -18277.826</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.22158113214561</v>
       </c>
       <c r="X2" t="n">
         <v>-18277.82618051678</v>
@@ -9454,7 +9162,7 @@
         <v>162.6737353687826</v>
       </c>
       <c r="Z2" t="n">
-        <v>491.5599999999997</v>
+        <v>2162.228436743672</v>
       </c>
       <c r="AA2" t="n">
         <v>1.521377037002092e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.13256016928565</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.792x + -25629.094</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.79240498817922</v>
       </c>
       <c r="X3" t="n">
         <v>-25629.09437306778</v>
@@ -9506,7 +9212,7 @@
         <v>1.323351647208594e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>246.52</v>
+        <v>1916.660323873801</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.43465412858183</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.049x + -26886.779</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.04944060331486</v>
       </c>
       <c r="X4" t="n">
         <v>-26886.77868228229</v>
@@ -9558,7 +9262,7 @@
         <v>3.793287299827609e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>190.22</v>
+        <v>1860.144351889452</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.25734388198219</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.287x + -25053.523</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.2870748294734</v>
       </c>
       <c r="X5" t="n">
         <v>-25053.52312847711</v>
@@ -9610,7 +9312,7 @@
         <v>5.202144731797539e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>170.6099999999999</v>
+        <v>1826.396393760933</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000031e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.67647062046937</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.220x + -27927.971</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.2200984019528</v>
       </c>
       <c r="X6" t="n">
         <v>-27927.97081087231</v>
@@ -9662,7 +9362,7 @@
         <v>1.696445211737782e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>155.0799999999999</v>
+        <v>1794.850558248901</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000024e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.27229855641723</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.349x + -24313.640</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.3485774849083</v>
       </c>
       <c r="X7" t="n">
         <v>-24313.63993911394</v>
@@ -9714,7 +9412,7 @@
         <v>5.459990444312311e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>160.76</v>
+        <v>1762.967762768062</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.06161589753195</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.525x + -22522.850</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.52512274261547</v>
       </c>
       <c r="X8" t="n">
         <v>-22522.8502908081</v>
@@ -9766,7 +9462,7 @@
         <v>3.839332757947256e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>163.45</v>
+        <v>1731.525000378381</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000668e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.21354702955047</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.110x + -23105.850</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.10974652623057</v>
       </c>
       <c r="X9" t="n">
         <v>-23105.8503023518</v>
@@ -9818,7 +9512,7 @@
         <v>6.278126041582441e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>152.55</v>
+        <v>1700.93793595741</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>86.27818843129664</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.373x + -23136.454</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.37293567916594</v>
       </c>
       <c r="X10" t="n">
         <v>-23136.45351873905</v>
@@ -9870,7 +9562,7 @@
         <v>3.727421379567755e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>146.78</v>
+        <v>1671.997039690264</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>86.0168749706659</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.361x + -21211.210</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.36144957870862</v>
       </c>
       <c r="X11" t="n">
         <v>-21211.2100944628</v>
@@ -9922,7 +9612,7 @@
         <v>1.501400957957264e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>148.0800000000002</v>
+        <v>1645.259342180763</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000010075e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-301.1800000000003</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-219.55</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-188.1500000000001</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-181.5500000000002</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-171.45</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-160.3499999999999</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-159.2499999999998</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-146.8899999999999</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-140.25</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-140.1899999999998</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-491.8600000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-293.5999999999999</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-247.6500000000001</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-210.2399999999998</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-210.6399999999999</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-201.05</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-191.8599999999999</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-189.78</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-177.24</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-163.5600000000002</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-562.9000000000001</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-284.3699999999999</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-227.25</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-214.8199999999999</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-203.5799999999999</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-197.6800000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-191.5999999999999</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-180.4000000000001</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-175.6000000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-168.73</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-518.3900000000003</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-275.29</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-236.45</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-207.6599999999999</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-187.1000000000001</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-183.5699999999999</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-168.99</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-160.3999999999999</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-159.4199999999998</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-155.6899999999998</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-491.5599999999997</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-246.52</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-190.22</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-170.6099999999999</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-147.0799999999999</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-145.3600000000001</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-150.23</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-128.0800000000002</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-121.51</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-117.97</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-301.1800000000003</v>
+        <v>1704.605</v>
       </c>
       <c r="D2" t="n">
         <v>2.32371e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-219.55</v>
+        <v>1664.688</v>
       </c>
       <c r="D3" t="n">
         <v>2.27875e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-188.1500000000001</v>
+        <v>1630.645</v>
       </c>
       <c r="D4" t="n">
         <v>2.26419e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-181.5500000000002</v>
+        <v>1600.033</v>
       </c>
       <c r="D5" t="n">
         <v>2.25594e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-171.45</v>
+        <v>1564.504</v>
       </c>
       <c r="D6" t="n">
         <v>2.25026e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-160.3499999999999</v>
+        <v>1535.392</v>
       </c>
       <c r="D7" t="n">
         <v>2.24808e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-159.2499999999998</v>
+        <v>1501.556</v>
       </c>
       <c r="D8" t="n">
         <v>2.24698e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-146.8899999999999</v>
+        <v>1480.783</v>
       </c>
       <c r="D9" t="n">
         <v>2.2455e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-140.25</v>
+        <v>1458.165</v>
       </c>
       <c r="D10" t="n">
         <v>2.24504e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-140.1899999999998</v>
+        <v>1430.516</v>
       </c>
       <c r="D11" t="n">
         <v>2.24506e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-213.23</v>
+        <v>2055.975</v>
       </c>
       <c r="D2" t="n">
         <v>2.19786e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-165.1400000000003</v>
+        <v>1927.415</v>
       </c>
       <c r="D3" t="n">
         <v>2.23489e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-155.3899999999999</v>
+        <v>1883.881</v>
       </c>
       <c r="D4" t="n">
         <v>2.24766e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-156.7000000000003</v>
+        <v>1846.941</v>
       </c>
       <c r="D5" t="n">
         <v>2.2551e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-152.4200000000001</v>
+        <v>1811.258</v>
       </c>
       <c r="D6" t="n">
         <v>2.26554e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-130.25</v>
+        <v>1801.913</v>
       </c>
       <c r="D7" t="n">
         <v>2.2703e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-121.5599999999999</v>
+        <v>1774.466</v>
       </c>
       <c r="D8" t="n">
         <v>2.2791e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-130.9200000000001</v>
+        <v>1735.871</v>
       </c>
       <c r="D9" t="n">
         <v>2.2848e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-118.8299999999999</v>
+        <v>1721.034</v>
       </c>
       <c r="D10" t="n">
         <v>2.29191e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-115.3699999999999</v>
+        <v>1694.981</v>
       </c>
       <c r="D11" t="n">
         <v>2.29819e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-114.7399999999998</v>
+        <v>1671.581</v>
       </c>
       <c r="D12" t="n">
         <v>2.30304e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-101.0600000000002</v>
+        <v>1658.271</v>
       </c>
       <c r="D13" t="n">
         <v>2.30797e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-96.05000000000018</v>
+        <v>1636.18</v>
       </c>
       <c r="D14" t="n">
         <v>2.31384e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-87.21000000000004</v>
+        <v>1615.278</v>
       </c>
       <c r="D15" t="n">
         <v>2.32064e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-83.31999999999994</v>
+        <v>1595.891</v>
       </c>
       <c r="D16" t="n">
         <v>2.32462e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-81.75</v>
+        <v>1571.486</v>
       </c>
       <c r="D17" t="n">
         <v>2.33055e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-77.52999999999997</v>
+        <v>1549.121</v>
       </c>
       <c r="D18" t="n">
         <v>2.33788e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-72.68000000000006</v>
+        <v>1529.287</v>
       </c>
       <c r="D19" t="n">
         <v>2.34189e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-69.31999999999994</v>
+        <v>1508.896</v>
       </c>
       <c r="D20" t="n">
         <v>2.34684e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-56.75</v>
+        <v>1493.872</v>
       </c>
       <c r="D21" t="n">
         <v>2.35226e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-63.19000000000005</v>
+        <v>1460.396</v>
       </c>
       <c r="D22" t="n">
         <v>2.35769e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-296.21</v>
+        <v>2177.713</v>
       </c>
       <c r="D2" t="n">
         <v>2.11868e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-223.5999999999999</v>
+        <v>2055.358</v>
       </c>
       <c r="D3" t="n">
         <v>2.14598e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-186.9000000000001</v>
+        <v>2036.184</v>
       </c>
       <c r="D4" t="n">
         <v>2.14944e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-188.9300000000003</v>
+        <v>2002.642</v>
       </c>
       <c r="D5" t="n">
         <v>2.15305e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-160.8200000000002</v>
+        <v>1990.091</v>
       </c>
       <c r="D6" t="n">
         <v>2.15907e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-162.1199999999999</v>
+        <v>1957.682</v>
       </c>
       <c r="D7" t="n">
         <v>2.16352e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-152.3099999999999</v>
+        <v>1928.249</v>
       </c>
       <c r="D8" t="n">
         <v>2.17234e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-145.4200000000001</v>
+        <v>1902.033</v>
       </c>
       <c r="D9" t="n">
         <v>2.17781e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-136.5500000000002</v>
+        <v>1876.253</v>
       </c>
       <c r="D10" t="n">
         <v>2.18538e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-139.04</v>
+        <v>1843.411</v>
       </c>
       <c r="D11" t="n">
         <v>2.1917e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-126.3000000000002</v>
+        <v>1821.224</v>
       </c>
       <c r="D12" t="n">
         <v>2.19756e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-118.4299999999998</v>
+        <v>1803.778</v>
       </c>
       <c r="D13" t="n">
         <v>2.20377e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-112.27</v>
+        <v>1783.416</v>
       </c>
       <c r="D14" t="n">
         <v>2.20764e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-109.25</v>
+        <v>1761.645</v>
       </c>
       <c r="D15" t="n">
         <v>2.2129e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-103.8200000000002</v>
+        <v>1742.101</v>
       </c>
       <c r="D16" t="n">
         <v>2.21886e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-94.85000000000036</v>
+        <v>1721.975</v>
       </c>
       <c r="D17" t="n">
         <v>2.22354e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-95.95000000000027</v>
+        <v>1697.583</v>
       </c>
       <c r="D18" t="n">
         <v>2.22879e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-88.6099999999999</v>
+        <v>1677.044</v>
       </c>
       <c r="D19" t="n">
         <v>2.2336e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-86.05999999999995</v>
+        <v>1657.118</v>
       </c>
       <c r="D20" t="n">
         <v>2.23833e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-83.0799999999997</v>
+        <v>1632.993</v>
       </c>
       <c r="D21" t="n">
         <v>2.24414e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-72.85000000000014</v>
+        <v>1611.377</v>
       </c>
       <c r="D22" t="n">
         <v>2.24924e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-491.8600000000001</v>
+        <v>2030.383</v>
       </c>
       <c r="D2" t="n">
         <v>2.22095e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-293.5999999999999</v>
+        <v>1768.114</v>
       </c>
       <c r="D3" t="n">
         <v>2.29232e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-247.6500000000001</v>
+        <v>1691.148</v>
       </c>
       <c r="D4" t="n">
         <v>2.28638e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-210.2399999999998</v>
+        <v>1663.227</v>
       </c>
       <c r="D5" t="n">
         <v>2.27723e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-210.6399999999999</v>
+        <v>1622.174</v>
       </c>
       <c r="D6" t="n">
         <v>2.27069e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-201.05</v>
+        <v>1587.455</v>
       </c>
       <c r="D7" t="n">
         <v>2.26984e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-191.8599999999999</v>
+        <v>1563.381</v>
       </c>
       <c r="D8" t="n">
         <v>2.26812e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-189.78</v>
+        <v>1529.002</v>
       </c>
       <c r="D9" t="n">
         <v>2.26852e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-177.24</v>
+        <v>1506.849</v>
       </c>
       <c r="D10" t="n">
         <v>2.26951e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-163.5600000000002</v>
+        <v>1487.658</v>
       </c>
       <c r="D11" t="n">
         <v>2.27246e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-346.3000000000002</v>
+        <v>2113.896</v>
       </c>
       <c r="D2" t="n">
         <v>2.2132e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-243.1199999999999</v>
+        <v>1995.458</v>
       </c>
       <c r="D3" t="n">
         <v>2.23485e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-205.0600000000004</v>
+        <v>1967.076</v>
       </c>
       <c r="D4" t="n">
         <v>2.23952e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-187.1099999999997</v>
+        <v>1929.858</v>
       </c>
       <c r="D5" t="n">
         <v>2.24564e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-163.1100000000001</v>
+        <v>1910.006</v>
       </c>
       <c r="D6" t="n">
         <v>2.25379e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-163.8399999999997</v>
+        <v>1877.66</v>
       </c>
       <c r="D7" t="n">
         <v>2.26035e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-145.2800000000002</v>
+        <v>1860.218</v>
       </c>
       <c r="D8" t="n">
         <v>2.26865e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-139.7200000000003</v>
+        <v>1834.022</v>
       </c>
       <c r="D9" t="n">
         <v>2.2748e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-134.9499999999998</v>
+        <v>1810.193</v>
       </c>
       <c r="D10" t="n">
         <v>2.28008e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-132.77</v>
+        <v>1780.483</v>
       </c>
       <c r="D11" t="n">
         <v>2.28817e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-117.1100000000001</v>
+        <v>1764.524</v>
       </c>
       <c r="D12" t="n">
         <v>2.29736e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-121.6799999999998</v>
+        <v>1727.338</v>
       </c>
       <c r="D13" t="n">
         <v>2.30153e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-115.5599999999999</v>
+        <v>1702.523</v>
       </c>
       <c r="D14" t="n">
         <v>2.30755e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-109.8500000000001</v>
+        <v>1682.053</v>
       </c>
       <c r="D15" t="n">
         <v>2.31374e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-100.1099999999999</v>
+        <v>1670.223</v>
       </c>
       <c r="D16" t="n">
         <v>2.3206e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-101.28</v>
+        <v>1644.115</v>
       </c>
       <c r="D17" t="n">
         <v>2.32423e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-93.81999999999971</v>
+        <v>1620.976</v>
       </c>
       <c r="D18" t="n">
         <v>2.33175e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-89.97000000000003</v>
+        <v>1600.633</v>
       </c>
       <c r="D19" t="n">
         <v>2.3373e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-84.19000000000005</v>
+        <v>1579.877</v>
       </c>
       <c r="D20" t="n">
         <v>2.34266e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-80.11999999999989</v>
+        <v>1560.119</v>
       </c>
       <c r="D21" t="n">
         <v>2.34789e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-68.63999999999987</v>
+        <v>1543.47</v>
       </c>
       <c r="D22" t="n">
         <v>2.35429e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-562.9000000000001</v>
+        <v>2174.471</v>
       </c>
       <c r="D2" t="n">
         <v>2.20078e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-284.3699999999999</v>
+        <v>1764.7</v>
       </c>
       <c r="D3" t="n">
         <v>2.33503e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-227.25</v>
+        <v>1671.263</v>
       </c>
       <c r="D4" t="n">
         <v>2.3384e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-214.8199999999999</v>
+        <v>1625.661</v>
       </c>
       <c r="D5" t="n">
         <v>2.33246e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-203.5799999999999</v>
+        <v>1597.852</v>
       </c>
       <c r="D6" t="n">
         <v>2.32974e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-197.6800000000001</v>
+        <v>1564.899</v>
       </c>
       <c r="D7" t="n">
         <v>2.33135e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-191.5999999999999</v>
+        <v>1538.293</v>
       </c>
       <c r="D8" t="n">
         <v>2.33142e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-180.4000000000001</v>
+        <v>1513.229</v>
       </c>
       <c r="D9" t="n">
         <v>2.33424e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-175.6000000000001</v>
+        <v>1488.29</v>
       </c>
       <c r="D10" t="n">
         <v>2.33649e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-168.73</v>
+        <v>1459.921</v>
       </c>
       <c r="D11" t="n">
         <v>2.34023e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-330.77</v>
+        <v>2093.148</v>
       </c>
       <c r="D2" t="n">
         <v>2.23371e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-220.8800000000001</v>
+        <v>1979.778</v>
       </c>
       <c r="D3" t="n">
         <v>2.25922e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-200.9100000000003</v>
+        <v>1936.725</v>
       </c>
       <c r="D4" t="n">
         <v>2.26895e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-190.5099999999998</v>
+        <v>1901.838</v>
       </c>
       <c r="D5" t="n">
         <v>2.27855e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-172.0099999999998</v>
+        <v>1881.244</v>
       </c>
       <c r="D6" t="n">
         <v>2.28716e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-171.2999999999997</v>
+        <v>1844.162</v>
       </c>
       <c r="D7" t="n">
         <v>2.29535e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-163.3799999999997</v>
+        <v>1818.872</v>
       </c>
       <c r="D8" t="n">
         <v>2.30346e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-164</v>
+        <v>1789.279</v>
       </c>
       <c r="D9" t="n">
         <v>2.30949e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-146.4000000000001</v>
+        <v>1769.016</v>
       </c>
       <c r="D10" t="n">
         <v>2.31837e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-141.6200000000003</v>
+        <v>1748.982</v>
       </c>
       <c r="D11" t="n">
         <v>2.32653e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-139.8899999999999</v>
+        <v>1720.424</v>
       </c>
       <c r="D12" t="n">
         <v>2.33275e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-133.5500000000002</v>
+        <v>1699.803</v>
       </c>
       <c r="D13" t="n">
         <v>2.33855e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-136.3100000000002</v>
+        <v>1671.467</v>
       </c>
       <c r="D14" t="n">
         <v>2.34328e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-112.4700000000003</v>
+        <v>1664.904</v>
       </c>
       <c r="D15" t="n">
         <v>2.35094e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-100.4500000000003</v>
+        <v>1653.147</v>
       </c>
       <c r="D16" t="n">
         <v>2.35864e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-113.97</v>
+        <v>1615.759</v>
       </c>
       <c r="D17" t="n">
         <v>2.36385e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-101.8799999999999</v>
+        <v>1602.056</v>
       </c>
       <c r="D18" t="n">
         <v>2.37029e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-96.98000000000002</v>
+        <v>1579.637</v>
       </c>
       <c r="D19" t="n">
         <v>2.37695e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-83.66000000000008</v>
+        <v>1568.663</v>
       </c>
       <c r="D20" t="n">
         <v>2.3828e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-81.50999999999999</v>
+        <v>1548.828</v>
       </c>
       <c r="D21" t="n">
         <v>2.38759e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-77.5</v>
+        <v>1523.119</v>
       </c>
       <c r="D22" t="n">
         <v>2.39541e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-518.3900000000003</v>
+        <v>2015.446</v>
       </c>
       <c r="D2" t="n">
         <v>2.2951e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-275.29</v>
+        <v>1701.466</v>
       </c>
       <c r="D3" t="n">
         <v>2.3632e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-236.45</v>
+        <v>1615.332</v>
       </c>
       <c r="D4" t="n">
         <v>2.35847e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-207.6599999999999</v>
+        <v>1579.975</v>
       </c>
       <c r="D5" t="n">
         <v>2.35448e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-187.1000000000001</v>
+        <v>1560.663</v>
       </c>
       <c r="D6" t="n">
         <v>2.35076e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-183.5699999999999</v>
+        <v>1533.154</v>
       </c>
       <c r="D7" t="n">
         <v>2.35186e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-168.99</v>
+        <v>1503.626</v>
       </c>
       <c r="D8" t="n">
         <v>2.35504e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-160.3999999999999</v>
+        <v>1478.668</v>
       </c>
       <c r="D9" t="n">
         <v>2.35779e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-159.4199999999998</v>
+        <v>1444.883</v>
       </c>
       <c r="D10" t="n">
         <v>2.36144e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-155.6899999999998</v>
+        <v>1415.103</v>
       </c>
       <c r="D11" t="n">
         <v>2.36593e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-274.1100000000001</v>
+        <v>2087.227</v>
       </c>
       <c r="D2" t="n">
         <v>2.25991e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-201.1000000000004</v>
+        <v>1975.505</v>
       </c>
       <c r="D3" t="n">
         <v>2.27602e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-174.9000000000001</v>
+        <v>1936.978</v>
       </c>
       <c r="D4" t="n">
         <v>2.28726e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-157.3599999999997</v>
+        <v>1906.245</v>
       </c>
       <c r="D5" t="n">
         <v>2.29696e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-150.7200000000003</v>
+        <v>1875.23</v>
       </c>
       <c r="D6" t="n">
         <v>2.3042e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-140.5300000000002</v>
+        <v>1848.091</v>
       </c>
       <c r="D7" t="n">
         <v>2.31277e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-131.4099999999999</v>
+        <v>1824.38</v>
       </c>
       <c r="D8" t="n">
         <v>2.32009e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-118.0699999999997</v>
+        <v>1807.371</v>
       </c>
       <c r="D9" t="n">
         <v>2.3284e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-110.3499999999999</v>
+        <v>1783.667</v>
       </c>
       <c r="D10" t="n">
         <v>2.33579e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-106.0599999999999</v>
+        <v>1757.416</v>
       </c>
       <c r="D11" t="n">
         <v>2.34293e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-109.5900000000001</v>
+        <v>1725.554</v>
       </c>
       <c r="D12" t="n">
         <v>2.34913e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-101.48</v>
+        <v>1701.919</v>
       </c>
       <c r="D13" t="n">
         <v>2.35566e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-109.9100000000001</v>
+        <v>1666.991</v>
       </c>
       <c r="D14" t="n">
         <v>2.36302e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-82.61000000000013</v>
+        <v>1663.012</v>
       </c>
       <c r="D15" t="n">
         <v>2.37135e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-74.67000000000007</v>
+        <v>1639.766</v>
       </c>
       <c r="D16" t="n">
         <v>2.37598e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-88.48000000000002</v>
+        <v>1601.694</v>
       </c>
       <c r="D17" t="n">
         <v>2.38251e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-72.79999999999995</v>
+        <v>1590.057</v>
       </c>
       <c r="D18" t="n">
         <v>2.38904e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-63.86999999999989</v>
+        <v>1565.619</v>
       </c>
       <c r="D19" t="n">
         <v>2.3969e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-59.73000000000002</v>
+        <v>1542.369</v>
       </c>
       <c r="D20" t="n">
         <v>2.40298e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-57.72000000000003</v>
+        <v>1512.118</v>
       </c>
       <c r="D21" t="n">
         <v>2.41056e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-47.51999999999998</v>
+        <v>1499.942</v>
       </c>
       <c r="D22" t="n">
         <v>2.41613e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-491.5599999999997</v>
+        <v>1564.238</v>
       </c>
       <c r="D2" t="n">
         <v>2.46739e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-246.52</v>
+        <v>1311.817</v>
       </c>
       <c r="D3" t="n">
         <v>2.46746e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-190.22</v>
+        <v>1257.615</v>
       </c>
       <c r="D4" t="n">
         <v>2.4432e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-170.6099999999999</v>
+        <v>1224.055</v>
       </c>
       <c r="D5" t="n">
         <v>2.43125e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-147.0799999999999</v>
+        <v>1206.946</v>
       </c>
       <c r="D6" t="n">
         <v>2.42612e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-145.3600000000001</v>
+        <v>1168.768</v>
       </c>
       <c r="D7" t="n">
         <v>2.42319e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-150.23</v>
+        <v>1137.28</v>
       </c>
       <c r="D8" t="n">
         <v>2.42295e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-128.0800000000002</v>
+        <v>1119.487</v>
       </c>
       <c r="D9" t="n">
         <v>2.42347e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-121.51</v>
+        <v>1096.526</v>
       </c>
       <c r="D10" t="n">
         <v>2.42372e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-117.97</v>
+        <v>1069.946</v>
       </c>
       <c r="D11" t="n">
         <v>2.42542e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1704.605</v>
       </c>
+      <c r="C2" t="n">
+        <v>2132.40221344781</v>
+      </c>
       <c r="D2" t="n">
         <v>2.32371e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1664.688</v>
       </c>
+      <c r="C3" t="n">
+        <v>2089.94350957349</v>
+      </c>
       <c r="D3" t="n">
         <v>2.27875e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1630.645</v>
       </c>
+      <c r="C4" t="n">
+        <v>2056.53487820432</v>
+      </c>
       <c r="D4" t="n">
         <v>2.26419e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1600.033</v>
       </c>
+      <c r="C5" t="n">
+        <v>2029.228445631155</v>
+      </c>
       <c r="D5" t="n">
         <v>2.25594e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1564.504</v>
       </c>
+      <c r="C6" t="n">
+        <v>1995.841836387625</v>
+      </c>
       <c r="D6" t="n">
         <v>2.25026e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1535.392</v>
       </c>
+      <c r="C7" t="n">
+        <v>1970.084291695183</v>
+      </c>
       <c r="D7" t="n">
         <v>2.24808e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1501.556</v>
       </c>
+      <c r="C8" t="n">
+        <v>1939.412165457162</v>
+      </c>
       <c r="D8" t="n">
         <v>2.24698e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1480.783</v>
       </c>
+      <c r="C9" t="n">
+        <v>1917.042172816891</v>
+      </c>
       <c r="D9" t="n">
         <v>2.2455e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1458.165</v>
       </c>
+      <c r="C10" t="n">
+        <v>1894.39898490107</v>
+      </c>
       <c r="D10" t="n">
         <v>2.24504e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1430.516</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1869.990451315093</v>
       </c>
       <c r="D11" t="n">
         <v>2.24506e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>2055.975</v>
       </c>
+      <c r="C2" t="n">
+        <v>2464.362302602164</v>
+      </c>
       <c r="D2" t="n">
         <v>2.19786e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1927.415</v>
       </c>
+      <c r="C3" t="n">
+        <v>2312.166020913373</v>
+      </c>
       <c r="D3" t="n">
         <v>2.23489e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1883.881</v>
       </c>
+      <c r="C4" t="n">
+        <v>2267.754455344852</v>
+      </c>
       <c r="D4" t="n">
         <v>2.24766e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1846.941</v>
       </c>
+      <c r="C5" t="n">
+        <v>2234.567278635461</v>
+      </c>
       <c r="D5" t="n">
         <v>2.2551e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1811.258</v>
       </c>
+      <c r="C6" t="n">
+        <v>2204.697825785984</v>
+      </c>
       <c r="D6" t="n">
         <v>2.26554e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1801.913</v>
       </c>
+      <c r="C7" t="n">
+        <v>2187.15772088575</v>
+      </c>
       <c r="D7" t="n">
         <v>2.2703e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1774.466</v>
       </c>
+      <c r="C8" t="n">
+        <v>2161.934230160967</v>
+      </c>
       <c r="D8" t="n">
         <v>2.2791e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1735.871</v>
       </c>
+      <c r="C9" t="n">
+        <v>2128.891783010265</v>
+      </c>
       <c r="D9" t="n">
         <v>2.2848e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1721.034</v>
       </c>
+      <c r="C10" t="n">
+        <v>2109.505464133086</v>
+      </c>
       <c r="D10" t="n">
         <v>2.29191e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1694.981</v>
       </c>
+      <c r="C11" t="n">
+        <v>2084.471351487034</v>
+      </c>
       <c r="D11" t="n">
         <v>2.29819e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1671.581</v>
       </c>
+      <c r="C12" t="n">
+        <v>2063.069266985512</v>
+      </c>
       <c r="D12" t="n">
         <v>2.30304e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1658.271</v>
       </c>
+      <c r="C13" t="n">
+        <v>2045.204912796311</v>
+      </c>
       <c r="D13" t="n">
         <v>2.30797e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1636.18</v>
       </c>
+      <c r="C14" t="n">
+        <v>2025.62557218841</v>
+      </c>
       <c r="D14" t="n">
         <v>2.31384e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1615.278</v>
       </c>
+      <c r="C15" t="n">
+        <v>2005.04681749927</v>
+      </c>
       <c r="D15" t="n">
         <v>2.32064e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1595.891</v>
       </c>
+      <c r="C16" t="n">
+        <v>1984.791937663044</v>
+      </c>
       <c r="D16" t="n">
         <v>2.32462e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1571.486</v>
       </c>
+      <c r="C17" t="n">
+        <v>1960.865054227795</v>
+      </c>
       <c r="D17" t="n">
         <v>2.33055e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1549.121</v>
       </c>
+      <c r="C18" t="n">
+        <v>1940.411146607287</v>
+      </c>
       <c r="D18" t="n">
         <v>2.33788e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1529.287</v>
       </c>
+      <c r="C19" t="n">
+        <v>1922.044859602127</v>
+      </c>
       <c r="D19" t="n">
         <v>2.34189e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1508.896</v>
       </c>
+      <c r="C20" t="n">
+        <v>1900.421201499156</v>
+      </c>
       <c r="D20" t="n">
         <v>2.34684e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1493.872</v>
       </c>
+      <c r="C21" t="n">
+        <v>1881.369059089088</v>
+      </c>
       <c r="D21" t="n">
         <v>2.35226e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1460.396</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1856.486926945022</v>
       </c>
       <c r="D22" t="n">
         <v>2.35769e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>2177.713</v>
       </c>
+      <c r="C2" t="n">
+        <v>2590.566926474108</v>
+      </c>
       <c r="D2" t="n">
         <v>2.11868e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>2055.358</v>
       </c>
+      <c r="C3" t="n">
+        <v>2447.848489300685</v>
+      </c>
       <c r="D3" t="n">
         <v>2.14598e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>2036.184</v>
       </c>
+      <c r="C4" t="n">
+        <v>2424.721380474324</v>
+      </c>
       <c r="D4" t="n">
         <v>2.14944e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>2002.642</v>
       </c>
+      <c r="C5" t="n">
+        <v>2399.42252309301</v>
+      </c>
       <c r="D5" t="n">
         <v>2.15305e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1990.091</v>
       </c>
+      <c r="C6" t="n">
+        <v>2381.53282050074</v>
+      </c>
       <c r="D6" t="n">
         <v>2.15907e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1957.682</v>
       </c>
+      <c r="C7" t="n">
+        <v>2351.783040028789</v>
+      </c>
       <c r="D7" t="n">
         <v>2.16352e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1928.249</v>
       </c>
+      <c r="C8" t="n">
+        <v>2323.483460609316</v>
+      </c>
       <c r="D8" t="n">
         <v>2.17234e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1902.033</v>
       </c>
+      <c r="C9" t="n">
+        <v>2297.520941038831</v>
+      </c>
       <c r="D9" t="n">
         <v>2.17781e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1876.253</v>
       </c>
+      <c r="C10" t="n">
+        <v>2273.173556443919</v>
+      </c>
       <c r="D10" t="n">
         <v>2.18538e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1843.411</v>
       </c>
+      <c r="C11" t="n">
+        <v>2245.030435716978</v>
+      </c>
       <c r="D11" t="n">
         <v>2.1917e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1821.224</v>
       </c>
+      <c r="C12" t="n">
+        <v>2221.18190126284</v>
+      </c>
       <c r="D12" t="n">
         <v>2.19756e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1803.778</v>
       </c>
+      <c r="C13" t="n">
+        <v>2203.865396376778</v>
+      </c>
       <c r="D13" t="n">
         <v>2.20377e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1783.416</v>
       </c>
+      <c r="C14" t="n">
+        <v>2180.758326327946</v>
+      </c>
       <c r="D14" t="n">
         <v>2.20764e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1761.645</v>
       </c>
+      <c r="C15" t="n">
+        <v>2160.958520287356</v>
+      </c>
       <c r="D15" t="n">
         <v>2.2129e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1742.101</v>
       </c>
+      <c r="C16" t="n">
+        <v>2139.606425454234</v>
+      </c>
       <c r="D16" t="n">
         <v>2.21886e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1721.975</v>
       </c>
+      <c r="C17" t="n">
+        <v>2120.111114023082</v>
+      </c>
       <c r="D17" t="n">
         <v>2.22354e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1697.583</v>
       </c>
+      <c r="C18" t="n">
+        <v>2092.77134814449</v>
+      </c>
       <c r="D18" t="n">
         <v>2.22879e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1677.044</v>
       </c>
+      <c r="C19" t="n">
+        <v>2072.035920391601</v>
+      </c>
       <c r="D19" t="n">
         <v>2.2336e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1657.118</v>
       </c>
+      <c r="C20" t="n">
+        <v>2051.082658491603</v>
+      </c>
       <c r="D20" t="n">
         <v>2.23833e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1632.993</v>
       </c>
+      <c r="C21" t="n">
+        <v>2028.587618601337</v>
+      </c>
       <c r="D21" t="n">
         <v>2.24414e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1611.377</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2008.274370449835</v>
       </c>
       <c r="D22" t="n">
         <v>2.24924e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2030.383</v>
       </c>
+      <c r="C2" t="n">
+        <v>2511.088117554245</v>
+      </c>
       <c r="D2" t="n">
         <v>2.22095e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1768.114</v>
       </c>
+      <c r="C3" t="n">
+        <v>2195.803911888395</v>
+      </c>
       <c r="D3" t="n">
         <v>2.29232e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1691.148</v>
       </c>
+      <c r="C4" t="n">
+        <v>2111.631978097801</v>
+      </c>
       <c r="D4" t="n">
         <v>2.28638e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1663.227</v>
       </c>
+      <c r="C5" t="n">
+        <v>2083.728059385726</v>
+      </c>
       <c r="D5" t="n">
         <v>2.27723e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1622.174</v>
       </c>
+      <c r="C6" t="n">
+        <v>2049.576417678078</v>
+      </c>
       <c r="D6" t="n">
         <v>2.27069e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1587.455</v>
       </c>
+      <c r="C7" t="n">
+        <v>2016.248796425973</v>
+      </c>
       <c r="D7" t="n">
         <v>2.26984e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1563.381</v>
       </c>
+      <c r="C8" t="n">
+        <v>1993.540739103445</v>
+      </c>
       <c r="D8" t="n">
         <v>2.26812e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1529.002</v>
       </c>
+      <c r="C9" t="n">
+        <v>1960.827062704892</v>
+      </c>
       <c r="D9" t="n">
         <v>2.26852e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1506.849</v>
       </c>
+      <c r="C10" t="n">
+        <v>1939.734527749967</v>
+      </c>
       <c r="D10" t="n">
         <v>2.26951e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1487.658</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1915.523207960869</v>
       </c>
       <c r="D11" t="n">
         <v>2.27246e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>2113.896</v>
       </c>
+      <c r="C2" t="n">
+        <v>2527.27840907594</v>
+      </c>
       <c r="D2" t="n">
         <v>2.2132e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1995.458</v>
       </c>
+      <c r="C3" t="n">
+        <v>2392.915050861463</v>
+      </c>
       <c r="D3" t="n">
         <v>2.23485e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1967.076</v>
       </c>
+      <c r="C4" t="n">
+        <v>2358.93003281647</v>
+      </c>
       <c r="D4" t="n">
         <v>2.23952e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1929.858</v>
       </c>
+      <c r="C5" t="n">
+        <v>2326.086936584482</v>
+      </c>
       <c r="D5" t="n">
         <v>2.24564e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1910.006</v>
       </c>
+      <c r="C6" t="n">
+        <v>2304.523567089471</v>
+      </c>
       <c r="D6" t="n">
         <v>2.25379e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1877.66</v>
       </c>
+      <c r="C7" t="n">
+        <v>2275.253803494995</v>
+      </c>
       <c r="D7" t="n">
         <v>2.26035e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1860.218</v>
       </c>
+      <c r="C8" t="n">
+        <v>2254.294549483137</v>
+      </c>
       <c r="D8" t="n">
         <v>2.26865e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1834.022</v>
       </c>
+      <c r="C9" t="n">
+        <v>2230.589010788009</v>
+      </c>
       <c r="D9" t="n">
         <v>2.2748e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1810.193</v>
       </c>
+      <c r="C10" t="n">
+        <v>2207.804857701676</v>
+      </c>
       <c r="D10" t="n">
         <v>2.28008e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1780.483</v>
       </c>
+      <c r="C11" t="n">
+        <v>2180.207273851791</v>
+      </c>
       <c r="D11" t="n">
         <v>2.28817e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1764.524</v>
       </c>
+      <c r="C12" t="n">
+        <v>2161.892031143489</v>
+      </c>
       <c r="D12" t="n">
         <v>2.29736e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1727.338</v>
       </c>
+      <c r="C13" t="n">
+        <v>2128.09506461134</v>
+      </c>
       <c r="D13" t="n">
         <v>2.30153e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1702.523</v>
       </c>
+      <c r="C14" t="n">
+        <v>2104.963604955995</v>
+      </c>
       <c r="D14" t="n">
         <v>2.30755e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1682.053</v>
       </c>
+      <c r="C15" t="n">
+        <v>2081.478353537413</v>
+      </c>
       <c r="D15" t="n">
         <v>2.31374e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1670.223</v>
       </c>
+      <c r="C16" t="n">
+        <v>2063.528999927567</v>
+      </c>
       <c r="D16" t="n">
         <v>2.3206e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1644.115</v>
       </c>
+      <c r="C17" t="n">
+        <v>2038.771365814003</v>
+      </c>
       <c r="D17" t="n">
         <v>2.32423e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1620.976</v>
       </c>
+      <c r="C18" t="n">
+        <v>2018.302094046946</v>
+      </c>
       <c r="D18" t="n">
         <v>2.33175e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1600.633</v>
       </c>
+      <c r="C19" t="n">
+        <v>1997.424923941518</v>
+      </c>
       <c r="D19" t="n">
         <v>2.3373e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1579.877</v>
       </c>
+      <c r="C20" t="n">
+        <v>1976.254585424846</v>
+      </c>
       <c r="D20" t="n">
         <v>2.34266e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1560.119</v>
       </c>
+      <c r="C21" t="n">
+        <v>1956.156183135844</v>
+      </c>
       <c r="D21" t="n">
         <v>2.34789e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1543.47</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1939.268179344469</v>
       </c>
       <c r="D22" t="n">
         <v>2.35429e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2174.471</v>
       </c>
+      <c r="C2" t="n">
+        <v>2746.370551224849</v>
+      </c>
       <c r="D2" t="n">
         <v>2.20078e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1764.7</v>
       </c>
+      <c r="C3" t="n">
+        <v>2211.277342287721</v>
+      </c>
       <c r="D3" t="n">
         <v>2.33503e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1671.263</v>
       </c>
+      <c r="C4" t="n">
+        <v>2105.369900384829</v>
+      </c>
       <c r="D4" t="n">
         <v>2.3384e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1625.661</v>
       </c>
+      <c r="C5" t="n">
+        <v>2063.665073347642</v>
+      </c>
       <c r="D5" t="n">
         <v>2.33246e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1597.852</v>
       </c>
+      <c r="C6" t="n">
+        <v>2036.569464982859</v>
+      </c>
       <c r="D6" t="n">
         <v>2.32974e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1564.899</v>
       </c>
+      <c r="C7" t="n">
+        <v>2007.634752078986</v>
+      </c>
       <c r="D7" t="n">
         <v>2.33135e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1538.293</v>
       </c>
+      <c r="C8" t="n">
+        <v>1981.883550846453</v>
+      </c>
       <c r="D8" t="n">
         <v>2.33142e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1513.229</v>
       </c>
+      <c r="C9" t="n">
+        <v>1957.875339325341</v>
+      </c>
       <c r="D9" t="n">
         <v>2.33424e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1488.29</v>
       </c>
+      <c r="C10" t="n">
+        <v>1931.908128396549</v>
+      </c>
       <c r="D10" t="n">
         <v>2.33649e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1459.921</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1904.838983538825</v>
       </c>
       <c r="D11" t="n">
         <v>2.34023e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>2093.148</v>
       </c>
+      <c r="C2" t="n">
+        <v>2515.940406644857</v>
+      </c>
       <c r="D2" t="n">
         <v>2.23371e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1979.778</v>
       </c>
+      <c r="C3" t="n">
+        <v>2375.863230327489</v>
+      </c>
       <c r="D3" t="n">
         <v>2.25922e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1936.725</v>
       </c>
+      <c r="C4" t="n">
+        <v>2331.492527989931</v>
+      </c>
       <c r="D4" t="n">
         <v>2.26895e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1901.838</v>
       </c>
+      <c r="C5" t="n">
+        <v>2298.871472637617</v>
+      </c>
       <c r="D5" t="n">
         <v>2.27855e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1881.244</v>
       </c>
+      <c r="C6" t="n">
+        <v>2276.667711482743</v>
+      </c>
       <c r="D6" t="n">
         <v>2.28716e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1844.162</v>
       </c>
+      <c r="C7" t="n">
+        <v>2243.725055684869</v>
+      </c>
       <c r="D7" t="n">
         <v>2.29535e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1818.872</v>
       </c>
+      <c r="C8" t="n">
+        <v>2216.583886034861</v>
+      </c>
       <c r="D8" t="n">
         <v>2.30346e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1789.279</v>
       </c>
+      <c r="C9" t="n">
+        <v>2190.128150582782</v>
+      </c>
       <c r="D9" t="n">
         <v>2.30949e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1769.016</v>
       </c>
+      <c r="C10" t="n">
+        <v>2170.587094266471</v>
+      </c>
       <c r="D10" t="n">
         <v>2.31837e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1748.982</v>
       </c>
+      <c r="C11" t="n">
+        <v>2148.156413193878</v>
+      </c>
       <c r="D11" t="n">
         <v>2.32653e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1720.424</v>
       </c>
+      <c r="C12" t="n">
+        <v>2121.390133963089</v>
+      </c>
       <c r="D12" t="n">
         <v>2.33275e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1699.803</v>
       </c>
+      <c r="C13" t="n">
+        <v>2100.688082523844</v>
+      </c>
       <c r="D13" t="n">
         <v>2.33855e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1671.467</v>
       </c>
+      <c r="C14" t="n">
+        <v>2075.641439464853</v>
+      </c>
       <c r="D14" t="n">
         <v>2.34328e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1664.904</v>
       </c>
+      <c r="C15" t="n">
+        <v>2063.550554723865</v>
+      </c>
       <c r="D15" t="n">
         <v>2.35094e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1653.147</v>
       </c>
+      <c r="C16" t="n">
+        <v>2047.278849630708</v>
+      </c>
       <c r="D16" t="n">
         <v>2.35864e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1615.759</v>
       </c>
+      <c r="C17" t="n">
+        <v>2014.447022512218</v>
+      </c>
       <c r="D17" t="n">
         <v>2.36385e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1602.056</v>
       </c>
+      <c r="C18" t="n">
+        <v>1998.275824275248</v>
+      </c>
       <c r="D18" t="n">
         <v>2.37029e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1579.637</v>
       </c>
+      <c r="C19" t="n">
+        <v>1978.739129081598</v>
+      </c>
       <c r="D19" t="n">
         <v>2.37695e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1568.663</v>
       </c>
+      <c r="C20" t="n">
+        <v>1963.576844550444</v>
+      </c>
       <c r="D20" t="n">
         <v>2.3828e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1548.828</v>
       </c>
+      <c r="C21" t="n">
+        <v>1944.468956381527</v>
+      </c>
       <c r="D21" t="n">
         <v>2.38759e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1523.119</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1919.076607883001</v>
       </c>
       <c r="D22" t="n">
         <v>2.39541e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>2015.446</v>
       </c>
+      <c r="C2" t="n">
+        <v>2611.852004526477</v>
+      </c>
       <c r="D2" t="n">
         <v>2.2951e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1701.466</v>
       </c>
+      <c r="C3" t="n">
+        <v>2210.101804745281</v>
+      </c>
       <c r="D3" t="n">
         <v>2.3632e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1615.332</v>
       </c>
+      <c r="C4" t="n">
+        <v>2121.439531758354</v>
+      </c>
       <c r="D4" t="n">
         <v>2.35847e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1579.975</v>
       </c>
+      <c r="C5" t="n">
+        <v>2086.473726962341</v>
+      </c>
       <c r="D5" t="n">
         <v>2.35448e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1560.663</v>
       </c>
+      <c r="C6" t="n">
+        <v>2064.59442080263</v>
+      </c>
       <c r="D6" t="n">
         <v>2.35076e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1533.154</v>
       </c>
+      <c r="C7" t="n">
+        <v>2038.106168240529</v>
+      </c>
       <c r="D7" t="n">
         <v>2.35186e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1503.626</v>
       </c>
+      <c r="C8" t="n">
+        <v>2013.147145614282</v>
+      </c>
       <c r="D8" t="n">
         <v>2.35504e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1478.668</v>
       </c>
+      <c r="C9" t="n">
+        <v>1988.305652485264</v>
+      </c>
       <c r="D9" t="n">
         <v>2.35779e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1444.883</v>
       </c>
+      <c r="C10" t="n">
+        <v>1961.110642737502</v>
+      </c>
       <c r="D10" t="n">
         <v>2.36144e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1415.103</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1935.314678258179</v>
       </c>
       <c r="D11" t="n">
         <v>2.36593e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>2087.227</v>
       </c>
+      <c r="C2" t="n">
+        <v>2543.817203678673</v>
+      </c>
       <c r="D2" t="n">
         <v>2.25991e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1975.505</v>
       </c>
+      <c r="C3" t="n">
+        <v>2424.218269333745</v>
+      </c>
       <c r="D3" t="n">
         <v>2.27602e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1936.978</v>
       </c>
+      <c r="C4" t="n">
+        <v>2383.746566833334</v>
+      </c>
       <c r="D4" t="n">
         <v>2.28726e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1906.245</v>
       </c>
+      <c r="C5" t="n">
+        <v>2352.779496355441</v>
+      </c>
       <c r="D5" t="n">
         <v>2.29696e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1875.23</v>
       </c>
+      <c r="C6" t="n">
+        <v>2324.842629658667</v>
+      </c>
       <c r="D6" t="n">
         <v>2.3042e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1848.091</v>
       </c>
+      <c r="C7" t="n">
+        <v>2301.320821955039</v>
+      </c>
       <c r="D7" t="n">
         <v>2.31277e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1824.38</v>
       </c>
+      <c r="C8" t="n">
+        <v>2276.278481123644</v>
+      </c>
       <c r="D8" t="n">
         <v>2.32009e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1807.371</v>
       </c>
+      <c r="C9" t="n">
+        <v>2254.900163859914</v>
+      </c>
       <c r="D9" t="n">
         <v>2.3284e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1783.667</v>
       </c>
+      <c r="C10" t="n">
+        <v>2230.464852046483</v>
+      </c>
       <c r="D10" t="n">
         <v>2.33579e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1757.416</v>
       </c>
+      <c r="C11" t="n">
+        <v>2207.532584711646</v>
+      </c>
       <c r="D11" t="n">
         <v>2.34293e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1725.554</v>
       </c>
+      <c r="C12" t="n">
+        <v>2179.758185047552</v>
+      </c>
       <c r="D12" t="n">
         <v>2.34913e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1701.919</v>
       </c>
+      <c r="C13" t="n">
+        <v>2155.727302247897</v>
+      </c>
       <c r="D13" t="n">
         <v>2.35566e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1666.991</v>
       </c>
+      <c r="C14" t="n">
+        <v>2123.189926248076</v>
+      </c>
       <c r="D14" t="n">
         <v>2.36302e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1663.012</v>
       </c>
+      <c r="C15" t="n">
+        <v>2114.138677286709</v>
+      </c>
       <c r="D15" t="n">
         <v>2.37135e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1639.766</v>
       </c>
+      <c r="C16" t="n">
+        <v>2093.312605265479</v>
+      </c>
       <c r="D16" t="n">
         <v>2.37598e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1601.694</v>
       </c>
+      <c r="C17" t="n">
+        <v>2058.19637927497</v>
+      </c>
       <c r="D17" t="n">
         <v>2.38251e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1590.057</v>
       </c>
+      <c r="C18" t="n">
+        <v>2042.97113161442</v>
+      </c>
       <c r="D18" t="n">
         <v>2.38904e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1565.619</v>
       </c>
+      <c r="C19" t="n">
+        <v>2018.645521873746</v>
+      </c>
       <c r="D19" t="n">
         <v>2.3969e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1542.369</v>
       </c>
+      <c r="C20" t="n">
+        <v>1997.156045658575</v>
+      </c>
       <c r="D20" t="n">
         <v>2.40298e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1512.118</v>
       </c>
+      <c r="C21" t="n">
+        <v>1969.834788910576</v>
+      </c>
       <c r="D21" t="n">
         <v>2.41056e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1499.942</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1952.749785563532</v>
       </c>
       <c r="D22" t="n">
         <v>2.41613e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1564.238</v>
       </c>
+      <c r="C2" t="n">
+        <v>2231.001235191762</v>
+      </c>
       <c r="D2" t="n">
         <v>2.46739e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1311.817</v>
       </c>
+      <c r="C3" t="n">
+        <v>1870.939716622361</v>
+      </c>
       <c r="D3" t="n">
         <v>2.46746e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1257.615</v>
       </c>
+      <c r="C4" t="n">
+        <v>1803.879236726743</v>
+      </c>
       <c r="D4" t="n">
         <v>2.4432e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1224.055</v>
       </c>
+      <c r="C5" t="n">
+        <v>1770.175803951287</v>
+      </c>
       <c r="D5" t="n">
         <v>2.43125e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1206.946</v>
       </c>
+      <c r="C6" t="n">
+        <v>1757.188851511705</v>
+      </c>
       <c r="D6" t="n">
         <v>2.42612e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1168.768</v>
       </c>
+      <c r="C7" t="n">
+        <v>1725.395907457301</v>
+      </c>
       <c r="D7" t="n">
         <v>2.42319e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1137.28</v>
       </c>
+      <c r="C8" t="n">
+        <v>1695.268255780691</v>
+      </c>
       <c r="D8" t="n">
         <v>2.42295e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1119.487</v>
       </c>
+      <c r="C9" t="n">
+        <v>1681.934517010292</v>
+      </c>
       <c r="D9" t="n">
         <v>2.42347e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>1096.526</v>
       </c>
+      <c r="C10" t="n">
+        <v>1660.756306129141</v>
+      </c>
       <c r="D10" t="n">
         <v>2.42372e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>1069.946</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1637.359407804559</v>
       </c>
       <c r="D11" t="n">
         <v>2.42542e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -565,7 +565,7 @@
         <v>1704.605</v>
       </c>
       <c r="C2" t="n">
-        <v>2132.40221344781</v>
+        <v>789.1252385968521</v>
       </c>
       <c r="D2" t="n">
         <v>2.32371e-07</v>
@@ -598,16 +598,13 @@
         <v>-26512.61895166363</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.415310947677803e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2410.448049943559</v>
+        <v>445.8558068598313</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000015e-08</v>
+        <v>9.305628153452265e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8233824879217257</v>
+        <v>0.997857442184127</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>1664.688</v>
       </c>
       <c r="C3" t="n">
-        <v>2089.94350957349</v>
+        <v>756.0294126570678</v>
       </c>
       <c r="D3" t="n">
         <v>2.27875e-07</v>
@@ -651,16 +648,13 @@
         <v>-29617.4678162674</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.011366547673892e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2359.317609741626</v>
+        <v>479.3287317735911</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000215e-08</v>
+        <v>1.072705889248211e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8233904233678926</v>
+        <v>0.9932243755241711</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>1630.645</v>
       </c>
       <c r="C4" t="n">
-        <v>2056.53487820432</v>
+        <v>739.5199470886137</v>
       </c>
       <c r="D4" t="n">
         <v>2.26419e-07</v>
@@ -704,16 +698,13 @@
         <v>-29107.97135255189</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.104590956173844e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2320.892027456387</v>
+        <v>484.8569712414229</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000011e-08</v>
+        <v>1.344663222313636e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8234056046303073</v>
+        <v>0.987679620304783</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>1600.033</v>
       </c>
       <c r="C5" t="n">
-        <v>2029.228445631155</v>
+        <v>728.0508909908334</v>
       </c>
       <c r="D5" t="n">
         <v>2.25594e-07</v>
@@ -757,16 +748,13 @@
         <v>-29473.00660329694</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.913578887301948e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2285.819968891027</v>
+        <v>484.247810062435</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000264e-08</v>
+        <v>1.066787413913173e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8235052362770372</v>
+        <v>0.9972806196486792</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>1564.504</v>
       </c>
       <c r="C6" t="n">
-        <v>1995.841836387625</v>
+        <v>716.2659646306292</v>
       </c>
       <c r="D6" t="n">
         <v>2.25026e-07</v>
@@ -810,16 +798,13 @@
         <v>-27455.43201969614</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.633778004024203e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2250.227692224049</v>
+        <v>504.798533540522</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000649e-08</v>
+        <v>1.77812386336561e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8236709883754649</v>
+        <v>0.9701983675496586</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1535.392</v>
       </c>
       <c r="C7" t="n">
-        <v>1970.084291695183</v>
+        <v>705.6292105510699</v>
       </c>
       <c r="D7" t="n">
         <v>2.24808e-07</v>
@@ -863,16 +848,13 @@
         <v>-26980.66251654135</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.302073442772051e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2215.639602243329</v>
+        <v>496.2933266672862</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000001893e-08</v>
+        <v>1.190992076474819e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8238878356306352</v>
+        <v>0.9952307149406624</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1501.556</v>
       </c>
       <c r="C8" t="n">
-        <v>1939.412165457162</v>
+        <v>696.1097815275585</v>
       </c>
       <c r="D8" t="n">
         <v>2.24698e-07</v>
@@ -916,16 +898,13 @@
         <v>-25375.11933162333</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.84599431062659e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2181.660894811766</v>
+        <v>499.6614562844672</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000093e-08</v>
+        <v>1.2128191952503e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8241075674849676</v>
+        <v>0.9973295883792194</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1480.783</v>
       </c>
       <c r="C9" t="n">
-        <v>1917.042172816891</v>
+        <v>686.4164863939033</v>
       </c>
       <c r="D9" t="n">
         <v>2.2455e-07</v>
@@ -969,16 +948,13 @@
         <v>-26702.59540322645</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.606193303780935e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2149.985626840088</v>
+        <v>495.7877803681088</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000253e-08</v>
+        <v>1.633939464715082e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8243225855446978</v>
+        <v>0.9775575997059598</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1458.165</v>
       </c>
       <c r="C10" t="n">
-        <v>1894.39898490107</v>
+        <v>682.4210613793318</v>
       </c>
       <c r="D10" t="n">
         <v>2.24504e-07</v>
@@ -1022,16 +998,13 @@
         <v>-25554.5036609288</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.715284651378623e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2119.966405870303</v>
+        <v>502.7087036473146</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000007374e-08</v>
+        <v>1.933455712162743e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8245325174446646</v>
+        <v>0.966792506372087</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1430.516</v>
       </c>
       <c r="C11" t="n">
-        <v>1869.990451315093</v>
+        <v>675.6410316924089</v>
       </c>
       <c r="D11" t="n">
         <v>2.24506e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-24703.07649563891</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.079048882999982e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2091.506950994974</v>
+        <v>493.569802718981</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000531e-08</v>
+        <v>1.526695858989799e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8247652552925044</v>
+        <v>0.9847643269176476</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>2055.975</v>
       </c>
       <c r="C2" t="n">
-        <v>2464.362302602164</v>
+        <v>901.9981249622977</v>
       </c>
       <c r="D2" t="n">
         <v>2.19786e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-30660.02153502501</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.075396332685376e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2757.57009933029</v>
+        <v>424.5504241356394</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000562e-08</v>
+        <v>1.314771593013144e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8239737920711422</v>
+        <v>0.9689433543790382</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1927.415</v>
       </c>
       <c r="C3" t="n">
-        <v>2312.166020913373</v>
+        <v>851.1772858526269</v>
       </c>
       <c r="D3" t="n">
         <v>2.23489e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-28099.15557419353</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.180535016618823e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2628.895283461112</v>
+        <v>431.8255419430795</v>
       </c>
       <c r="AA3" t="n">
-        <v>1e-08</v>
+        <v>9.586200871577991e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8243521382922012</v>
+        <v>0.996649466252913</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1883.881</v>
       </c>
       <c r="C4" t="n">
-        <v>2267.754455344852</v>
+        <v>834.7982885734758</v>
       </c>
       <c r="D4" t="n">
         <v>2.24766e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-27112.95277324877</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.034578536778927e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2583.028355356804</v>
+        <v>418.3580900956671</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000002802e-08</v>
+        <v>1.049174484287314e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8244304712573326</v>
+        <v>0.9929301796297062</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1846.941</v>
       </c>
       <c r="C5" t="n">
-        <v>2234.567278635461</v>
+        <v>822.2365755781736</v>
       </c>
       <c r="D5" t="n">
         <v>2.2551e-07</v>
@@ -1433,16 +1394,13 @@
         <v>-25225.26241618456</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.736386840969188e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2549.26393814946</v>
+        <v>455.4192230577498</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001974e-08</v>
+        <v>1.295011426033876e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8245172483092832</v>
+        <v>0.9799967491234716</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1811.258</v>
       </c>
       <c r="C6" t="n">
-        <v>2204.697825785984</v>
+        <v>809.7540274873982</v>
       </c>
       <c r="D6" t="n">
         <v>2.26554e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-23117.85400731676</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.734692249110454e-13</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2517.318306344748</v>
+        <v>453.7747845226124</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.020826025692316e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8246550093241634</v>
+        <v>0.9991607568008143</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1801.913</v>
       </c>
       <c r="C7" t="n">
-        <v>2187.15772088575</v>
+        <v>798.1387260316864</v>
       </c>
       <c r="D7" t="n">
         <v>2.2703e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-24527.17234841071</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.441533647954122e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2485.543471191366</v>
+        <v>428.493975503777</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>9.693415734132599e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8248736551774272</v>
+        <v>0.9998510353796511</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1774.466</v>
       </c>
       <c r="C8" t="n">
-        <v>2161.934230160967</v>
+        <v>787.7001203500962</v>
       </c>
       <c r="D8" t="n">
         <v>2.2791e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-22627.33967337245</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.033304018910433e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2453.951101126005</v>
+        <v>454.1073009039566</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>9.470292033505606e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8251194166917888</v>
+        <v>0.996565038853495</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1735.871</v>
       </c>
       <c r="C9" t="n">
-        <v>2128.891783010265</v>
+        <v>777.2760407970519</v>
       </c>
       <c r="D9" t="n">
         <v>2.2848e-07</v>
@@ -1645,16 +1594,13 @@
         <v>-20780.16045926497</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.948437754477155e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2424.035502175891</v>
+        <v>458.4460023873259</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000309e-08</v>
+        <v>1.02033670884322e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8254046977366076</v>
+        <v>0.9990211815598836</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1721.034</v>
       </c>
       <c r="C10" t="n">
-        <v>2109.505464133086</v>
+        <v>769.8513560515462</v>
       </c>
       <c r="D10" t="n">
         <v>2.29191e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-20449.78197501574</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.254071109854306e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2395.761097073741</v>
+        <v>453.991091468356</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.168423796309702e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8256932436551032</v>
+        <v>0.988393602869659</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1694.981</v>
       </c>
       <c r="C11" t="n">
-        <v>2084.471351487034</v>
+        <v>763.566838729862</v>
       </c>
       <c r="D11" t="n">
         <v>2.29819e-07</v>
@@ -1751,16 +1694,13 @@
         <v>-18462.85703754847</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.263430458204318e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2368.05908293269</v>
+        <v>447.1133734917667</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.050592409254854e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.826008644242491</v>
+        <v>0.9985282621969197</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1671.581</v>
       </c>
       <c r="C12" t="n">
-        <v>2063.069266985512</v>
+        <v>754.3565104195676</v>
       </c>
       <c r="D12" t="n">
         <v>2.30304e-07</v>
@@ -1804,16 +1744,13 @@
         <v>-18355.64765139138</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.464301324947811e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2340.665388963708</v>
+        <v>451.6332028261887</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000083176e-08</v>
+        <v>9.853892388865768e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8263375904205432</v>
+        <v>0.999535894457263</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1658.271</v>
       </c>
       <c r="C13" t="n">
-        <v>2045.204912796311</v>
+        <v>745.9514693912604</v>
       </c>
       <c r="D13" t="n">
         <v>2.30797e-07</v>
@@ -1857,16 +1794,13 @@
         <v>-17156.13490481778</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.631307393981735e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2313.782422428646</v>
+        <v>436.6050317852157</v>
       </c>
       <c r="AA13" t="n">
-        <v>1e-08</v>
+        <v>9.844266406729888e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8266969867697139</v>
+        <v>0.9995196710991068</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1811,7 @@
         <v>1636.18</v>
       </c>
       <c r="C14" t="n">
-        <v>2025.62557218841</v>
+        <v>736.916117763445</v>
       </c>
       <c r="D14" t="n">
         <v>2.31384e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-16227.32390932036</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.706458700410186e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2286.936405802662</v>
+        <v>453.5561140536855</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>1.138868719174058e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8270545364460221</v>
+        <v>0.9988334318927955</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1615.278</v>
       </c>
       <c r="C15" t="n">
-        <v>2005.04681749927</v>
+        <v>727.8837533856138</v>
       </c>
       <c r="D15" t="n">
         <v>2.32064e-07</v>
@@ -1963,16 +1894,13 @@
         <v>-14059.64894322642</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.203271988021492e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2260.62424563863</v>
+        <v>440.0454902966474</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000003576e-08</v>
+        <v>1.009586013580901e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.827436630697757</v>
+        <v>0.9984524713630711</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1595.891</v>
       </c>
       <c r="C16" t="n">
-        <v>1984.791937663044</v>
+        <v>720.5244778241429</v>
       </c>
       <c r="D16" t="n">
         <v>2.32462e-07</v>
@@ -2016,16 +1944,13 @@
         <v>-13177.04396881474</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.890564578953269e-12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2234.884909838563</v>
+        <v>436.6520336301237</v>
       </c>
       <c r="AA16" t="n">
-        <v>1e-08</v>
+        <v>1.035580898405363e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8278227955550146</v>
+        <v>0.9986929079816208</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1571.486</v>
       </c>
       <c r="C17" t="n">
-        <v>1960.865054227795</v>
+        <v>713.2363358930988</v>
       </c>
       <c r="D17" t="n">
         <v>2.33055e-07</v>
@@ -2069,16 +1994,13 @@
         <v>-12692.44696356226</v>
       </c>
       <c r="Y17" t="n">
-        <v>212.4812723188523</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2223.75627310775</v>
+        <v>435.9305201094611</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.380833949190603e-08</v>
+        <v>1.027517524687013e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8209815868380305</v>
+        <v>0.9984765659273631</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1549.121</v>
       </c>
       <c r="C18" t="n">
-        <v>1940.411146607287</v>
+        <v>705.118353250703</v>
       </c>
       <c r="D18" t="n">
         <v>2.33788e-07</v>
@@ -2122,16 +2044,13 @@
         <v>-11148.92228587478</v>
       </c>
       <c r="Y18" t="n">
-        <v>206.861668179744</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2197.477832755963</v>
+        <v>442.8025497071019</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.40792039562032e-08</v>
+        <v>1.40973773865807e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8195633697059974</v>
+        <v>0.9831968826506552</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1529.287</v>
       </c>
       <c r="C19" t="n">
-        <v>1922.044859602127</v>
+        <v>695.2104667373521</v>
       </c>
       <c r="D19" t="n">
         <v>2.34189e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-10532.81262975529</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.47998912098377e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2156.5440610064</v>
+        <v>424.3557198567456</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000101e-08</v>
+        <v>9.810419016208845e-10</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8290581426232366</v>
+        <v>0.9996971261784489</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1508.896</v>
       </c>
       <c r="C20" t="n">
-        <v>1900.421201499156</v>
+        <v>688.5318642635903</v>
       </c>
       <c r="D20" t="n">
         <v>2.34684e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-9469.764652776803</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.072714896296982e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2130.146285283991</v>
+        <v>510.0761609992887</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>4.540673231350383e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8294699482796445</v>
+        <v>0.9122303636219534</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1493.872</v>
       </c>
       <c r="C21" t="n">
-        <v>1881.369059089088</v>
+        <v>680.3132896289363</v>
       </c>
       <c r="D21" t="n">
         <v>2.35226e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-6233.095012111938</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.966431116877329e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2103.727843958342</v>
+        <v>500.8965019650021</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000169e-08</v>
+        <v>4.51120912486177e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8298965896031515</v>
+        <v>0.9135189666461168</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1460.396</v>
       </c>
       <c r="C22" t="n">
-        <v>1856.486926945022</v>
+        <v>673.2088055432091</v>
       </c>
       <c r="D22" t="n">
         <v>2.35769e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-6862.051675706942</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.614793725905983e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2078.340268613085</v>
+        <v>447.434119429976</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>1.525646545620131e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8303157667479026</v>
+        <v>0.9857536259248709</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>2177.713</v>
       </c>
       <c r="C2" t="n">
-        <v>2590.566926474108</v>
+        <v>979.7602952489356</v>
       </c>
       <c r="D2" t="n">
         <v>2.11868e-07</v>
@@ -2533,16 +2440,13 @@
         <v>-32182.28269469809</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.59442307260886e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2915.954589926854</v>
+        <v>386.0834879747979</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000087e-08</v>
+        <v>8.658466211977026e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8220981973325222</v>
+        <v>0.9852009834053987</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>2055.358</v>
       </c>
       <c r="C3" t="n">
-        <v>2447.848489300685</v>
+        <v>919.4646961956995</v>
       </c>
       <c r="D3" t="n">
         <v>2.14598e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-30102.17944132951</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.117241225930757e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2809.082698967638</v>
+        <v>425.0744719122259</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000192e-08</v>
+        <v>8.43489758527719e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.822087465869785</v>
+        <v>0.9971774183174581</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>2036.184</v>
       </c>
       <c r="C4" t="n">
-        <v>2424.721380474324</v>
+        <v>904.1658315095563</v>
       </c>
       <c r="D4" t="n">
         <v>2.14944e-07</v>
@@ -2639,16 +2540,13 @@
         <v>-31151.40379032491</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.825737732110178e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2779.103494459513</v>
+        <v>434.160173398929</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000637e-08</v>
+        <v>8.849015622705693e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8219147326852899</v>
+        <v>0.999126367578377</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>2002.642</v>
       </c>
       <c r="C5" t="n">
-        <v>2399.42252309301</v>
+        <v>893.66136611088</v>
       </c>
       <c r="D5" t="n">
         <v>2.15305e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-28949.67655070433</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.137282678068201e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2752.227983503276</v>
+        <v>457.3978352784607</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.181787932576081e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8219250745537761</v>
+        <v>0.9705595357409182</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1990.091</v>
       </c>
       <c r="C6" t="n">
-        <v>2381.53282050074</v>
+        <v>881.9954001395161</v>
       </c>
       <c r="D6" t="n">
         <v>2.15907e-07</v>
@@ -2745,16 +2640,13 @@
         <v>-29241.17998515358</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.034390778127763e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2723.276059701413</v>
+        <v>448.1409515866558</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.017269272194978e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8220989419735825</v>
+        <v>0.9896756527320006</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1957.682</v>
       </c>
       <c r="C7" t="n">
-        <v>2351.783040028789</v>
+        <v>870.3205447758146</v>
       </c>
       <c r="D7" t="n">
         <v>2.16352e-07</v>
@@ -2798,16 +2690,13 @@
         <v>-27379.5874050473</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.519918255122773e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2690.199763488245</v>
+        <v>512.4291449367422</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.00000000000006e-08</v>
+        <v>2.465092443567091e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8223384124082387</v>
+        <v>0.9377978274393122</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1928.249</v>
       </c>
       <c r="C8" t="n">
-        <v>2323.483460609316</v>
+        <v>856.4036317743705</v>
       </c>
       <c r="D8" t="n">
         <v>2.17234e-07</v>
@@ -2851,16 +2740,13 @@
         <v>-26427.70560616207</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.342906300109985e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2655.487400575091</v>
+        <v>452.5342663223117</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000878e-08</v>
+        <v>8.99561287367817e-10</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8225911753494387</v>
+        <v>0.9929033483911823</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1902.033</v>
       </c>
       <c r="C9" t="n">
-        <v>2297.520941038831</v>
+        <v>844.7130429426649</v>
       </c>
       <c r="D9" t="n">
         <v>2.17781e-07</v>
@@ -2904,16 +2790,13 @@
         <v>-25369.22255346926</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.939495515668526e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2623.329471766109</v>
+        <v>451.3212669283607</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000696e-08</v>
+        <v>9.225821065985022e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.822851788607222</v>
+        <v>0.9999421621623661</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1876.253</v>
       </c>
       <c r="C10" t="n">
-        <v>2273.173556443919</v>
+        <v>834.4585920275235</v>
       </c>
       <c r="D10" t="n">
         <v>2.18538e-07</v>
@@ -2957,16 +2840,13 @@
         <v>-24202.13855168521</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.706620553159562e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2592.348915597973</v>
+        <v>448.1400097451416</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000002331e-08</v>
+        <v>9.508659163224527e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8230841242048756</v>
+        <v>0.9970940362729055</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2857,7 @@
         <v>1843.411</v>
       </c>
       <c r="C11" t="n">
-        <v>2245.030435716978</v>
+        <v>823.030754673843</v>
       </c>
       <c r="D11" t="n">
         <v>2.1917e-07</v>
@@ -3010,16 +2890,13 @@
         <v>-22687.21857963646</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.127431609741145e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2563.02284458603</v>
+        <v>450.6398296865987</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000386e-08</v>
+        <v>9.148108055149389e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8233149760934312</v>
+        <v>0.9987196841226386</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2907,7 @@
         <v>1821.224</v>
       </c>
       <c r="C12" t="n">
-        <v>2221.18190126284</v>
+        <v>812.8324644352683</v>
       </c>
       <c r="D12" t="n">
         <v>2.19756e-07</v>
@@ -3063,16 +2940,13 @@
         <v>-20732.16588551441</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.859345571410595e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2534.730011262545</v>
+        <v>465.2811124481253</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000299e-08</v>
+        <v>9.7795068569388e-10</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8235502638891337</v>
+        <v>0.9969578823115164</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2957,7 @@
         <v>1803.778</v>
       </c>
       <c r="C13" t="n">
-        <v>2203.865396376778</v>
+        <v>802.4543478722625</v>
       </c>
       <c r="D13" t="n">
         <v>2.20377e-07</v>
@@ -3116,16 +2990,13 @@
         <v>-21023.29645173243</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.239488607329279e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2507.234636243908</v>
+        <v>462.1504214175474</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000076e-08</v>
+        <v>9.336101242216899e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8238066182788678</v>
+        <v>0.9965278581603036</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3007,7 @@
         <v>1783.416</v>
       </c>
       <c r="C14" t="n">
-        <v>2180.758326327946</v>
+        <v>793.1268482122269</v>
       </c>
       <c r="D14" t="n">
         <v>2.20764e-07</v>
@@ -3169,16 +3040,13 @@
         <v>-20322.20238838419</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.359231651318668e-11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2480.629410918885</v>
+        <v>464.5504525600144</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>1.015827687775982e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8240655230017409</v>
+        <v>0.9966521359667809</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3057,7 @@
         <v>1761.645</v>
       </c>
       <c r="C15" t="n">
-        <v>2160.958520287356</v>
+        <v>784.1779912943689</v>
       </c>
       <c r="D15" t="n">
         <v>2.2129e-07</v>
@@ -3222,16 +3090,13 @@
         <v>-19518.57299755024</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.973967348233778e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2454.630797555196</v>
+        <v>467.7895670355546</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000107e-08</v>
+        <v>1.018157412626924e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8243369069067397</v>
+        <v>0.9976962260567748</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1742.101</v>
       </c>
       <c r="C16" t="n">
-        <v>2139.606425454234</v>
+        <v>775.6054393869753</v>
       </c>
       <c r="D16" t="n">
         <v>2.21886e-07</v>
@@ -3275,16 +3140,13 @@
         <v>-18859.62323868267</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.45003817486749e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2428.185404745177</v>
+        <v>461.7486418451144</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000084e-08</v>
+        <v>1.138783180371006e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8246493687092759</v>
+        <v>0.9981287030891625</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3157,7 @@
         <v>1721.975</v>
       </c>
       <c r="C17" t="n">
-        <v>2120.111114023082</v>
+        <v>767.1557055495909</v>
       </c>
       <c r="D17" t="n">
         <v>2.22354e-07</v>
@@ -3328,16 +3190,13 @@
         <v>-16703.09046365776</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.970517935624754e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2401.983530257716</v>
+        <v>451.3879289905367</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.004219405511296e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8249770548153392</v>
+        <v>0.9990873555331395</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3207,7 @@
         <v>1697.583</v>
       </c>
       <c r="C18" t="n">
-        <v>2092.77134814449</v>
+        <v>760.9696752845321</v>
       </c>
       <c r="D18" t="n">
         <v>2.22879e-07</v>
@@ -3381,16 +3240,13 @@
         <v>-15828.72167675995</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.627140714989261e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2375.280445590422</v>
+        <v>454.2643399989161</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000782e-08</v>
+        <v>1.006312876161724e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8253435196826101</v>
+        <v>0.9974513620454353</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3257,7 @@
         <v>1677.044</v>
       </c>
       <c r="C19" t="n">
-        <v>2072.035920391601</v>
+        <v>754.280145776136</v>
       </c>
       <c r="D19" t="n">
         <v>2.2336e-07</v>
@@ -3434,16 +3290,13 @@
         <v>-14100.43427184204</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.29289101531848e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2347.508273255232</v>
+        <v>445.1760648726865</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>1.002467605953772e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8257276008085358</v>
+        <v>0.9988664677543952</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3307,7 @@
         <v>1657.118</v>
       </c>
       <c r="C20" t="n">
-        <v>2051.082658491603</v>
+        <v>746.2956418055076</v>
       </c>
       <c r="D20" t="n">
         <v>2.23833e-07</v>
@@ -3487,16 +3340,13 @@
         <v>-13842.07640576425</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.075119883901549e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2320.071994721753</v>
+        <v>443.076820304161</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000034e-08</v>
+        <v>1.026045027687463e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8261241899379637</v>
+        <v>0.9989928096147006</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3357,7 @@
         <v>1632.993</v>
       </c>
       <c r="C21" t="n">
-        <v>2028.587618601337</v>
+        <v>737.478730262087</v>
       </c>
       <c r="D21" t="n">
         <v>2.24414e-07</v>
@@ -3540,16 +3390,13 @@
         <v>-12814.5406608731</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.777177309290668e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2292.691756936614</v>
+        <v>453.0766557874038</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.333143240629861e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8265312128622175</v>
+        <v>0.9839628715227235</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3407,7 @@
         <v>1611.377</v>
       </c>
       <c r="C22" t="n">
-        <v>2008.274370449835</v>
+        <v>728.251634441539</v>
       </c>
       <c r="D22" t="n">
         <v>2.24924e-07</v>
@@ -3593,16 +3440,13 @@
         <v>-9880.899672481139</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.319115630141283e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2264.958903157273</v>
+        <v>457.0162044853968</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000029683e-08</v>
+        <v>1.120745367705978e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8269492738709937</v>
+        <v>0.9935021454987638</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3603,7 @@
         <v>2030.383</v>
       </c>
       <c r="C2" t="n">
-        <v>2511.088117554245</v>
+        <v>17362.85105348138</v>
       </c>
       <c r="D2" t="n">
         <v>2.22095e-07</v>
@@ -3792,10 +3636,7 @@
         <v>-23184.55585740781</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.175791473510778e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2713.895048948965</v>
+        <v>-14251.19946194258</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000011e-08</v>
@@ -3812,7 +3653,7 @@
         <v>1768.114</v>
       </c>
       <c r="C3" t="n">
-        <v>2195.803911888395</v>
+        <v>806.8001114870414</v>
       </c>
       <c r="D3" t="n">
         <v>2.29232e-07</v>
@@ -3845,16 +3686,13 @@
         <v>-29079.41320062482</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.613124622069379e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2462.955700602321</v>
+        <v>442.9464821104301</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000027034e-08</v>
+        <v>9.32922079112914e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8231340282117653</v>
+        <v>0.997038388138087</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>1691.148</v>
       </c>
       <c r="C4" t="n">
-        <v>2111.631978097801</v>
+        <v>771.6718745891676</v>
       </c>
       <c r="D4" t="n">
         <v>2.28638e-07</v>
@@ -3898,16 +3736,13 @@
         <v>-29117.09723860739</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.866575263797109e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2391.660990471461</v>
+        <v>456.0167851746235</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>9.376297321941717e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.823235943927017</v>
+        <v>0.9994877575407074</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3753,7 @@
         <v>1663.227</v>
       </c>
       <c r="C5" t="n">
-        <v>2083.728059385726</v>
+        <v>752.8929458684177</v>
       </c>
       <c r="D5" t="n">
         <v>2.27723e-07</v>
@@ -3951,16 +3786,13 @@
         <v>-31187.05100397402</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.252834411476645e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2350.065362473626</v>
+        <v>485.3013861453782</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>1.062796405345876e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8232282947826255</v>
+        <v>0.9979401153157476</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3803,7 @@
         <v>1622.174</v>
       </c>
       <c r="C6" t="n">
-        <v>2049.576417678078</v>
+        <v>739.3239163011802</v>
       </c>
       <c r="D6" t="n">
         <v>2.27069e-07</v>
@@ -4004,16 +3836,13 @@
         <v>-29621.55290490708</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.230498828401794e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2314.022769149911</v>
+        <v>493.9521200654434</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000214e-08</v>
+        <v>1.074081856723682e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8233952573463059</v>
+        <v>0.9986398407749556</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1587.455</v>
       </c>
       <c r="C7" t="n">
-        <v>2016.248796425973</v>
+        <v>726.2729682150415</v>
       </c>
       <c r="D7" t="n">
         <v>2.26984e-07</v>
@@ -4057,16 +3886,13 @@
         <v>-27432.60076755711</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.075233288206583e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2278.892645829634</v>
+        <v>483.3013281793037</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000017374e-08</v>
+        <v>1.060227865913488e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8235924097749807</v>
+        <v>0.9973560292061521</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1563.381</v>
       </c>
       <c r="C8" t="n">
-        <v>1993.540739103445</v>
+        <v>714.9346009832803</v>
       </c>
       <c r="D8" t="n">
         <v>2.26812e-07</v>
@@ -4110,16 +3936,13 @@
         <v>-29333.3200110806</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.655333856793304e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2243.353996478384</v>
+        <v>504.197291480174</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.222597985837605e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8238469270957746</v>
+        <v>0.9920653221256941</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1529.002</v>
       </c>
       <c r="C9" t="n">
-        <v>1960.827062704892</v>
+        <v>704.1475640962292</v>
       </c>
       <c r="D9" t="n">
         <v>2.26852e-07</v>
@@ -4163,16 +3986,13 @@
         <v>-27820.63681942162</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.270528794341422e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2208.580200814447</v>
+        <v>498.3276456285006</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000022e-08</v>
+        <v>1.732890930687819e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8241363452360965</v>
+        <v>0.9722814106574545</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1506.849</v>
       </c>
       <c r="C10" t="n">
-        <v>1939.734527749967</v>
+        <v>694.5658520145498</v>
       </c>
       <c r="D10" t="n">
         <v>2.26951e-07</v>
@@ -4216,16 +4036,13 @@
         <v>-29172.18338027941</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.592247695071056e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2175.345500587092</v>
+        <v>485.4068794195424</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000348e-08</v>
+        <v>1.100399554553836e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8244195535222555</v>
+        <v>0.9993879852696712</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1487.658</v>
       </c>
       <c r="C11" t="n">
-        <v>1915.523207960869</v>
+        <v>690.4731916866268</v>
       </c>
       <c r="D11" t="n">
         <v>2.27246e-07</v>
@@ -4269,16 +4086,13 @@
         <v>-28947.25785771579</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.279332546116162e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2144.019452580205</v>
+        <v>492.9974995703274</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000015e-08</v>
+        <v>1.29903999789776e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8247099040408369</v>
+        <v>0.988877949036323</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4249,7 @@
         <v>2113.896</v>
       </c>
       <c r="C2" t="n">
-        <v>2527.27840907594</v>
+        <v>966.9705208146013</v>
       </c>
       <c r="D2" t="n">
         <v>2.2132e-07</v>
@@ -4468,16 +4282,13 @@
         <v>-29342.81972963851</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.129234063954383e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2845.948042091551</v>
+        <v>375.980311265705</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.00000000000011e-08</v>
+        <v>7.559056038214564e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8222241979160136</v>
+        <v>0.9923626055981772</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>1995.458</v>
       </c>
       <c r="C3" t="n">
-        <v>2392.915050861463</v>
+        <v>893.2060209788295</v>
       </c>
       <c r="D3" t="n">
         <v>2.23485e-07</v>
@@ -4521,16 +4332,13 @@
         <v>-29607.45348988348</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.320284713375369e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2736.327374494666</v>
+        <v>433.6641506948944</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000001217e-08</v>
+        <v>8.817223622248883e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8223748627702101</v>
+        <v>0.9955274830176691</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4349,7 @@
         <v>1967.076</v>
       </c>
       <c r="C4" t="n">
-        <v>2358.93003281647</v>
+        <v>873.7969392320451</v>
       </c>
       <c r="D4" t="n">
         <v>2.23952e-07</v>
@@ -4574,16 +4382,13 @@
         <v>-30951.44415194967</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.500191835565047e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2694.955799695584</v>
+        <v>438.4294153062677</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001151e-08</v>
+        <v>9.007586319374736e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8223615677257196</v>
+        <v>0.9985398105653699</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1929.858</v>
       </c>
       <c r="C5" t="n">
-        <v>2326.086936584482</v>
+        <v>860.1917070424038</v>
       </c>
       <c r="D5" t="n">
         <v>2.24564e-07</v>
@@ -4627,16 +4432,13 @@
         <v>-27757.30246292592</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.607539098225247e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2662.460103949847</v>
+        <v>451.6452585115562</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.87398163954675e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8223624909571154</v>
+        <v>0.9887487947735597</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1910.006</v>
       </c>
       <c r="C6" t="n">
-        <v>2304.523567089471</v>
+        <v>847.723438791074</v>
       </c>
       <c r="D6" t="n">
         <v>2.25379e-07</v>
@@ -4680,16 +4482,13 @@
         <v>-28307.20923820126</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.87015092989737e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2629.468457631028</v>
+        <v>449.3333419221836</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000023e-08</v>
+        <v>9.483304132962818e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8225151409289783</v>
+        <v>0.99531669237597</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4499,7 @@
         <v>1877.66</v>
       </c>
       <c r="C7" t="n">
-        <v>2275.253803494995</v>
+        <v>836.7899914400522</v>
       </c>
       <c r="D7" t="n">
         <v>2.26035e-07</v>
@@ -4733,16 +4532,13 @@
         <v>-26260.51963328112</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.249466642569781e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2597.564665233623</v>
+        <v>453.1418851225816</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000504e-08</v>
+        <v>9.617355918731906e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8226875476927562</v>
+        <v>0.9958386712658956</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1860.218</v>
       </c>
       <c r="C8" t="n">
-        <v>2254.294549483137</v>
+        <v>824.9764006634524</v>
       </c>
       <c r="D8" t="n">
         <v>2.26865e-07</v>
@@ -4786,16 +4582,13 @@
         <v>-27001.91315188662</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.515287388830445e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2567.732605236057</v>
+        <v>469.6494869946612</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000019e-08</v>
+        <v>1.501100649341874e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8228613277627862</v>
+        <v>0.9740684678645571</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1834.022</v>
       </c>
       <c r="C9" t="n">
-        <v>2230.589010788009</v>
+        <v>814.2263419956711</v>
       </c>
       <c r="D9" t="n">
         <v>2.2748e-07</v>
@@ -4839,16 +4632,13 @@
         <v>-26231.71028594182</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.014359159496607e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2537.481018250261</v>
+        <v>459.804393285795</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>9.554903063966667e-10</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8230824662655123</v>
+        <v>0.997788139272071</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1810.193</v>
       </c>
       <c r="C10" t="n">
-        <v>2207.804857701676</v>
+        <v>804.1916521744764</v>
       </c>
       <c r="D10" t="n">
         <v>2.28008e-07</v>
@@ -4892,16 +4682,13 @@
         <v>-25330.30802200493</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11453348004922e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2508.488900648735</v>
+        <v>466.3518409611533</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000142e-08</v>
+        <v>1.134260635466478e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8233193736138535</v>
+        <v>0.9870268072198131</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1780.483</v>
       </c>
       <c r="C11" t="n">
-        <v>2180.207273851791</v>
+        <v>793.8707965174109</v>
       </c>
       <c r="D11" t="n">
         <v>2.28817e-07</v>
@@ -4945,16 +4732,13 @@
         <v>-23485.12470902395</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.147155854151793e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2479.048500598249</v>
+        <v>470.7324780477792</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000017e-08</v>
+        <v>1.316163652668913e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8236209212926803</v>
+        <v>0.9838175614583587</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4749,7 @@
         <v>1764.524</v>
       </c>
       <c r="C12" t="n">
-        <v>2161.892031143489</v>
+        <v>783.5230974416256</v>
       </c>
       <c r="D12" t="n">
         <v>2.29736e-07</v>
@@ -4998,16 +4782,13 @@
         <v>-23048.36933268379</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.515346933716058e-11</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2449.680458364413</v>
+        <v>461.8670387259208</v>
       </c>
       <c r="AA12" t="n">
-        <v>1e-08</v>
+        <v>1.009399762362299e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8239501520027088</v>
+        <v>0.9971263773023272</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4799,7 @@
         <v>1727.338</v>
       </c>
       <c r="C13" t="n">
-        <v>2128.09506461134</v>
+        <v>773.6545599930472</v>
       </c>
       <c r="D13" t="n">
         <v>2.30153e-07</v>
@@ -5051,16 +4832,13 @@
         <v>-19862.95549832066</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.229944194588911e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2419.819317598993</v>
+        <v>460.3072373587686</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000196e-08</v>
+        <v>1.003131309393028e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8243123698056691</v>
+        <v>0.9973592854293034</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4849,7 @@
         <v>1702.523</v>
       </c>
       <c r="C14" t="n">
-        <v>2104.963604955995</v>
+        <v>763.8660475719878</v>
       </c>
       <c r="D14" t="n">
         <v>2.30755e-07</v>
@@ -5104,16 +4882,13 @@
         <v>-18460.8542965073</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.89318947762486e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2391.138214515793</v>
+        <v>459.8788185665593</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000123e-08</v>
+        <v>9.728437689720031e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8246902588566679</v>
+        <v>0.9995904073779859</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4899,7 @@
         <v>1682.053</v>
       </c>
       <c r="C15" t="n">
-        <v>2081.478353537413</v>
+        <v>754.8752049303515</v>
       </c>
       <c r="D15" t="n">
         <v>2.31374e-07</v>
@@ -5157,16 +4932,13 @@
         <v>-17913.34268513276</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.788585878560492e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2362.419624778477</v>
+        <v>458.3615727051573</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.01161725375498e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.825081230583431</v>
+        <v>0.9978185791857291</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1670.223</v>
       </c>
       <c r="C16" t="n">
-        <v>2063.528999927567</v>
+        <v>750.3240927355178</v>
       </c>
       <c r="D16" t="n">
         <v>2.3206e-07</v>
@@ -5210,16 +4982,13 @@
         <v>-17384.61005729551</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.555286651214082e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2334.801746610437</v>
+        <v>444.922745925849</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000007969e-08</v>
+        <v>1.04597281800303e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8254671928352076</v>
+        <v>0.9997479369251979</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +4999,7 @@
         <v>1644.115</v>
       </c>
       <c r="C17" t="n">
-        <v>2038.771365814003</v>
+        <v>742.2838329757932</v>
       </c>
       <c r="D17" t="n">
         <v>2.32423e-07</v>
@@ -5263,16 +5032,13 @@
         <v>-16647.10093931793</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.797281210055078e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2307.80205912893</v>
+        <v>456.7771860265002</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000512e-08</v>
+        <v>1.34043693779613e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8258693475308785</v>
+        <v>0.9832298171054987</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5049,7 @@
         <v>1620.976</v>
       </c>
       <c r="C18" t="n">
-        <v>2018.302094046946</v>
+        <v>734.1206825121023</v>
       </c>
       <c r="D18" t="n">
         <v>2.33175e-07</v>
@@ -5316,16 +5082,13 @@
         <v>-14434.2722710301</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31020319319979e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2280.930890948543</v>
+        <v>450.0659558599971</v>
       </c>
       <c r="AA18" t="n">
-        <v>1e-08</v>
+        <v>1.061155208754188e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8262783354061436</v>
+        <v>0.9971430218969883</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5099,7 @@
         <v>1600.633</v>
       </c>
       <c r="C19" t="n">
-        <v>1997.424923941518</v>
+        <v>725.2351529927615</v>
       </c>
       <c r="D19" t="n">
         <v>2.3373e-07</v>
@@ -5369,16 +5132,13 @@
         <v>-14192.03971697599</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.333047516245059e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2254.676723734933</v>
+        <v>460.5117665873611</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000014787e-08</v>
+        <v>1.079137231458343e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8266918028915716</v>
+        <v>0.9998598378183564</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5149,7 @@
         <v>1579.877</v>
       </c>
       <c r="C20" t="n">
-        <v>1976.254585424846</v>
+        <v>716.991822784439</v>
       </c>
       <c r="D20" t="n">
         <v>2.34266e-07</v>
@@ -5422,16 +5182,13 @@
         <v>-12937.89300768527</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.460650300269002e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2227.970377721017</v>
+        <v>520.5100730288557</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000839e-08</v>
+        <v>4.281049664756871e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8271051462140998</v>
+        <v>0.9146444489849165</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5199,7 @@
         <v>1560.119</v>
       </c>
       <c r="C21" t="n">
-        <v>1956.156183135844</v>
+        <v>710.2364184342158</v>
       </c>
       <c r="D21" t="n">
         <v>2.34789e-07</v>
@@ -5475,16 +5232,13 @@
         <v>-11706.66105071141</v>
       </c>
       <c r="Y21" t="n">
-        <v>214.0256189424472</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2207.389570706674</v>
+        <v>459.2924956993676</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.363638032946128e-08</v>
+        <v>1.2332929412391e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8213434993113213</v>
+        <v>0.9884086810811313</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5249,7 @@
         <v>1543.47</v>
       </c>
       <c r="C22" t="n">
-        <v>1939.268179344469</v>
+        <v>699.9231594152428</v>
       </c>
       <c r="D22" t="n">
         <v>2.35429e-07</v>
@@ -5528,16 +5282,13 @@
         <v>-9586.32539212309</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.193834251485703e-12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2174.872196386693</v>
+        <v>461.0148410882724</v>
       </c>
       <c r="AA22" t="n">
-        <v>1e-08</v>
+        <v>1.161747276287872e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8279655906794595</v>
+        <v>0.9918227839228417</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5445,7 @@
         <v>2174.471</v>
       </c>
       <c r="C2" t="n">
-        <v>2746.370551224849</v>
+        <v>1361.879066517029</v>
       </c>
       <c r="D2" t="n">
         <v>2.20078e-07</v>
@@ -5727,16 +5478,13 @@
         <v>-21007.56366235087</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.041846685555586e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2855.65665514407</v>
+        <v>84.33833604542663</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>2.070768863127949e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8204215626802764</v>
+        <v>0.8906204224740718</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>1764.7</v>
       </c>
       <c r="C3" t="n">
-        <v>2211.277342287721</v>
+        <v>19445.62634419492</v>
       </c>
       <c r="D3" t="n">
         <v>2.33503e-07</v>
@@ -5780,10 +5528,7 @@
         <v>-29762.80413971239</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.158947464803032e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2460.840346272374</v>
+        <v>-16737.29153439964</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000072e-08</v>
@@ -5800,7 +5545,7 @@
         <v>1671.263</v>
       </c>
       <c r="C4" t="n">
-        <v>2105.369900384829</v>
+        <v>760.4868885208369</v>
       </c>
       <c r="D4" t="n">
         <v>2.3384e-07</v>
@@ -5833,16 +5578,13 @@
         <v>-29847.4360263286</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.56846089924788e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2373.551420344808</v>
+        <v>493.6697344930625</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000021011e-08</v>
+        <v>1.157589037109879e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8215641561774838</v>
+        <v>0.989174781202131</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5595,7 @@
         <v>1625.661</v>
       </c>
       <c r="C5" t="n">
-        <v>2063.665073347642</v>
+        <v>744.1683888203449</v>
       </c>
       <c r="D5" t="n">
         <v>2.33246e-07</v>
@@ -5886,16 +5628,13 @@
         <v>-28068.06724866177</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.334758227760508e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2333.537564832739</v>
+        <v>512.6518534932267</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.164913838712499e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8215930723633277</v>
+        <v>0.9916246823000023</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5645,7 @@
         <v>1597.852</v>
       </c>
       <c r="C6" t="n">
-        <v>2036.569464982859</v>
+        <v>732.5655727353389</v>
       </c>
       <c r="D6" t="n">
         <v>2.32974e-07</v>
@@ -5939,16 +5678,13 @@
         <v>-28245.92726466854</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.736481504495536e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2300.107205920785</v>
+        <v>505.0326418923444</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.127273250694311e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8216909541616423</v>
+        <v>0.9969951563557182</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1564.899</v>
       </c>
       <c r="C7" t="n">
-        <v>2007.634752078986</v>
+        <v>722.1431003349614</v>
       </c>
       <c r="D7" t="n">
         <v>2.33135e-07</v>
@@ -5992,16 +5728,13 @@
         <v>-26819.05838577188</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.425876005003627e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2269.287311431293</v>
+        <v>514.9430388923331</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000003992e-08</v>
+        <v>1.246586917075369e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8217908062015363</v>
+        <v>0.9888926956574201</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5745,7 @@
         <v>1538.293</v>
       </c>
       <c r="C8" t="n">
-        <v>1981.883550846453</v>
+        <v>712.2705770037653</v>
       </c>
       <c r="D8" t="n">
         <v>2.33142e-07</v>
@@ -6045,16 +5778,13 @@
         <v>-26811.47510177144</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.288055662162158e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2237.907758369383</v>
+        <v>514.935833296954</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000146e-08</v>
+        <v>1.648165491151982e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8219453149809027</v>
+        <v>0.9744268033285335</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1513.229</v>
       </c>
       <c r="C9" t="n">
-        <v>1957.875339325341</v>
+        <v>702.766927919712</v>
       </c>
       <c r="D9" t="n">
         <v>2.33424e-07</v>
@@ -6098,16 +5828,13 @@
         <v>-26448.81097753151</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.374342983002057e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2206.807522206962</v>
+        <v>526.6719556149442</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000029e-08</v>
+        <v>1.9967844193334e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8221534722933097</v>
+        <v>0.9629263258196423</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1488.29</v>
       </c>
       <c r="C10" t="n">
-        <v>1931.908128396549</v>
+        <v>694.3873377576778</v>
       </c>
       <c r="D10" t="n">
         <v>2.33649e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-26404.51397399669</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.40292540559079e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2176.098698950425</v>
+        <v>542.4779658197808</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000004222e-08</v>
+        <v>2.188843002399087e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8223805662431459</v>
+        <v>0.9557323359327976</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1459.921</v>
       </c>
       <c r="C11" t="n">
-        <v>1904.838983538825</v>
+        <v>686.2169085009454</v>
       </c>
       <c r="D11" t="n">
         <v>2.34023e-07</v>
@@ -6204,16 +5928,13 @@
         <v>-24635.61255281352</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.742571044718832e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2146.827841083477</v>
+        <v>524.0953580840319</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000184e-08</v>
+        <v>1.715912978870112e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8226377992422598</v>
+        <v>0.9739007955533205</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6091,7 @@
         <v>2093.148</v>
       </c>
       <c r="C2" t="n">
-        <v>2515.940406644857</v>
+        <v>953.0122248699223</v>
       </c>
       <c r="D2" t="n">
         <v>2.23371e-07</v>
@@ -6403,16 +6124,13 @@
         <v>-28098.65600786905</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.516309795665231e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2832.479758107666</v>
+        <v>389.6894912650604</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000011e-08</v>
+        <v>1.232668486959394e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8218694643867974</v>
+        <v>0.9644282738627106</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>1979.778</v>
       </c>
       <c r="C3" t="n">
-        <v>2375.863230327489</v>
+        <v>879.9027014991814</v>
       </c>
       <c r="D3" t="n">
         <v>2.25922e-07</v>
@@ -6456,16 +6174,13 @@
         <v>-30921.52940052495</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.558440525962691e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2709.448860319832</v>
+        <v>435.4574587105518</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000001159e-08</v>
+        <v>8.574585407921753e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8221500865567808</v>
+        <v>0.9984346452857512</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6191,7 @@
         <v>1936.725</v>
       </c>
       <c r="C4" t="n">
-        <v>2331.492527989931</v>
+        <v>861.7432255709004</v>
       </c>
       <c r="D4" t="n">
         <v>2.26895e-07</v>
@@ -6509,16 +6224,13 @@
         <v>-30303.514849251</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.013495115745491e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2665.179508477985</v>
+        <v>443.6725251404395</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.423955029498212e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8221849038869791</v>
+        <v>0.9929554014777152</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6241,7 @@
         <v>1901.838</v>
       </c>
       <c r="C5" t="n">
-        <v>2298.871472637617</v>
+        <v>848.9229582936174</v>
       </c>
       <c r="D5" t="n">
         <v>2.27855e-07</v>
@@ -6562,16 +6274,13 @@
         <v>-27674.41706039802</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.912568205178581e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2631.110526981742</v>
+        <v>455.1531992784085</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000014e-08</v>
+        <v>9.539388042590762e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.822277231834462</v>
+        <v>0.9959779957156106</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6291,7 @@
         <v>1881.244</v>
       </c>
       <c r="C6" t="n">
-        <v>2276.667711482743</v>
+        <v>836.5790958066243</v>
       </c>
       <c r="D6" t="n">
         <v>2.28716e-07</v>
@@ -6615,16 +6324,13 @@
         <v>-28438.26903061018</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.395283970990217e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2595.744206171674</v>
+        <v>452.8194700804873</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000622e-08</v>
+        <v>9.221695820143408e-10</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8225465393082664</v>
+        <v>0.9979832350457178</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1844.162</v>
       </c>
       <c r="C7" t="n">
-        <v>2243.725055684869</v>
+        <v>824.0195633259351</v>
       </c>
       <c r="D7" t="n">
         <v>2.29535e-07</v>
@@ -6668,16 +6374,13 @@
         <v>-26079.56078795576</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.097861802157766e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2561.390606631469</v>
+        <v>453.5736879509614</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000005275e-08</v>
+        <v>9.476180977355189e-10</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8228030056295692</v>
+        <v>0.9962255112200923</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6391,7 @@
         <v>1818.872</v>
       </c>
       <c r="C8" t="n">
-        <v>2216.583886034861</v>
+        <v>813.0121672601031</v>
       </c>
       <c r="D8" t="n">
         <v>2.30346e-07</v>
@@ -6721,16 +6424,13 @@
         <v>-25375.22291093219</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.303595998404677e-12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2529.255322404762</v>
+        <v>464.947764366213</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.103535986628787e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8230318450763889</v>
+        <v>0.9888114751837165</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1789.279</v>
       </c>
       <c r="C9" t="n">
-        <v>2190.128150582782</v>
+        <v>801.9265954505463</v>
       </c>
       <c r="D9" t="n">
         <v>2.30949e-07</v>
@@ -6774,16 +6474,13 @@
         <v>-24136.30563903323</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.1400411281563e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2499.487328830749</v>
+        <v>468.0800150765444</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.076852449303619e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.823273375898105</v>
+        <v>0.9925489031958861</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1769.016</v>
       </c>
       <c r="C10" t="n">
-        <v>2170.587094266471</v>
+        <v>791.5006664475138</v>
       </c>
       <c r="D10" t="n">
         <v>2.31837e-07</v>
@@ -6827,16 +6524,13 @@
         <v>-23748.95608733457</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.264077801157476e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2470.362966036245</v>
+        <v>470.3558918217516</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000007143e-08</v>
+        <v>1.318609787516519e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.823525410754765</v>
+        <v>0.9842832175839344</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1748.982</v>
       </c>
       <c r="C11" t="n">
-        <v>2148.156413193878</v>
+        <v>782.3345684704176</v>
       </c>
       <c r="D11" t="n">
         <v>2.32653e-07</v>
@@ -6880,16 +6574,13 @@
         <v>-23811.52145006346</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.736970107731786e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2442.704039156864</v>
+        <v>470.7908235142146</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000017284e-08</v>
+        <v>1.015764836308911e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8237838347778901</v>
+        <v>0.9991118366426999</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6591,7 @@
         <v>1720.424</v>
       </c>
       <c r="C12" t="n">
-        <v>2121.390133963089</v>
+        <v>773.4092036675291</v>
       </c>
       <c r="D12" t="n">
         <v>2.33275e-07</v>
@@ -6933,16 +6624,13 @@
         <v>-21778.60456972539</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.703072928447077e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2415.773380742343</v>
+        <v>473.5643551574981</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000004286e-08</v>
+        <v>1.033518041973094e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8240697090143507</v>
+        <v>0.99299848690078</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1699.803</v>
       </c>
       <c r="C13" t="n">
-        <v>2100.688082523844</v>
+        <v>764.5717476310285</v>
       </c>
       <c r="D13" t="n">
         <v>2.33855e-07</v>
@@ -6986,16 +6674,13 @@
         <v>-21320.76304847044</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.796389850219528e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2389.21634967006</v>
+        <v>445.108602080831</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000065e-08</v>
+        <v>9.687591273927835e-10</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8243677071297558</v>
+        <v>0.9998018507440846</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1671.467</v>
       </c>
       <c r="C14" t="n">
-        <v>2075.641439464853</v>
+        <v>754.9071998651414</v>
       </c>
       <c r="D14" t="n">
         <v>2.34328e-07</v>
@@ -7039,16 +6724,13 @@
         <v>-20159.52844389887</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.824930918373567e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2362.603687215268</v>
+        <v>449.6288957215151</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000197e-08</v>
+        <v>1.208213932819997e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8246845197610774</v>
+        <v>0.9924115361764864</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1664.904</v>
       </c>
       <c r="C15" t="n">
-        <v>2063.550554723865</v>
+        <v>747.138640738997</v>
       </c>
       <c r="D15" t="n">
         <v>2.35094e-07</v>
@@ -7092,16 +6774,13 @@
         <v>-19518.80075947692</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.473080802826887e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2336.332762416729</v>
+        <v>449.6486623135133</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000004113e-08</v>
+        <v>1.216182201102893e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8250098687698577</v>
+        <v>0.9920727903188867</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6791,7 @@
         <v>1653.147</v>
       </c>
       <c r="C16" t="n">
-        <v>2047.278849630708</v>
+        <v>742.5779137981634</v>
       </c>
       <c r="D16" t="n">
         <v>2.35864e-07</v>
@@ -7145,16 +6824,13 @@
         <v>-18992.52057695977</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.667522414754383e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2310.940986393167</v>
+        <v>443.3475066176657</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000308e-08</v>
+        <v>1.225526170326791e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8253397893911518</v>
+        <v>0.9928374172386624</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6841,7 @@
         <v>1615.759</v>
       </c>
       <c r="C17" t="n">
-        <v>2014.447022512218</v>
+        <v>735.7340155572861</v>
       </c>
       <c r="D17" t="n">
         <v>2.36385e-07</v>
@@ -7198,16 +6874,13 @@
         <v>-17149.4884667881</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.002937517158759e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2285.377112737908</v>
+        <v>466.749329782513</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000010564e-08</v>
+        <v>1.02494334773884e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8256829077079835</v>
+        <v>0.9994051199491175</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6891,7 @@
         <v>1602.056</v>
       </c>
       <c r="C18" t="n">
-        <v>1998.275824275248</v>
+        <v>727.0249537850181</v>
       </c>
       <c r="D18" t="n">
         <v>2.37029e-07</v>
@@ -7251,16 +6924,13 @@
         <v>-16631.39926971079</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.75017130529854e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2259.916081722555</v>
+        <v>459.7727907053791</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000010925e-08</v>
+        <v>1.064838464273437e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8260437833206654</v>
+        <v>0.9995922754558128</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6941,7 @@
         <v>1579.637</v>
       </c>
       <c r="C19" t="n">
-        <v>1978.739129081598</v>
+        <v>719.4460320330542</v>
       </c>
       <c r="D19" t="n">
         <v>2.37695e-07</v>
@@ -7304,16 +6974,13 @@
         <v>-15087.00295811185</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.186025180523736e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2234.719984376756</v>
+        <v>454.1707221190902</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000713e-08</v>
+        <v>1.225159395891567e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.826405951208726</v>
+        <v>0.9950666629138568</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6991,7 @@
         <v>1568.663</v>
       </c>
       <c r="C20" t="n">
-        <v>1963.576844550444</v>
+        <v>711.0944573454043</v>
       </c>
       <c r="D20" t="n">
         <v>2.3828e-07</v>
@@ -7357,16 +7024,13 @@
         <v>-14364.12233441492</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.112743634453489e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2209.293118100206</v>
+        <v>468.8337408396676</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000094e-08</v>
+        <v>1.216918420037166e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8267873042100341</v>
+        <v>0.9925897287846013</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7041,7 @@
         <v>1548.828</v>
       </c>
       <c r="C21" t="n">
-        <v>1944.468956381527</v>
+        <v>704.5204234092257</v>
       </c>
       <c r="D21" t="n">
         <v>2.38759e-07</v>
@@ -7410,16 +7074,13 @@
         <v>-13962.15478543122</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.77775154945498e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2183.771627758495</v>
+        <v>455.2296336738441</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000501e-08</v>
+        <v>1.128820070197287e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8271748786062363</v>
+        <v>0.9990381870111001</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7091,7 @@
         <v>1523.119</v>
       </c>
       <c r="C22" t="n">
-        <v>1919.076607883001</v>
+        <v>696.5146490537602</v>
       </c>
       <c r="D22" t="n">
         <v>2.39541e-07</v>
@@ -7463,16 +7124,13 @@
         <v>-11790.90891477915</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.409358536093444e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2157.791352734257</v>
+        <v>452.5313398520178</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000728e-08</v>
+        <v>1.132234771329827e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8275681735177792</v>
+        <v>0.9962322293587613</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7287,7 @@
         <v>2015.446</v>
       </c>
       <c r="C2" t="n">
-        <v>2611.852004526477</v>
+        <v>15388.72165182136</v>
       </c>
       <c r="D2" t="n">
         <v>2.2951e-07</v>
@@ -7662,10 +7320,7 @@
         <v>-21350.10912091603</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.288473459606596e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2640.53776847434</v>
+        <v>-12273.40540016325</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000024413e-08</v>
@@ -7682,7 +7337,7 @@
         <v>1701.466</v>
       </c>
       <c r="C3" t="n">
-        <v>2210.101804745281</v>
+        <v>759.3767292094668</v>
       </c>
       <c r="D3" t="n">
         <v>2.3632e-07</v>
@@ -7715,16 +7370,13 @@
         <v>-29479.66127775418</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.054871269118177e-12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2349.503403421527</v>
+        <v>458.0650596218998</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000012586e-08</v>
+        <v>9.969655728498577e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8251235722242805</v>
+        <v>0.9991223036380793</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>1615.332</v>
       </c>
       <c r="C4" t="n">
-        <v>2121.439531758354</v>
+        <v>725.7332980343529</v>
       </c>
       <c r="D4" t="n">
         <v>2.35847e-07</v>
@@ -7768,16 +7420,13 @@
         <v>-27298.55563783196</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.317944178429333e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2279.715259742693</v>
+        <v>486.151633541262</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000005e-08</v>
+        <v>1.174980664214271e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8252129352714285</v>
+        <v>0.9985251995528907</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1579.975</v>
       </c>
       <c r="C5" t="n">
-        <v>2086.473726962341</v>
+        <v>709.31046666418</v>
       </c>
       <c r="D5" t="n">
         <v>2.35448e-07</v>
@@ -7821,16 +7470,13 @@
         <v>-27115.73589711453</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.899469626949051e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2242.36267692865</v>
+        <v>489.2146775434792</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.205656287623636e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.825212890366271</v>
+        <v>0.990401433778232</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7487,7 @@
         <v>1560.663</v>
       </c>
       <c r="C6" t="n">
-        <v>2064.59442080263</v>
+        <v>698.8224245797921</v>
       </c>
       <c r="D6" t="n">
         <v>2.35076e-07</v>
@@ -7874,16 +7520,13 @@
         <v>-28667.12261074701</v>
       </c>
       <c r="Y6" t="n">
-        <v>186.1080253299602</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2211.862347563584</v>
+        <v>494.7922564293505</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.382244200619495e-08</v>
+        <v>1.212378966638929e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8159039158184652</v>
+        <v>0.9951797379866743</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7537,7 @@
         <v>1533.154</v>
       </c>
       <c r="C7" t="n">
-        <v>2038.106168240529</v>
+        <v>694.0865552593356</v>
       </c>
       <c r="D7" t="n">
         <v>2.35186e-07</v>
@@ -7927,16 +7570,13 @@
         <v>-26993.33078943432</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.675000967276618e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2180.94831184644</v>
+        <v>491.4656796967368</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000015584e-08</v>
+        <v>1.529886510050651e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8254023148446075</v>
+        <v>0.9825829327349537</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7587,7 @@
         <v>1503.626</v>
       </c>
       <c r="C8" t="n">
-        <v>2013.147145614282</v>
+        <v>683.5037005251703</v>
       </c>
       <c r="D8" t="n">
         <v>2.35504e-07</v>
@@ -7980,16 +7620,13 @@
         <v>-26286.68335206001</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.101096256983958e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2148.73215383579</v>
+        <v>472.9097508905863</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000427e-08</v>
+        <v>1.11748048817519e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8256323614413871</v>
+        <v>0.999326962664797</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7637,7 @@
         <v>1478.668</v>
       </c>
       <c r="C9" t="n">
-        <v>1988.305652485264</v>
+        <v>675.2450558944614</v>
       </c>
       <c r="D9" t="n">
         <v>2.35779e-07</v>
@@ -8033,16 +7670,13 @@
         <v>-25941.16270923146</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.252752228430736e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2115.756282430544</v>
+        <v>491.8005977663384</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.196435945242283e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8259010857081182</v>
+        <v>0.9990786989639262</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7687,7 @@
         <v>1444.883</v>
       </c>
       <c r="C10" t="n">
-        <v>1961.110642737502</v>
+        <v>665.0679307575998</v>
       </c>
       <c r="D10" t="n">
         <v>2.36144e-07</v>
@@ -8086,16 +7720,13 @@
         <v>-24281.90336628448</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.290137604425771e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2084.486497516774</v>
+        <v>486.2434608511051</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.317460796727901e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8261887128519112</v>
+        <v>0.9983414969105259</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1415.103</v>
       </c>
       <c r="C11" t="n">
-        <v>1935.314678258179</v>
+        <v>655.6120946529621</v>
       </c>
       <c r="D11" t="n">
         <v>2.36593e-07</v>
@@ -8139,16 +7770,13 @@
         <v>-22725.38444258767</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.546089694979385e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2054.950347124875</v>
+        <v>478.1156249982164</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000053009e-08</v>
+        <v>1.387730298097852e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8264845125175559</v>
+        <v>0.9904846935838968</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>2087.227</v>
       </c>
       <c r="C2" t="n">
-        <v>2543.817203678673</v>
+        <v>917.0742930924354</v>
       </c>
       <c r="D2" t="n">
         <v>2.25991e-07</v>
@@ -8338,16 +7966,13 @@
         <v>-32128.84861043092</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.018497924899276e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2766.750533962472</v>
+        <v>388.4611165267889</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000032e-08</v>
+        <v>1.288970354978538e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8252253134487614</v>
+        <v>0.9752309726849687</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1975.505</v>
       </c>
       <c r="C3" t="n">
-        <v>2424.218269333745</v>
+        <v>863.0743766665368</v>
       </c>
       <c r="D3" t="n">
         <v>2.27602e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-28740.52815406123</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.482444433917909e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2667.402029510698</v>
+        <v>411.0538278557223</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>8.386346857968384e-10</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8254504445705302</v>
+        <v>0.9999607201048025</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1936.978</v>
       </c>
       <c r="C4" t="n">
-        <v>2383.746566833334</v>
+        <v>842.9885442261738</v>
       </c>
       <c r="D4" t="n">
         <v>2.28726e-07</v>
@@ -8444,16 +8066,13 @@
         <v>-28195.25688813455</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.750350788854377e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2621.92439174166</v>
+        <v>442.8738021691206</v>
       </c>
       <c r="AA4" t="n">
-        <v>1e-08</v>
+        <v>1.279183830320478e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8255304963047722</v>
+        <v>0.9773985598338401</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1906.245</v>
       </c>
       <c r="C5" t="n">
-        <v>2352.779496355441</v>
+        <v>830.8914682063747</v>
       </c>
       <c r="D5" t="n">
         <v>2.29696e-07</v>
@@ -8497,16 +8116,13 @@
         <v>-26301.86661403129</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.947837157897419e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2585.253226771898</v>
+        <v>435.5576041431559</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>9.721993873583052e-10</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8256235195939408</v>
+        <v>0.9963157807648427</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1875.23</v>
       </c>
       <c r="C6" t="n">
-        <v>2324.842629658667</v>
+        <v>817.5307603226011</v>
       </c>
       <c r="D6" t="n">
         <v>2.3042e-07</v>
@@ -8550,16 +8166,13 @@
         <v>-25313.03262601143</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.953554496488012e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2551.158655032718</v>
+        <v>471.4589080768959</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000001853e-08</v>
+        <v>1.552131908477001e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8257504715414885</v>
+        <v>0.9629229363063581</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1848.091</v>
       </c>
       <c r="C7" t="n">
-        <v>2301.320821955039</v>
+        <v>806.5762311597883</v>
       </c>
       <c r="D7" t="n">
         <v>2.31277e-07</v>
@@ -8603,16 +8216,13 @@
         <v>-23891.63781397516</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.166065075582911e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2519.883370992912</v>
+        <v>440.4247683678303</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000656e-08</v>
+        <v>1.003563830915128e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8259028022210997</v>
+        <v>0.9993322794352676</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1824.38</v>
       </c>
       <c r="C8" t="n">
-        <v>2276.278481123644</v>
+        <v>795.4678791982763</v>
       </c>
       <c r="D8" t="n">
         <v>2.32009e-07</v>
@@ -8656,16 +8266,13 @@
         <v>-23111.43067449572</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.009672237852387e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2490.440800320759</v>
+        <v>450.4324112861451</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000001725e-08</v>
+        <v>1.060476139403464e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8260852607427001</v>
+        <v>0.9976614044932782</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8283,7 @@
         <v>1807.371</v>
       </c>
       <c r="C9" t="n">
-        <v>2254.900163859914</v>
+        <v>790.1111755697382</v>
       </c>
       <c r="D9" t="n">
         <v>2.3284e-07</v>
@@ -8709,16 +8316,13 @@
         <v>-21624.09864836832</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.021825600564301e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2461.192357789637</v>
+        <v>444.3077342305343</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000001761e-08</v>
+        <v>1.004043591954353e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8263354310367195</v>
+        <v>0.9988910913869289</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8333,7 @@
         <v>1783.667</v>
       </c>
       <c r="C10" t="n">
-        <v>2230.464852046483</v>
+        <v>780.2244781470379</v>
       </c>
       <c r="D10" t="n">
         <v>2.33579e-07</v>
@@ -8762,16 +8366,13 @@
         <v>-19985.38718802719</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.280938585877643e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2431.737844928728</v>
+        <v>449.784929501843</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>1.085368406901574e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8266642920549608</v>
+        <v>0.9984441273268063</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1757.416</v>
       </c>
       <c r="C11" t="n">
-        <v>2207.532584711646</v>
+        <v>769.7848577997001</v>
       </c>
       <c r="D11" t="n">
         <v>2.34293e-07</v>
@@ -8815,16 +8416,13 @@
         <v>-18778.43135635072</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.971303253004576e-11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2402.151911987078</v>
+        <v>447.2454487228217</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>9.814945254798687e-10</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8270396121778827</v>
+        <v>0.9992194150487096</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8433,7 @@
         <v>1725.554</v>
       </c>
       <c r="C12" t="n">
-        <v>2179.758185047552</v>
+        <v>759.3011141376286</v>
       </c>
       <c r="D12" t="n">
         <v>2.34913e-07</v>
@@ -8868,16 +8466,13 @@
         <v>-18100.47329219053</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.92107921365423e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2371.647713132661</v>
+        <v>453.0690385578976</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000000153e-08</v>
+        <v>1.027792478371262e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8274583103561436</v>
+        <v>0.9980410358806323</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1701.919</v>
       </c>
       <c r="C13" t="n">
-        <v>2155.727302247897</v>
+        <v>749.298585486656</v>
       </c>
       <c r="D13" t="n">
         <v>2.35566e-07</v>
@@ -8921,16 +8516,13 @@
         <v>-16302.09312969965</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.593582725294761e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2342.020353029596</v>
+        <v>444.6292774541904</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.061333897329491e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8278971848263614</v>
+        <v>0.9967458728260447</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1666.991</v>
       </c>
       <c r="C14" t="n">
-        <v>2123.189926248076</v>
+        <v>740.9200388912736</v>
       </c>
       <c r="D14" t="n">
         <v>2.36302e-07</v>
@@ -8974,16 +8566,13 @@
         <v>-15156.61205430785</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.326223305162802e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2311.659965095116</v>
+        <v>439.4018801179344</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.090806394503472e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8283458396673902</v>
+        <v>0.9967799063122318</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1663.012</v>
       </c>
       <c r="C15" t="n">
-        <v>2114.138677286709</v>
+        <v>729.9929126684563</v>
       </c>
       <c r="D15" t="n">
         <v>2.37135e-07</v>
@@ -9027,16 +8616,13 @@
         <v>-13392.69519369811</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.345693589351309e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2281.619374699685</v>
+        <v>432.301116605798</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.246543771201783e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8288164091000833</v>
+        <v>0.9901767675108998</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1639.766</v>
       </c>
       <c r="C16" t="n">
-        <v>2093.312605265479</v>
+        <v>720.3795980744724</v>
       </c>
       <c r="D16" t="n">
         <v>2.37598e-07</v>
@@ -9080,16 +8666,13 @@
         <v>-11112.43555011945</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.047915646325895e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2252.811461591035</v>
+        <v>449.8061552522</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000587e-08</v>
+        <v>1.170208913346279e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8292669708099299</v>
+        <v>0.9954808380101716</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1601.694</v>
       </c>
       <c r="C17" t="n">
-        <v>2058.19637927497</v>
+        <v>710.6103936414135</v>
       </c>
       <c r="D17" t="n">
         <v>2.38251e-07</v>
@@ -9133,16 +8716,13 @@
         <v>-12675.7855336765</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.918555176209131e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2223.671646583151</v>
+        <v>438.0509540014458</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000016e-08</v>
+        <v>1.058380103076538e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8297354120510478</v>
+        <v>0.9999390309345435</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1590.057</v>
       </c>
       <c r="C18" t="n">
-        <v>2042.97113161442</v>
+        <v>703.9623142747769</v>
       </c>
       <c r="D18" t="n">
         <v>2.38904e-07</v>
@@ -9186,16 +8766,13 @@
         <v>-10239.6909478978</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.034582895725092e-12</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2195.094847795729</v>
+        <v>444.2288087090116</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000055e-08</v>
+        <v>1.162857988672184e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8302051714946416</v>
+        <v>0.9988655086537448</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8783,7 @@
         <v>1565.619</v>
       </c>
       <c r="C19" t="n">
-        <v>2018.645521873746</v>
+        <v>692.4404671595746</v>
       </c>
       <c r="D19" t="n">
         <v>2.3969e-07</v>
@@ -9239,16 +8816,13 @@
         <v>-7640.345798778478</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.432931517641712e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2165.992430881933</v>
+        <v>451.4933624683733</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000026e-08</v>
+        <v>1.222148153328854e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8306727791216445</v>
+        <v>0.9951651159270229</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8833,7 @@
         <v>1542.369</v>
       </c>
       <c r="C20" t="n">
-        <v>1997.156045658575</v>
+        <v>684.6702722891569</v>
       </c>
       <c r="D20" t="n">
         <v>2.40298e-07</v>
@@ -9292,16 +8866,13 @@
         <v>-6039.21534301539</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.660458373077296e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2137.132715118158</v>
+        <v>426.0534355621184</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000002782e-08</v>
+        <v>1.158492455202897e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8311611615719875</v>
+        <v>0.9943461951515514</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8883,7 @@
         <v>1512.118</v>
       </c>
       <c r="C21" t="n">
-        <v>1969.834788910576</v>
+        <v>674.5666274111434</v>
       </c>
       <c r="D21" t="n">
         <v>2.41056e-07</v>
@@ -9345,16 +8916,13 @@
         <v>-5310.017213698121</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.92893508239642e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2108.33894790977</v>
+        <v>447.6733454209104</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.0000000000003e-08</v>
+        <v>1.238081846468976e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8316375930716181</v>
+        <v>0.993631847495152</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8933,7 @@
         <v>1499.942</v>
       </c>
       <c r="C22" t="n">
-        <v>1952.749785563532</v>
+        <v>667.6549048243232</v>
       </c>
       <c r="D22" t="n">
         <v>2.41613e-07</v>
@@ -9398,16 +8966,13 @@
         <v>-2490.739084547793</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.570472746967216e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2081.046908599812</v>
+        <v>423.8719669265045</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000047997e-08</v>
+        <v>1.083777918389465e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8321209555534694</v>
+        <v>0.9999714208434733</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9129,7 @@
         <v>1564.238</v>
       </c>
       <c r="C2" t="n">
-        <v>2231.001235191762</v>
+        <v>18557.1948092744</v>
       </c>
       <c r="D2" t="n">
         <v>2.46739e-07</v>
@@ -9597,10 +9162,7 @@
         <v>-18277.82618051678</v>
       </c>
       <c r="Y2" t="n">
-        <v>162.6737353687826</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2162.228436743672</v>
+        <v>-15950.40175500545</v>
       </c>
       <c r="AA2" t="n">
         <v>1.521377037002092e-08</v>
@@ -9617,7 +9179,7 @@
         <v>1311.817</v>
       </c>
       <c r="C3" t="n">
-        <v>1870.939716622361</v>
+        <v>620.663062301287</v>
       </c>
       <c r="D3" t="n">
         <v>2.46746e-07</v>
@@ -9650,16 +9212,13 @@
         <v>-25629.09437306778</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.323351647208594e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1916.660323873801</v>
+        <v>482.8211778428329</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.278653997737872e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8277510929816904</v>
+        <v>0.9980450610847955</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1257.615</v>
       </c>
       <c r="C4" t="n">
-        <v>1803.879236726743</v>
+        <v>607.9607437620015</v>
       </c>
       <c r="D4" t="n">
         <v>2.4432e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-26886.77868228229</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.793287299827609e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1860.144351889452</v>
+        <v>465.443391037469</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.214360492579191e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.827919603522968</v>
+        <v>0.9998294887965838</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1224.055</v>
       </c>
       <c r="C5" t="n">
-        <v>1770.175803951287</v>
+        <v>550.6451635831075</v>
       </c>
       <c r="D5" t="n">
         <v>2.43125e-07</v>
@@ -9756,16 +9312,13 @@
         <v>-25053.52312847711</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.202144731797539e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1826.396393760933</v>
+        <v>530.1982008311821</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000031e-08</v>
+        <v>1.761839033401758e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8280891351992294</v>
+        <v>0.9886637790707428</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1206.946</v>
       </c>
       <c r="C6" t="n">
-        <v>1757.188851511705</v>
+        <v>554.5222262901136</v>
       </c>
       <c r="D6" t="n">
         <v>2.42612e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-27927.97081087231</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.696445211737782e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1794.850558248901</v>
+        <v>528.3171127618006</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000024e-08</v>
+        <v>2.269641591029448e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8283454907159454</v>
+        <v>0.9726486654605065</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1168.768</v>
       </c>
       <c r="C7" t="n">
-        <v>1725.395907457301</v>
+        <v>557.9012240620262</v>
       </c>
       <c r="D7" t="n">
         <v>2.42319e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-24313.63993911394</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.459990444312311e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1762.967762768062</v>
+        <v>481.9973132070575</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.476327178834879e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8286812595417239</v>
+        <v>0.9963299206514785</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1137.28</v>
       </c>
       <c r="C8" t="n">
-        <v>1695.268255780691</v>
+        <v>556.9850641705146</v>
       </c>
       <c r="D8" t="n">
         <v>2.42295e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-22522.8502908081</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.839332757947256e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1731.525000378381</v>
+        <v>470.3611929173554</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000668e-08</v>
+        <v>1.371756819242044e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8290768969353889</v>
+        <v>0.9993355510760945</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>1119.487</v>
       </c>
       <c r="C9" t="n">
-        <v>1681.934517010292</v>
+        <v>558.4266651550913</v>
       </c>
       <c r="D9" t="n">
         <v>2.42347e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-23105.8503023518</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.278126041582441e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1700.93793595741</v>
+        <v>452.7585013650657</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>1.424565437100536e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.829482136310853</v>
+        <v>0.9971283611891693</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>1096.526</v>
       </c>
       <c r="C10" t="n">
-        <v>1660.756306129141</v>
+        <v>560.7813215340782</v>
       </c>
       <c r="D10" t="n">
         <v>2.42372e-07</v>
@@ -10021,16 +9562,13 @@
         <v>-23136.45351873905</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.727421379567755e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1671.997039690264</v>
+        <v>444.5339752024031</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.439763010047601e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8298934578820746</v>
+        <v>0.9987894148069445</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>1069.946</v>
       </c>
       <c r="C11" t="n">
-        <v>1637.359407804559</v>
+        <v>560.6888702785679</v>
       </c>
       <c r="D11" t="n">
         <v>2.42542e-07</v>
@@ -10074,16 +9612,13 @@
         <v>-21211.2100944628</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.501400957957264e-07</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1645.259342180763</v>
+        <v>433.9836685719425</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000010075e-08</v>
+        <v>1.40953251257967e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8303035760423194</v>
+        <v>0.9991753529937906</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 39.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.000000000000531e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8247652552925044</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1704.605</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2091.481092227319</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.32371e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-67.977</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01575433911882367</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.002420856610799424</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5938962360121987</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.438078902229933</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.41886389617179</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.46502329812238</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.6078004481823</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-26512.61895166363</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>16.41713379500607</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8233824879217257</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1664.688</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9765828447059585</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2045.132322117786</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9778392593259481</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.27875e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-69.797</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3082210242587696</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4001349527665555</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9851943755169142</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.973079492317973</v>
+      </c>
+      <c r="L13" t="n">
+        <v>32.13402264537932</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.01872816656795</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.36815610460482</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-29617.4678162674</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>16.89958722845097</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000215e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8233904233678926</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1630.645</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9566116490330605</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2073.607431723819</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9914540654611108</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.26419e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-70.614</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.05466237942121539</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5841807909604443</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.37890442890439</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.077980456026101</v>
+      </c>
+      <c r="L14" t="n">
+        <v>32.26730097667861</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.01905782346823</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.36934975221151</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-29107.97135255189</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-11.42203684605488</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8234056046303073</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1600.033</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9386532363802759</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1978.509877836155</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9459850654108206</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.25594e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-71.068</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1577680525164098</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3983709273182684</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.078103315343079</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.897581699346319</v>
+      </c>
+      <c r="L15" t="n">
+        <v>33.44492000605699</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.12382935935841</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.75898457011279</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-29473.00660329694</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>18.74555509968036</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000264e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8235052362770372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1564.504</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9178102844940618</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2021.907793804924</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9667349139894436</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.25026e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-71.563</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.210745233968823</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4955786736021136</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.023116089613024</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.887412587412628</v>
+      </c>
+      <c r="L16" t="n">
+        <v>26.70903795241034</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.91615261099008</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.00608632591148</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-27455.43201969614</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-15.5675902907891</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000649e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8236709883754649</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1535.392</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9007318411010176</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1998.168873960798</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9553846225943416</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.24808e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-71.98</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1611263736263687</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4287380699893699</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.01772151898723</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.635299145299093</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.58949857001882</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.90613361084375</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.97169244112645</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-26980.66251654135</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-18.59912732629493</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000001893e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8238878356306352</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1501.556</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.880882081185964</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1974.691551366488</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9441594087104772</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.24698e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-72.328</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.06542057126002078</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6303688896605991</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.63129725553657</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.078027739177654</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.72401982761939</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.37456341053684</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-25375.11933162333</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-21.59221179972792</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000093e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8241075674849676</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1480.783</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.8686956802309039</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1950.163820959665</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9324319632662047</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.2455e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-72.651</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2910290237466855</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3506963788301051</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7874269005848177</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.990821256038708</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.1539926175388</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.98038142467519</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.23064104904719</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-26702.59540322645</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-22.89619129659604</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000253e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8243225855446978</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1458.165</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8554269170863632</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1932.614529865772</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9240411194956765</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.24504e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72.977</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3619582664526448</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3673437499999841</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9012208657048381</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.035925612848683</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.88729463789171</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.86205760765881</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.82236009498581</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-25554.5036609288</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-27.21942047632626</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000007374e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8245325174446646</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1430.516</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8392067370446528</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1914.944718569675</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9155926513924916</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.24506e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-73.235</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1365533417420565</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7330079791909093</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.709923149880702</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.125179212934257</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.78245531365859</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.5605575802007</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-24703.07649563891</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-30.85873522200654</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000531e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8247652552925044</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000000005e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8303157667479026</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2055.975</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2433.856438969819</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.19786e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-66.867</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1802071346375068</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5785915492957741</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.451624933404409</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.492857142857138</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28.34008100768899</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.50598793787236</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.72320458846078</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-30660.02153502501</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.586975054406821</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000562e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8239737920711422</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1927.415</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9374700567857098</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2340.016589125933</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.961443966726482</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.23489e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-68.33799999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5511930585682971</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8598851517637072</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.476523582405947</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.515280464216627</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.37491727899916</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.36113574657744</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-28099.15557419353</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-5.721285440908787</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8243521382922012</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1883.881</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9162956748014932</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2295.901979764094</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9433185717132448</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.24766e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-68.764</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4578002244669354</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7948696383515627</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.919136172765452</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.636610738254964</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.30000873053365</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.1632583156551</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-27112.95277324877</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-4.860057488174562</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000002802e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8244304712573326</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1846.941</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.898328530259366</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2270.046040876671</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9326951271774746</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.2551e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-69.04900000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1092522179974737</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9742179072275774</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.57566820276496</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.110467289719682</v>
+      </c>
+      <c r="L26" t="n">
+        <v>3.020735313118535</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.03164750472718</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.50322944524455</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-25225.26241618456</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-6.571095093932627</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001974e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8245172483092832</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1811.258</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8809727744743977</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2243.047276798683</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9216021293959723</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.26554e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-69.342</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1400000000000118</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5327956989247116</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.151415525114055</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.835872235872209</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.018957815828966</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.66596044994454</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.71048618201072</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-23117.85400731676</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-6.661529619445218</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8246550093241634</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1801.913</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8764274857427742</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2146.410225080057</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8818968081735219</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.2703e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-69.624</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5412054120541531</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.06234309623428</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.670918665886443</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.836098981077149</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.01050864696612</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.45424830216113</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-24527.17234841071</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>23.93711605249109</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8248736551774272</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1774.466</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.863077615243376</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2121.749384988958</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8717643945700565</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.2791e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-69.913</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.128387734915926</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.39521094640839</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.709373097991405</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.729118250170881</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.67699592376789</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.73281948843169</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-22627.33967337245</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>22.84294318027332</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8251194166917888</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1735.871</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8443054998236847</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2141.962730235136</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.880069463399315</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.2848e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-70.16200000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.02919896640827236</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.317182497331934</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.022502424830318</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.694043321299626</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.29826115100296</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.01563234301469</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-20780.16045926497</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.837186616251074</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000309e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8254046977366076</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1721.034</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8370889723853646</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2120.083008692708</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8710797295793162</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.29191e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-70.395</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.4997405966277689</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6021596244131465</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.518346456692978</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.133608949416354</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.2712164075494</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.968035663900809</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-20449.78197501574</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.903980206977167</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8256932436551032</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1694.981</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8244171256946217</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2051.819822705704</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8430323949485614</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.29819e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-70.666</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.135006119951049</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7344244984160547</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.004152712659027</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.759837092731814</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.75832372707492</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.143208650833428</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-18462.85703754847</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>21.60878799582497</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.826008644242491</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1671.581</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8130356643441677</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2078.623487630881</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8540452322285295</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.30304e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-70.87</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2628532974428122</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8041509433962931</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.140512333965837</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.154610951008759</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.78996971321338</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.190171697026022</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-18355.64765139138</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.8037024747725354</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000083176e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8263375904205432</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1658.271</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8065618502170503</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2008.543896457852</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8252515901504901</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.30797e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-71.11799999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3218403547672029</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8378521126760539</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.279046129788924</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.381999999999885</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>83.45126095644565</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.710999328556046</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-17156.13490481778</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>20.53778824273479</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8266969867697139</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1636.18</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7958170697600895</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1986.861151073106</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8163427880381008</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.31384e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-71.34699999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5927016645326141</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.244992947813806</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.65286738351246</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.917790262172152</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.17518335639733</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.355468768286636</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-16227.32390932036</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>19.69729632798294</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8270545364460221</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1615.278</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7856506037281582</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1964.405588836847</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8071164582198297</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.32064e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-71.587</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.337026239067047</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7141509433962131</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.6944600938967</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.715100864553279</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>82.28085262154526</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.377590253911315</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-14059.64894322642</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>19.88237998120792</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000003576e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.827436630697757</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1595.891</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7762210143605832</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1946.276854201701</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7996678945556476</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.32462e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-71.815</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5232258064515973</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.40558659217883</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.475256916996072</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.577396893411866</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>81.89092025946779</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>7.018392932429194</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-13177.04396881474</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>18.18950512683375</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8278227955550146</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1571.486</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7643507338367441</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1925.687154798075</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7912081928764716</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.33055e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-72.033</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.4485568760610772</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.3660098522167387</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8396864686468625</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.070670391061319</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>81.68937925222713</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>6.845866801445387</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12692.44696356226</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>17.56382128648568</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.380833949190603e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8209815868380305</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1549.121</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7534726832767908</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1904.800392722738</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7826264368858934</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.33788e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-72.25700000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3045882352941126</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.083644189383168</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.084695817490599</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.190494296577945</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>80.74281756918141</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6.135382375984592</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-11148.92228587478</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>16.86785700149562</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.40792039562032e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8195633697059974</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1529.287</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7438256788141879</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1885.905349883963</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.774863019727742</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.34189e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-72.465</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6690962099124523</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4795226130653476</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.24868651488616</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.827852586817832</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>80.35663735634036</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5.885264029021153</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-10532.81262975529</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>15.39136659109988</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000101e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8290581426232366</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1508.896</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7339077566604654</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1864.966397556627</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7662598202981987</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.34684e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-72.685</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3172727272727013</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.179904306220037</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.312691466083251</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.819213114754107</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>79.50211583326845</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>5.39662936502856</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9469.764652776803</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>14.71233909877833</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8294699482796445</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1493.872</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.726600274808789</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1841.705597004931</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7567026417484474</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.35226e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.93300000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.109752066115668</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.109416445623318</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.43614457831318</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3869.825999999938</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.020329891677771</v>
+      </c>
+      <c r="M42" t="n">
+        <v>75.13928367587035</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>3.768672979039274</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-6233.095012111938</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>15.38192514641082</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000169e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8298965896031515</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1460.396</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7103179756563188</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1824.696391825402</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7497140597979327</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.35769e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-73.16800000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1232809430255364</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4383522727273231</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8847385272144909</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.583150800337002</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>76.35452891099136</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4.11919820013659</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-6862.051675706942</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>13.00517354415001</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8303157667479026</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.000000000029683e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8269492738709937</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2177.713</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2564.878471699803</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.11868e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-65.646</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1098455598455433</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8441637630661368</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.59448123620311</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.576652692679827</v>
+      </c>
+      <c r="L23" t="n">
+        <v>42.35610608393787</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.47740357708268</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.64245775396967</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-32182.28269469809</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.050131809995037</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000087e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8220981973325222</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2055.358</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9438149104128967</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2421.797745513826</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9442153974292771</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.14598e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-67.401</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1445640473627439</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.6408829174663828</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.086684599865488</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.933839022334632</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.02176452649005</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.40729846195727</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.44866727823189</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-30102.17944132951</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>19.99408535860152</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000192e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.822087465869785</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2036.184</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9350102607643892</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2451.698659030889</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9558732259958082</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.14944e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.93000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1706691109074243</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7913617886179025</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.306173496540693</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.670488044546418</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3.270687415058976</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.6031663285822</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.00555575634132</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-31151.40379032491</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-3.712714906933343</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000637e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8219147326852899</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2002.642</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9196078638461542</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2368.269045038438</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9233455195516274</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.15305e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-68.21599999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.08549734244494966</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.6131639722863405</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.241092814371271</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.204386792452783</v>
+      </c>
+      <c r="L26" t="n">
+        <v>18.783876611418</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.33117075431733</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.24480590383915</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-28949.67655070433</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>21.99563627117027</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8219250745537761</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1990.091</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.91384447812912</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2408.55538375971</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9390524386769505</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.15907e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.55500000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.185291005290999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9443946188340352</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.407814149947247</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.088693373268399</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.41581355186332</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.4718898332636</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-29241.17998515358</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-5.374448934996963</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8220989419735825</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1957.682</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8989623517883212</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2383.888739231748</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9294353574779282</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.16352e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.83199999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1442020665901259</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3890710382513604</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.092827256425648</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.273155929038388</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4.669810255625353</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.17673575532864</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.85097246861213</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-27379.5874050473</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-6.676267689965698</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.00000000000006e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8223384124082387</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1928.249</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.88544679670829</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2357.208147501865</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9190330744753337</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.17234e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-69.12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1422163588390584</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8428044280441966</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.244055433989742</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.127853260869508</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.07080889104667</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>11.59507811208227</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-26427.70560616207</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-7.962447989406201</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000878e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8225911753494387</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1902.033</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8734084794460979</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2331.718705352123</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9090951992773524</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.17781e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.401</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.008898305084734433</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4965798045602346</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.209722222222238</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.978830823737812</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.93251314701644</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.27705041499087</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-25369.22255346926</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-8.877229603165006</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000696e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.822851788607222</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1876.253</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8615703722207656</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2305.578093959543</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8989034448995099</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.18538e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.67400000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.07467532467532592</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9119820828667052</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.888967343336295</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.504748908296921</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.7572836689485</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>10.8981259096984</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-24202.13855168521</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-9.032549250940292</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000002331e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8230841242048756</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1843.411</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.846489413435104</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2209.870358393891</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8615887196126529</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.1917e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.905</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1583710407239683</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1160780669144989</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6299870466321181</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.853763440860316</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.7256032147506585</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.48698420787788</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>10.36072652966269</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-22687.21857963646</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>21.9468639984982</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000386e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8233149760934312</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1821.224</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8363012022245355</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2261.026274759222</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8815334916280804</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.19756e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-70.202</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.03377403846153303</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.2061965811966036</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9566897918732133</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.95441176470595</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.05746256025441</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.607038328102856</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-20732.16588551441</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-10.82469200645733</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000299e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8235502638891337</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1803.778</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8282900455661515</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2162.84132032558</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8432529432446036</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.20377e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.38200000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1953846153846251</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7242004264392643</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.460220994475175</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.540000000000011</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.19017320735685</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.828050558208488</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-21023.29645173243</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>22.12494099597961</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000076e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8238066182788678</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1783.416</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8189398694869344</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2141.515766030338</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8349384930550361</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.20764e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.608</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.07652270210409827</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.897517730496484</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.261376404494422</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.359563409563315</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.0597828895913</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.610818009825834</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-20322.20238838419</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>21.90743859321242</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8240655230017409</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1761.645</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8089426843665809</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2121.136645381281</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8269930403273867</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.2129e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.81</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3312101910827592</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9457249070630582</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.36671675431999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.87262124002458</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>83.8901954968315</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.342105661777383</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-19518.57299755024</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>21.46630147040878</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000107e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8243369069067397</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1742.101</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7999681317051422</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2100.76527456546</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8190506091203748</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.21886e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-71.004</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2723427331887356</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4587778855480008</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.881640624999999</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.153864059590277</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.74941351313974</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.130071237065776</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-18859.62323868267</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>20.66310976711634</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000084e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8246493687092759</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1721.975</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7907263261963354</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2080.119539871911</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8110012083704567</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.22354e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.259</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3485675306957466</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.011145833333333</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.50279569892478</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.426176176176132</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>83.06412942258612</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.220400592297104</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-16703.09046365776</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>20.17536436277805</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8249770548153392</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1697.583</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7795255848681621</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2054.310648771054</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8009387857700782</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.22879e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.473</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3025757575757648</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4279661016948995</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.9549635036496484</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.920328282828279</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.7794422333864</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.893038477879482</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-15828.72167675995</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>21.99579637022543</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000782e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8253435196826101</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1677.044</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7700941308611375</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2032.643562072578</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7924911782371892</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.2336e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.724</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0949105914718029</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4800632911392513</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.006318082788606</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.934666666666655</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.04578403029792</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.156861038940522</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14100.43427184204</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>21.26719278779683</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8257276008085358</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1657.118</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7609441648187802</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2012.610673419676</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7846807151396432</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.23833e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-71.91800000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2085981308411403</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.520278099652362</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.153530950305083</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.137734537873553</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>81.99373261841544</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.109726657969135</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-13842.07640576425</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>19.70736196993857</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8261241899379637</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1632.993</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.749866029178317</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1989.408186950281</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7756344828423215</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.24414e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.128</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3473491773308761</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6112412177986117</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9204152249134706</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.947265077139058</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>81.49581742349871</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>6.687816557150684</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-12814.5406608731</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>19.93219540840209</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8265312128622175</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1611.377</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.739940019644462</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1965.805139294828</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7664320789405841</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.24924e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.405</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1813106796116408</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4153474903474602</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.620291616038882</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.153587443946236</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>79.35258673424356</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>5.319105195019072</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9880.899672481139</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>19.83073733038066</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000029683e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8269492738709937</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.000000000000015e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8247099040408369</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2030.383</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2460.394035668148</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.22095e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-63.118</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1220486111111091</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7008005822416385</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.347007366482514</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.093574186431338</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17.32987887890171</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.03803453681488</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.575506236164767</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-23184.55585740781</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-18.78379116456813</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8226209941140983</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1768.114</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8708278191848533</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2149.769564843025</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.873750112249492</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.29232e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-67.717</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3162087912088161</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5683640303358953</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.548994974874328</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.045325389550874</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30.13223226671916</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.74417511292592</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.43813964239288</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-29079.41320062482</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>12.41124778768653</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000027034e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8231340282117653</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1691.148</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.83292068540763</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2065.137650595122</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8393524048006035</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.28638e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-69.13500000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4070301291248039</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.41938283510127</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.020137299771166</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.854754505904197</v>
+      </c>
+      <c r="L14" t="n">
+        <v>30.07278178709917</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.89763405516429</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.94264609402739</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-29117.09723860739</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>21.14150753977083</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.823235943927017</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1663.227</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8191690927278252</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2035.259485512774</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8272087543733927</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.27723e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-69.914</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1895899053627418</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.121363040629071</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.664781491002689</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.585289163391339</v>
+      </c>
+      <c r="L15" t="n">
+        <v>41.67392060173427</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.22216617206217</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.14431993250762</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-31187.05100397402</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>18.54906242079892</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8232282947826255</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1622.174</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7989497547999564</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2071.150698279291</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8417963416647799</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.27069e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-70.39400000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2501182033096876</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.476215738284692</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9676067073171003</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.858579088471822</v>
+      </c>
+      <c r="L16" t="n">
+        <v>33.16918599947498</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.09348935868756</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.64400672490536</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-29621.55290490708</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-12.37632746289205</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000214e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8233952573463059</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1587.455</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7818500253400467</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2043.74230546287</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8306565029157489</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.26984e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-70.85599999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.08515624999999723</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.05123966942147855</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9014038876890423</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.702127659574402</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27.18575678552921</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.85877222536543</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.81135608980062</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-27432.60076755711</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-13.30552305778258</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000017374e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8235924097749807</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1563.381</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7699931490758148</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2021.236619118559</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8215093151002818</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.26812e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.202</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.3318627450980517</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.3161538461538473</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.832163742690067</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.872208883553501</v>
+      </c>
+      <c r="L18" t="n">
+        <v>33.56191142807042</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.16905453599718</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.93374736148099</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-29333.3200110806</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-17.14617271267423</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8238469270957746</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1529.002</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7530608757067015</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1915.833941673823</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7786695602005702</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.26852e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-71.56100000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1249999999999899</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2471956224350241</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.154967502321266</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.69293924466331</v>
+      </c>
+      <c r="L19" t="n">
+        <v>28.45347751775343</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.03247901786544</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.4181144247495</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-27820.63681942162</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>18.35687005329771</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000022e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8241363452360965</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1506.849</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7421501263554708</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1969.117939802747</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8003262531353075</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.26951e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-71.896</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5293670886075377</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.479439252336388</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.164573991031357</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.363161711385153</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.00875072411803</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.25867427784912</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.29252632478277</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-29172.18338027941</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-20.40534374478159</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000348e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8244195535222555</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1487.658</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7326982150658274</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1947.733356305642</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7916347251982804</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.27246e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-72.233</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6108481262326875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.952957359009571</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.866439135380954</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.969736842105297</v>
+      </c>
+      <c r="L21" t="n">
+        <v>32.92381894142269</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.28112362820183</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.38510325869044</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-28947.25785771579</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-23.22518473667935</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8247099040408369</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8279655906794595</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2113.896</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2496.526199445871</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.2132e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-64.26000000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.04047393364928762</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9164908916586658</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.285432473444619</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.188699551569524</v>
+      </c>
+      <c r="L23" t="n">
+        <v>30.79266949516174</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.15439600006185</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.79607618392666</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-29342.81972963851</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.681141724488725</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.00000000000011e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8222241979160136</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1995.458</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9439716996484219</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2426.043925059417</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.971767861117541</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.23485e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-66.61</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1341726618705011</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3148979591836766</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.114285714285739</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.914896373057035</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.29955128211617</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.43070239531707</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.51270257503911</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-29607.45348988348</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-6.85561836091324</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000001217e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8223748627702101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1967.076</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9305453059185504</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2323.39236102786</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9306501015465253</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.23952e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.298</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.02356389214536648</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8233937397034857</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.6879128137385</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.63320920785384</v>
+      </c>
+      <c r="L25" t="n">
+        <v>36.48417236147111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.68678733577332</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.2586799007924</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-30951.44415194967</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>21.41968037702304</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001151e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8223615677257196</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1929.858</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9129389525312506</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2361.258975845411</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9458178233296798</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.24564e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-67.818</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1156488549618358</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4454767726161264</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9403225806451495</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.093678707224317</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20.74049801809669</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.27414832266591</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.09639920983481</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-27757.30246292592</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-6.745111030436874</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8223624909571154</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1910.006</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9035477620469503</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2334.356107238078</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9350417022485935</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.25379e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.19799999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03056603773584505</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9198096885813276</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.962694651320219</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.734963768115925</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.4115635437113</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.46028835942666</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-28307.20923820126</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-7.172760386253231</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8225151409289783</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1877.66</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8882461578053037</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2283.366967376909</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9146176666937144</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.26035e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.468</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2323809523809657</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3945261437908364</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.756717687074789</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.155678160919474</v>
+      </c>
+      <c r="L28" t="n">
+        <v>8.7414236785126</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.13057979456765</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.73810518550821</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-26260.51963328112</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.895747018420934</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000504e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8226875476927562</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1860.218</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.879995042329424</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2258.947606941955</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9048363311562087</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.26865e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-68.752</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2087649402390367</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7957403651115159</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.456453488372073</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.871153846153851</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.30570000872549</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.17807113455072</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-27001.91315188662</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.731901816980553</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8228613277627862</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1834.022</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8676027581300122</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2233.46667537408</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8946297763147131</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.2748e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.023</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6843888070692123</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.814323784143848</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.726468481375337</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.22706329430788</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.97652255515362</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-26231.71028594182</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.287761656460589</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8230824662655123</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1810.193</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8563302073517337</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2211.542671619737</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8858479723187409</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.28008e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.279</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1899147727272484</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9814285714285785</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.669898605830247</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.747302608074345</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.11867932411808</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11.70934970729109</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-25330.30802200493</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.356816486704929</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000142e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8233193736138535</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1780.483</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8422755897168075</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2186.950554686992</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8759974380290533</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.28817e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.54000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2600000000000281</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9957678355501665</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.346407624633448</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.555450500556183</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.81339168368416</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.0166774388787</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-23485.12470902395</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.353656556083706</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8236209212926803</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1764.524</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8347260224722505</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2165.473114022616</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.867394507817809</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.29736e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-69.783</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4852941176471022</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.008219178082242</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.484637350085594</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.932651485912797</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.77473285432448</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.93472255779627</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-23048.36933268379</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-0.01153974949579606</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8239501520027088</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1727.338</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8171348070103733</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2141.612084268411</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8578368153091139</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.30153e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.101</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.01227495908346669</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6361702127659588</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.146112886048983</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.839500912964054</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.05446588382652</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>9.602161265969851</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19862.95549832066</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.4823524885539427</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000196e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8243123698056691</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1702.523</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8053958189049983</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2068.519582375173</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8285591326196786</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.30755e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.367</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1147627416520174</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.489266547406058</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.109372236958438</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.703928571428658</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.69720606072319</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.053838899109923</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-18460.8542965073</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>21.55391450362572</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000123e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8246902588566679</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1682.053</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7957122772359664</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2046.784537400939</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8198530173067056</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.31374e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.598</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2696458684654143</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3953455571226735</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9396378269618257</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.513562091503234</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>83.58707067747386</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8.897076074909853</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-17913.34268513276</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>20.60227575914143</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.825081230583431</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1670.223</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7901159754311471</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2024.155359300325</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8107887510852508</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.3206e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-70.815</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.2981461286804799</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7021837349397462</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.379871692061011</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.618269747447632</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>83.4736610241447</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8.741159248358283</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-17384.61005729551</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>20.4674245021132</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000007969e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8254671928352076</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1644.115</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7777653205266485</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2001.817440535976</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8018411507078513</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.32423e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.054</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.07460317460317165</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2896718146718121</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.314396887159522</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.988235294117687</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>83.27502334215912</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.480687778600023</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-16647.10093931793</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>20.11264504717849</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000512e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8258693475308785</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1620.976</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7668191812653037</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1980.804470636032</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7934242673182006</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.33175e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.309</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.03333333333333663</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.4337625178826869</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.161163032191077</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.47549842602309</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>82.39789008811356</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>7.492546707066781</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-14434.2722710301</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>19.27996398672792</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8262783354061436</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1600.633</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7571957182377941</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1959.408131879426</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7848538230098832</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.3373e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.505</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1572496263079194</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3895072992700779</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.316071428571395</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.602076970067188</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.35609982469042</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.451097844058213</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-14192.03971697599</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>18.99737892865267</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000014787e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8266918028915716</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1579.877</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.747376881360294</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1939.629081621498</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7769311942538468</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.34266e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-71.741</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4541910331383483</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.3448359659781006</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.727453416149203</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1.770740223463655</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>81.76283892476937</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>6.907779746240011</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-12937.89300768527</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>17.8540758211592</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000839e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8271051462140998</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1560.119</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7380301585319241</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1918.831775727499</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7686006965011635</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.34789e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-71.97199999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3286451612903075</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6538261997405984</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.336847710330121</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1.804721549636801</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>81.06612897739333</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>6.361261055691005</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-11706.66105071141</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>16.93877759413363</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.363638032946128e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8213434993113213</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1543.47</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7301541797704335</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1896.945842908872</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7598341420690553</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.35429e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.19</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3031746031746149</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7615631691648806</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.370565749235529</v>
+      </c>
+      <c r="K43" t="n">
+        <v>601.8416753926655</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.042389155177109</v>
+      </c>
+      <c r="M43" t="n">
+        <v>79.43008667995478</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>5.359014765432666</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-9586.32539212309</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>16.81983081886983</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8279655906794595</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.000000000000184e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8226377992422598</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2174.471</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2693.417200024134</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.20078e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-60.202</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1040333796940281</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4511385816525647</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.285525070955493</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.053920181149171</v>
+      </c>
+      <c r="L12" t="n">
+        <v>14.08887945959876</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.00035781414279</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.144766929927242</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-21007.56366235087</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-58.4039162128779</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8204215626802764</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1764.7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8115537066256574</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2155.854395974762</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8004160647505498</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.33503e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-67.166</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.537909186905984</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9771992818670909</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.627439024390211</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.618230277185515</v>
+      </c>
+      <c r="L13" t="n">
+        <v>39.97008204670375</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.8198252162511</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.68222325035115</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-29762.80413971239</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.904102133535162</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.00000000000072e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8214456177052405</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1671.263</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7685837153036302</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2121.713561895538</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7877404071959316</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.3384e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-68.83799999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3777960526315622</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.6938461538461717</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.315348208248859</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.392331768388165</v>
+      </c>
+      <c r="L14" t="n">
+        <v>36.82064225037296</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.01260614144554</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.34602480409702</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-29847.4360263286</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-13.64630869741836</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000021011e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8215641561774838</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1625.661</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7476121778584309</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2088.955386813252</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7755780971453414</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.33246e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-69.529</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2934782608695099</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.798453038674102</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.613242009132506</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.757312252964392</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29.96204194217254</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.85115141078617</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.78589804091581</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-28068.06724866177</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-14.59204268270878</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8215930723633277</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1597.852</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7348233202466254</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2062.783227390022</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7658610137974684</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.32974e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-69.97199999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8006726457398874</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4491614255765128</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.762284820031518</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.653255131964861</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.88959434536302</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.93285633669966</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.06380409498742</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-28245.92726466854</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-16.37732550080716</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8216909541616423</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1564.899</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7196688297981439</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2043.501739456507</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7587022684187938</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.33135e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-70.355</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1713080168776374</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4923588039867518</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.064382239382267</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.398034591195023</v>
+      </c>
+      <c r="L17" t="n">
+        <v>25.60772086173403</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.78326682271455</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.56317675557796</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-26819.05838577188</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-19.59565762949728</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000003992e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8217908062015363</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1538.293</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7074332101922721</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2019.436418192933</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7497674026047052</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.33142e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-70.691</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1009324009323884</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5792279411765235</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9313294797687937</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.509238249594776</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.23455671333188</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.83747668403021</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.74044962876983</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-26811.47510177144</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-20.73524079667425</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000146e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8219453149809027</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1513.229</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6959067285790429</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2000.074936558932</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.74257895751947</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.33424e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-71.036</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.3611260053619244</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5078864353312126</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9369418132610492</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.52115518441191</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25.80868672096129</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.83781108931814</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.74155747999234</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-26448.81097753151</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-24.3411257098287</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8221534722933097</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1488.29</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6844377322116505</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1886.560967701142</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7004339942895729</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.33649e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-71.327</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.009266409266412539</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4111398963730439</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.112142038946202</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.49617834394908</v>
+      </c>
+      <c r="L20" t="n">
+        <v>25.74560314492659</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.88364294295634</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.89509371658258</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-26404.51397399669</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>17.71761307824954</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000004222e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8223805662431459</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1459.921</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6713913406984963</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1952.918946431251</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7250710905142183</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.34023e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-71.66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9051109736292599</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.697284832594463</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.119095126010044</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.619261944851646</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.66028011763316</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>13.17738752761341</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-24635.61255281352</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-26.40572936000797</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8226377992422598</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000000728e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8275681735177792</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2093.148</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2488.11695803149</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.23371e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-64.34099999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0809061488673158</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1023454157782567</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8288996372430152</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.029238095238278</v>
+      </c>
+      <c r="L23" t="n">
+        <v>25.00162207437533</v>
+      </c>
+      <c r="M23" t="n">
+        <v>84.97606556400319</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.37532048525893</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-28098.65600786905</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.643315672264407</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000011e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8218694643867974</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1979.778</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9458375614146729</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2405.614718431081</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9668414945953014</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.25922e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-66.69</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3217267552181979</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8364925373134581</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.549771092217152</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.675247175141254</v>
+      </c>
+      <c r="L24" t="n">
+        <v>43.30795581512977</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.65134975680714</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.15022264494989</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-30921.52940052495</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-7.508719957563471</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000001159e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8221500865567808</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1936.725</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9252690206330368</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2296.155983892136</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9228488944140203</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.26895e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.27</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2802492809203852</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8331536388139784</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.434259727134891</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.594490644490689</v>
+      </c>
+      <c r="L25" t="n">
+        <v>31.00766521514688</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.64293230504576</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.12471970893197</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-30303.514849251</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>22.81293313244919</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8221849038869791</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1901.838</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9086017806672056</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2333.519845095925</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9378658175868559</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.27855e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-67.661</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.02744886975242326</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2292573143286009</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.184395318595566</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.224987775061072</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.21012721728083</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.30943588204234</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.18781407529653</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-27674.41706039802</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-5.783799477316734</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.822277231834462</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1881.244</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8987630115022922</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2239.102292625791</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.899918424412528</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.28716e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.130037546933661</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6874023437500634</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.442436727486785</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.646309898565917</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.48201254710068</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>12.65540850339689</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-28438.26903061018</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>22.33207316189032</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000622e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8225465393082664</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1844.162</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8810471118143581</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2253.533429023407</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9057184477398211</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.29535e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.31399999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00669856459328325</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7736998514114718</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.110273556231087</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.233889418493688</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12.84863328387019</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.15700123226335</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>11.80245208977526</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-26079.56078795576</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.074329198468149</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000005275e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8228030056295692</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1818.872</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.86896483191824</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2225.484599377334</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8944453323199318</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.30346e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-68.599</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.05796105383735044</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8685685685686056</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.173164392462603</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.309392547217955</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8.38602817894076</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.08619277063494</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>11.63155880635866</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-25375.22291093219</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.350535055195905</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8230318450763889</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1789.279</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8548267967673571</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2204.034789626985</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8858244314088592</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.30949e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-68.84</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2586466165413275</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.2469072164948295</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6554216867469626</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.452947424322871</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.82751354128434</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.9062979099409</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>11.21870740715667</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-24136.30563903323</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.567178505536731</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.823273375898105</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1769.016</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.845146162622041</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2131.664081689658</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8567378936141954</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.31837e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.161</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3041666666666669</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7017297297297563</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.511480362537788</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.199494949494985</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.87960821906553</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11.1599205966619</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-23748.95608733457</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>22.70665169963536</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000007143e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.823525410754765</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1748.982</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8355749330673224</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2157.514004773915</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8671272456905978</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.32653e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.352</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.03813333333334976</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.035560588901516</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.365130111524119</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.042268041237089</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>84.94434092385205</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11.30357114063363</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-23811.52145006346</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.7529993816947353</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000017284e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8237838347778901</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1720.424</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8219313684459962</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2135.774173577194</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8583897821535457</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.33275e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-69.622</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2040350877193175</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.6175544794189241</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.328907168037511</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.700172018348655</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5.137615845988649</v>
+      </c>
+      <c r="M33" t="n">
+        <v>84.55642893097483</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.49371455950274</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-21778.60456972539</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.5059858652023195</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000004286e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8240697090143507</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1699.803</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.812079700049877</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2115.586778287053</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8502762587016125</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.33855e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-69.863</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3227790432801905</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4027737226277694</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.696302003081642</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.824007330482529</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2.854485635614069</v>
+      </c>
+      <c r="M34" t="n">
+        <v>84.50021061082096</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.38579723572532</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-21320.76304847044</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-0.5688275645898102</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000065e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8243677071297558</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1671.467</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7985421957740206</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2095.624145631742</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8422530696827552</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.34328e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.08499999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0133086876155333</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.03235955056179655</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.066167023554578</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.220197740113074</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8.021444629477305</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.26300311926651</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>9.953669445178058</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-20159.52844389887</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-1.652417648127312</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000197e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8246845197610774</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1664.904</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7954067270923986</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2075.339745151342</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8341005588391943</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.35094e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.354</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2200371057513933</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.057422680412351</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.587196110210733</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.006810709253115</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>84.13873340762382</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>9.741200637983383</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-19518.80075947692</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-2.604728517144622</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000004113e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8250098687698577</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1653.147</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7897898285262197</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2001.739651560084</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8045199182050466</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.35864e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-70.565</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5773881499395267</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9449699054170516</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.641075650118218</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.995249597423582</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.04451907982248</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9.58600799485348</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-18992.52057695977</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>21.20101201500643</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000308e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8253397893911518</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1615.759</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7719277375512863</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1982.940707282916</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7969644276094433</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.36385e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-70.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2260245901639544</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7179012345678809</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.246932952924365</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>83.513309699044</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8.795051481163036</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-17149.4884667881</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>20.06670557395853</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000010564e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8256829077079835</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1602.056</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7653811388396807</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1961.447993840404</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7883262832597034</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.37029e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.01300000000001</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.1558904109588963</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3820568927789874</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.128640308582387</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1.718535031847054</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>83.38946512490763</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>8.628851252904269</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-16631.39926971079</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>20.07927148353042</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000010925e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8260437833206654</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1579.637</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7546704771951147</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1941.743282918325</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7804067556593332</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.37695e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.254</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.04683698296836433</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.3808618504435921</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.165964172813463</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.891546391752542</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>82.83076238342716</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>7.950140409021635</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-15087.00295811185</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>19.46247048430723</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000713e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.826405951208726</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1568.663</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7494276563339046</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1921.510724457245</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7722750806607883</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.3828e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-71.467</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3764705882353017</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5918181818181696</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.673052245646301</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.454574811625402</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>82.57466012938002</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>7.673002776236249</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-14364.12233441492</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>18.78763703453649</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000094e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8267873042100341</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1548.828</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.739951498890666</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1902.707258938189</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7647177729311982</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.38759e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-71.675</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5140703517588011</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7286191536747774</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.462418831168834</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.608103545300964</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>82.45793970557759</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>7.552905227386511</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-13962.15478543122</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>17.49054643197815</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000501e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8271748786062363</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1523.119</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7276690420362057</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1881.249951042898</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7560938584379393</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.39541e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-71.93300000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2981967213114778</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.4647777777777389</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.179924242424327</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.298817034700333</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>81.27339245855396</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>6.514793796397279</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-11790.90891477915</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>17.35501053921587</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000728e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8275681735177792</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.000000000053009e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8264845125175559</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2015.446</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2557.360760399212</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.2951e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-61.452</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4160278745644348</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9753569211669666</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.625624024961014</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.661461051062258</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17.09758723828508</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.55552605910758</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.853159625008077</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-21350.10912091603</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-74.5116978831627</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000024413e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8242984860832673</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1701.466</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8442131419050672</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2158.791762286517</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8441483093490191</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.3632e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-67.754</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5007399577167322</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.313785310734404</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.601752402487271</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.968958893584331</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40.9674588641219</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.91443960564308</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.0001938732639</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-29479.66127775418</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-28.9571422842921</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000012586e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8251235722242805</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1615.332</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.801476199312708</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2078.141571161396</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.81261181579911</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.35847e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-69.217</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1504424778761148</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4919014084506652</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.888244766505627</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.847430058555695</v>
+      </c>
+      <c r="L14" t="n">
+        <v>28.59654714010141</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.76694640305577</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.51069463908578</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-27298.55563783196</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-22.76122943816836</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8252129352714285</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1579.975</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7839331840198149</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2127.449932037373</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8318927720253563</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.35448e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-69.95099999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.04457274826789211</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2721719457013488</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.137408088235341</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.86001213592231</v>
+      </c>
+      <c r="L15" t="n">
+        <v>29.68672015104412</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.81296358917007</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.65972128107918</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-27115.73589711453</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-61.7455928055216</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.825212890366271</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1560.663</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7743511857921275</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2016.321091553708</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.7884382691626793</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.35076e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-70.405</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4699186991869847</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8912816041848701</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.544372093023271</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.292757371960615</v>
+      </c>
+      <c r="L16" t="n">
+        <v>37.34837149265547</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.07823582328332</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.58687223386161</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-28667.12261074701</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-21.71715331664791</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.382244200619495e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8159039158184652</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1533.154</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7607020976994671</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2084.080679222739</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8149341741277863</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.35186e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-70.762</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.312907608695647</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4997455470738197</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.265306122448948</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.038978668390476</v>
+      </c>
+      <c r="L17" t="n">
+        <v>28.97436229499401</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.90297124511967</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.96087133101888</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-26993.33078943432</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-66.94031516858831</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000015584e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8254023148446075</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1503.626</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7460512462254012</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1967.091583769562</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7691881467136039</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.35504e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.176</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.0251213592232991</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4588571428571035</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.468770764119623</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.950234427327516</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.47506797986986</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.85662652813693</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>13.8041787308637</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-26286.68335206001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-24.42561171256386</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000427e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8256323614413871</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1478.668</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.733667882940054</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1942.470403962876</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7595605727756809</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.35779e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-71.517</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5572078907435488</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2037720033529005</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.529585152838445</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.894195583596128</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25.41187575372227</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.86279157538219</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>13.82482081850526</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-25941.16270923146</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-26.84250871407369</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8259010857081182</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1444.883</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7169048438906327</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2023.711928782582</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7913282944353438</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.36144e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-71.828</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5006482982171756</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.784459459459438</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8204139228598286</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.287045454545467</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.54277039829208</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.65624277715484</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.165092706867</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-24281.90336628448</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-79.61173240024209</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8261887128519112</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1415.103</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7021289580569264</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2011.846598422314</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.786688616473594</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.36593e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-72.128</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3775688605583363</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.699446554381619</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.103115810472999</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.43695396758204</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>12.52991837568329</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-22725.38444258767</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-86.2931485681471</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000053009e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8264845125175559</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000047997e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8321209555534694</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2087.227</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2515.522287757915</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.25991e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-64.831</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.5723749999999403</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.312478031634365</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.685557894736832</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.170070648683279</v>
+      </c>
+      <c r="L23" t="n">
+        <v>101.8860566448791</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.63524863918384</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.10152568608163</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-32128.84861043092</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-19.67369677572424</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000032e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8252253134487614</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1975.505</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9464734789268249</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2462.479749076472</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9789139062931064</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.27602e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-66.834</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1120231213872788</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5649017933390124</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.376593465452596</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.604135338345854</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.16175837511034</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.35730990994833</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12.31405156636912</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-28740.52815406123</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-36.9916220655864</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8254504445705302</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1936.978</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9280150170537272</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2421.856342349786</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9627648119581507</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.28726e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-67.413</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1365753424657578</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8870329670329908</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.791141034727171</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.553001053001076</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.35317263523869</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.30303966469938</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-28195.25688813455</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-37.4367592435608</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8255304963047722</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1906.245</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9132906962203921</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2394.24535172561</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9517885662860101</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.29696e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-67.84699999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3219745222929785</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.635750853242292</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.457060849598147</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.557975034674046</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.09924036513074</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.66267838901804</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-26301.86661403129</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-39.7987893601321</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8256235195939408</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1875.23</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8984312678975501</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2367.955896618826</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9413376729527549</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.3042e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-68.17400000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.001942740286291946</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6601859024012048</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.530011520737455</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.77569648093854</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.97962710126282</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11.383431827165</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-25313.03262601143</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-41.51579620730081</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000001853e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8257504715414885</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1848.091</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8854288488985625</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2268.691032367803</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9018767368544712</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.31277e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-68.489</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3398137369033932</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8916666666666568</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.454398663697092</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.92703020792467</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.75671805038773</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.8969436870905</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-23891.63781397516</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-10.42486121754882</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000656e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8259028022210997</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1824.38</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8740688003748515</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2290.82983944102</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9106776157737153</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.32009e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-68.764</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2668428005283719</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8126948775055723</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.583255269320848</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.592251815980618</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.64720096815343</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.67273194047834</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-23111.43067449572</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-31.24233755280147</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000001725e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8260852607427001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1807.371</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.865919710697495</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2219.278776100495</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8822337957015431</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.3284e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-69.053</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1503042596348779</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8238645747316141</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.557203907203963</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.822773777946202</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.35774023042264</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.12191088673692</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-21624.09864836832</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-11.21450631050561</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000001761e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8263354310367195</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1783.667</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8545630159057928</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2244.460618222683</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8922443776966774</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.33579e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-69.334</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2535256410256428</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.080947012401343</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.715498392282939</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.681988873435331</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>83.98921141455334</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.497161802539541</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-19985.38718802719</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-33.20215337616969</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8266642920549608</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1757.416</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8419860417673786</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2222.417102958223</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8834813802977926</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.34293e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-69.59699999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2878995433790343</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7415413533834884</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.8355057705363</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.962480680061886</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.69762411592801</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>9.054444339298467</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-18778.43135635072</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-34.69937760300149</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8270396121778827</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1725.554</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8267208118714447</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2199.736442828971</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8744650975800323</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.34913e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-69.849</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1959459459459592</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3916809605488831</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.632053742802306</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.623685800604308</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.55078183886248</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.8465917255314</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-18100.47329219053</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-36.53738914332666</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000000153e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8274583103561436</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1701.919</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8153971752952602</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2124.393478621933</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8445138764862248</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.35566e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-70.139</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0144110275689139</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.022893772893792</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.447757475083052</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.34336877448235</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>82.96560479702194</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.104124007129103</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-16302.09312969965</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-14.10313270389111</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8278971848263614</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1666.991</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.7986630107793738</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2098.382711640865</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8341737705338136</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.36302e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-70.392</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3474254742547305</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.001884057971008142</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4034155597723186</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.181689141234956</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.55800099243558</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.655632473944894</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-15156.61205430785</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-14.05760049760829</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8283458396673902</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1663.012</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7967566536845299</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2076.75206254782</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8255749005503065</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.37135e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-70.64</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.5605324074074219</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.640379403794121</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.584392699811261</v>
+      </c>
+      <c r="K36" t="n">
+        <v>596.9381465517057</v>
+      </c>
+      <c r="L36" t="n">
+        <v>7.13848497661192</v>
+      </c>
+      <c r="M36" t="n">
+        <v>81.75868938459175</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>6.904253241952115</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-13392.69519369811</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-16.07190884855345</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8288164091000833</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1639.766</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7856193887871324</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2055.904907271061</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8172874942417979</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.37598e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-70.94199999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5507763975154822</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8870071684588102</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.683710961420757</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5140.91018518183</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.44372470179876</v>
+      </c>
+      <c r="M37" t="n">
+        <v>80.34619777210902</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>5.878777862048966</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11112.43555011945</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-18.05374419918383</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000587e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8292669708099299</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1601.694</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7673789194946213</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2029.408788352388</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8067544454798689</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.38251e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-71.146</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1912977099236809</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.3223985890652784</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.169556840077134</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.643558282208636</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>81.52007563877578</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>6.707231645344365</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12675.7855336765</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-16.91970043217873</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000016e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8297354120510478</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1590.057</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7618035795819047</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2009.516921611974</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7988467967036208</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.38904e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-71.414</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0245330012453345</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.646008869179612</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.894066985646014</v>
+      </c>
+      <c r="K39" t="n">
+        <v>384.7309065933882</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.346020165896984</v>
+      </c>
+      <c r="M39" t="n">
+        <v>79.82663183593523</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>5.572627045231184</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10239.6909478978</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-19.51460762186468</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000055e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8302051714946416</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1565.619</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7500952220338277</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1983.391273957533</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7884610220350422</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.3969e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-71.696</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1837096774193462</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.7720183486238464</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.737690631808223</v>
+      </c>
+      <c r="K40" t="n">
+        <v>935.6347245408055</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.555251169481611</v>
+      </c>
+      <c r="M40" t="n">
+        <v>76.98816776782273</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>4.327398508367631</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7640.345798778478</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-18.77662171749864</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000026e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8306727791216445</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1542.369</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7389560407181395</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1962.631351781541</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7802082936545293</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.40298e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-71.95399999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.1939580764488281</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.50547147846332</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.573830845771184</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3400.357575757806</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6.825901617404211</v>
+      </c>
+      <c r="M41" t="n">
+        <v>74.31179345564641</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3.560426366862554</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-6039.21534301539</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-20.91603623869776</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000002782e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8311611615719875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1512.118</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7244626482888541</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1936.848506684789</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7699587938897181</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.41056e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-72.226</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.08940170940169886</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6626112759643923</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.216792249730922</v>
+      </c>
+      <c r="K42" t="n">
+        <v>785.3685236767851</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6.044026163819121</v>
+      </c>
+      <c r="M42" t="n">
+        <v>72.70441040408457</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>3.211501033589583</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-5310.017213698121</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-20.56400765772207</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.0000000000003e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8316375930716181</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1499.942</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7186290710114425</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1917.895599076186</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7624244111888219</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.41613e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-72.45</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3944367176634253</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7806768558952196</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.437854609929031</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>7.078815382166172</v>
+      </c>
+      <c r="M43" t="n">
+        <v>60.72049696681752</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.783473718065563</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-2490.739084547793</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-22.41645841463617</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000047997e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8321209555534694</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8303035760423194</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1564.238</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2169.937480610714</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.46739e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-65.28700000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.148071495766701</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4071428571428432</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.168761220825841</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.485561797752806</v>
+      </c>
+      <c r="L12" t="n">
+        <v>13.14007254924212</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.81095713910436</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.22158113214561</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-18277.82618051678</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-105.5190131430252</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.521377037002092e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8096593554514424</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1311.817</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8386300550172032</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1818.69660154962</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8381331802415619</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.46746e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-71.31699999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.09920159680639046</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8220216606497706</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.163281249999947</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.802617801047157</v>
+      </c>
+      <c r="L13" t="n">
+        <v>26.92419408642001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.13256016928565</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.79240498817922</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-25629.09437306778</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-51.47950509675843</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8277510929816904</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1257.615</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8039793177253076</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1751.124431780698</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8069930343282776</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.4432e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-72.71299999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3014109347442888</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4793048973144131</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.291356382978837</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.710690789473662</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31.59098951499389</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.43465412858183</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.04944060331486</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-26886.77868228229</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-45.06185427425066</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.827919603522968</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1224.055</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7825247820344474</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1881.933579650155</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8672754844164901</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.43125e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-73.36799999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1564978190786663</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8641974120131196</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.822934842459651</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.371834686067927</v>
+      </c>
+      <c r="L15" t="n">
+        <v>90.59509644737403</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.25734388198219</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.2870748294734</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-25053.52312847711</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-126.8942363770689</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000031e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8280891351992294</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1206.946</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7715871881388893</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1847.860257834997</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8515730403969657</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.42612e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-73.81</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.199054820415874</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.056344410876083</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.572947976878567</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.281065918653554</v>
+      </c>
+      <c r="L16" t="n">
+        <v>38.56824195629877</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.67647062046937</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17.2200984019528</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-27927.97081087231</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-125.2318487986388</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8283454907159454</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1168.768</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7471804162793642</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1674.714629933562</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7717801295649429</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.42319e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-74.22199999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2498593865056875</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.197721990346083</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.857777937773798</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.520881064632068</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.578145077480873</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.27229855641723</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.3485774849083</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-24313.63993911394</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-50.24574117894508</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8286812595417239</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1137.28</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7270504872020753</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1792.443715436506</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8260347274761278</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.42295e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-74.518</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.09165315017653425</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6457027632349499</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.32994630754852</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.385940363634762</v>
+      </c>
+      <c r="L18" t="n">
+        <v>37.68441587148421</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.06161589753195</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.52512274261547</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-22522.8502908081</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-127.0491592408197</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000668e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8290768969353889</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1119.487</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7156756196947011</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1854.51340099124</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8546390933204676</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.42347e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-74.91800000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5078999893496523</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8008512156044596</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.045334526025893</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.667334227684406</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.21354702955047</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.10974652623057</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-23105.8503023518</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-176.2792810255982</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.829482136310853</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1096.526</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.700996907120272</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1825.836214030399</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8414234190362617</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.42372e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-75.209</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5554768075315711</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.25520627560639</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.399482020099188</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.848198602599174</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.27818843129664</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.37293567916594</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-23136.45351873905</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-176.0846286442279</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8298934578820746</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1069.946</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6840046079944355</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1798.828263351845</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8289770002247148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.42542e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-75.501</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4094739861139957</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.159202638471224</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.077429005319718</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.016222018158163</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.0168749706659</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.36144957870862</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-21211.2100944628</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-175.6593026687447</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000010075e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8303035760423194</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
